--- a/Dataset/Dataset Produk.xlsx
+++ b/Dataset/Dataset Produk.xlsx
@@ -68,9 +68,7 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
@@ -439,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7388,17 +7386,17 @@
       <c r="A195" s="3" t="inlineStr">
         <is>
           <t>Azarine
-AHA-BHA-PHA Peeling Serum Marvel Edition</t>
+Pore Tightening &amp; Oil Control Moist Serum</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycolic Acid, Lactic Acid, Mandelic Acid, Salicylic Acid, Portulaca Oleracea Extract, Carica Papaya Fruit Extract, Sodium Hyaluronate, Lactobionic Acid, Aloe Barbadensis Leaf Juice, Allantoin, Royal Jelly, Chlorphenesin, Phenoxyethanol, Xanthan Gum, Gluconobacter/​Honey Ferment Filtrate"</t>
+          <t>"Aqua, Glycerin, Propanediol, Centella Asiatica Extract, Backhousia Citriodora Leaf Extract, Pistacia Lentiscus Gum, Sodium Hyaluronate, Epilobium Angustifolium Flower/​Leaf/​Stem Extract, Chlorphenesin, Phenoxyethanol, Xanthan Gum, Hydrogenated Lecithin, Caprylic/​Capric Triglyceride"</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -7407,16 +7405,16 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>49000</v>
+        <v>48000</v>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasl-m125ignof06cdc@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasc-m125ignoj7vo7e@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8pjHL7MpQF</t>
+          <t>https://s.shopee.co.id/LkjDaukcp</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7422,7 @@
       <c r="A196" s="3" t="inlineStr">
         <is>
           <t>Azarine
-Pore Tightening &amp; Oil Control Moist Serum</t>
+Niacinamide 10% + Dipotassium Glycyrrhizate Glorious Serum</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -7434,7 +7432,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Propanediol, Centella Asiatica Extract, Backhousia Citriodora Leaf Extract, Pistacia Lentiscus Gum, Sodium Hyaluronate, Epilobium Angustifolium Flower/​Leaf/​Stem Extract, Chlorphenesin, Phenoxyethanol, Xanthan Gum, Hydrogenated Lecithin, Caprylic/​Capric Triglyceride"</t>
+          <t>"Aqua, Niacinamide, Glycerin, Camellia Sinensis Leaf Water, Acetyl Glucosamine, Chlorphenesin, Caprylic/​Capric Triglyceride, Cetyl Palmitate, Sorbitan Stearate, Xanthan Gum, Polysorbate 80, Hydrogenated Lecithin, Palmitoyl Tetrapeptide-10, Potassium Hydroxide, Dipotassium Glycyrrhizate"</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -7443,16 +7441,16 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>48000</v>
+        <v>59000</v>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasc-m125ignoj7vo7e@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7qul6-lhsh5a7ecfjdd0@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/LkjDaukcp</t>
+          <t>https://s.shopee.co.id/4ftiNbUF7K</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7458,7 @@
       <c r="A197" s="3" t="inlineStr">
         <is>
           <t>Azarine
-Niacinamide 10% + Dipotassium Glycyrrhizate Glorious Serum</t>
+Azarine Daily Defender Multivitamin Serum</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -7470,7 +7468,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Glycerin, Camellia Sinensis Leaf Water, Acetyl Glucosamine, Chlorphenesin, Caprylic/​Capric Triglyceride, Cetyl Palmitate, Sorbitan Stearate, Xanthan Gum, Polysorbate 80, Hydrogenated Lecithin, Palmitoyl Tetrapeptide-10, Potassium Hydroxide, Dipotassium Glycyrrhizate"</t>
+          <t>"Aqua, Glycerin, Butylene Glycol, Ectoin, Resveratrol, Chlorphenesin, Allantoin, Phenoxyethanol, Tocopherol, Niacinamide, Panthenol, Biotin, Folic Acid, Ascorbic Acid, Retinyl Palmitate, Pyridoxine Hcl, Xanthan Gum, Arachis Hypogaea Oil"</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -7479,16 +7477,16 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>59000</v>
+        <v>60000</v>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7qul6-lhsh5a7ecfjdd0@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r992-lzisxz0brle029.webp</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4ftiNbUF7K</t>
+          <t>https://s.shopee.co.id/8Kn0kOWX9F</t>
         </is>
       </c>
     </row>
@@ -7496,17 +7494,17 @@
       <c r="A198" s="3" t="inlineStr">
         <is>
           <t>Azarine
-Azarine Daily Defender Multivitamin Serum</t>
+PHA 10% + Astaxanthin Hilarious Serum</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Eksfoliasi</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Butylene Glycol, Ectoin, Resveratrol, Chlorphenesin, Allantoin, Phenoxyethanol, Tocopherol, Niacinamide, Panthenol, Biotin, Folic Acid, Ascorbic Acid, Retinyl Palmitate, Pyridoxine Hcl, Xanthan Gum, Arachis Hypogaea Oil"</t>
+          <t>"Aqua, Lactobionic Acid, Glycerin, Camellia Sinensis Leaf Water, Sodium Hyaluronate, Propanediol, Baicalin, Chlorphenesin, Enteromorpha Compressa Extract, Silybum Marianum Fruit Extract, Ocimum Sanctum Leaf Extract, Xanthan Gum, Polyacrylate Crosspolymer-6, Potassium Hydroxide, Citric Acid, Astaxanthin"</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -7515,16 +7513,16 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>60000</v>
+        <v>59000</v>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r992-lzisxz0brle029.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7qukw-lhshcb89q1nr17@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8Kn0kOWX9F</t>
+          <t>https://s.shopee.co.id/2qS4CKRiYr</t>
         </is>
       </c>
     </row>
@@ -7532,17 +7530,17 @@
       <c r="A199" s="3" t="inlineStr">
         <is>
           <t>Azarine
-PHA 10% + Astaxanthin Hilarious Serum</t>
+Radiant Luminous Serum</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Lactobionic Acid, Glycerin, Camellia Sinensis Leaf Water, Sodium Hyaluronate, Propanediol, Baicalin, Chlorphenesin, Enteromorpha Compressa Extract, Silybum Marianum Fruit Extract, Ocimum Sanctum Leaf Extract, Xanthan Gum, Polyacrylate Crosspolymer-6, Potassium Hydroxide, Citric Acid, Astaxanthin"</t>
+          <t>"Aqua, Glycerin, Arbutin, Propanediol", Portulaca Oleracea Extract, Prunus Lannesiana Flower Extract, Gluconobacter/​Honey Ferment Filtrate", Chlorphenesin, Allantoin, Phenoxyethanol, Panthenol, Xanthan Gum", Dimethylmethoxy Chromanyl Palmitate"</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -7551,16 +7549,16 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>59000</v>
+        <v>49000</v>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7qukw-lhshcb89q1nr17@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasc-m1294ohw7pusf1@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/2qS4CKRiYr</t>
+          <t>https://s.shopee.co.id/7fXJxIoCAk</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7566,7 @@
       <c r="A200" s="3" t="inlineStr">
         <is>
           <t>Azarine
-Radiant Luminous Serum</t>
+Retinol Complex + 5x Ceramide Mighty Serum</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7578,7 +7576,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Arbutin, Propanediol", Portulaca Oleracea Extract, Prunus Lannesiana Flower Extract, Gluconobacter/​Honey Ferment Filtrate", Chlorphenesin, Allantoin, Phenoxyethanol, Panthenol, Xanthan Gum", Dimethylmethoxy Chromanyl Palmitate"</t>
+          <t>"Aqua, Glycerin, Retinol, Dimethyl Isosorbide, Chlorphenesin, Squalane, Ceteareth-25, Hydroxypinacolone Retinoate, Cetyl Alcohol, Polyacrylate Crosspolymer-6, Behenic Acid, Cholesterol, Ceramide NP, Ceramide NS, Ceramide EOS, Ceramide EOP, Ceramide AP, Caprooyl Phytosphingosine, Caprooyl Sphingosine, Mannitol, Phosphatidylcholine, Retinal, Potassium Sorbate, Sodium Benzoate, Citric Acid, Sodium Chloride"</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -7587,16 +7585,16 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>49000</v>
+        <v>59000</v>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasc-m1294ohw7pusf1@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-q2cy5i1v9fovfa@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/7fXJxIoCAk</t>
+          <t>https://s.shopee.co.id/1LdGPhPnSl</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7602,7 @@
       <c r="A201" s="3" t="inlineStr">
         <is>
           <t>Azarine
-Retinol Complex + 5x Ceramide Mighty Serum</t>
+Vitamin C 10% + Diamond Booster Serum</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -7614,7 +7612,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Retinol, Dimethyl Isosorbide, Chlorphenesin, Squalane, Ceteareth-25, Hydroxypinacolone Retinoate, Cetyl Alcohol, Polyacrylate Crosspolymer-6, Behenic Acid, Cholesterol, Ceramide NP, Ceramide NS, Ceramide EOS, Ceramide EOP, Ceramide AP, Caprooyl Phytosphingosine, Caprooyl Sphingosine, Mannitol, Phosphatidylcholine, Retinal, Potassium Sorbate, Sodium Benzoate, Citric Acid, Sodium Chloride"</t>
+          <t>"Aqua, Ascorbyl Glucoside, Glycerin, Propanediol, Diamond Powder, Hydroxyresveratrol, Guaiazulene, Chlorphenesin, Polyacrylate Crosspolymer-6, Xanthan Gum, Polyglyceryl-10 Oleate, Potassium Hydroxide, Polyglyceryl-6 Laurate, Sorbitan Palmitate"</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -7623,24 +7621,24 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>59000</v>
+        <v>88000</v>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-q2cy5i1v9fovfa@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-23030-h6k2wxu6neovd3.webp</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/1LdGPhPnSl</t>
+          <t>https://s.shopee.co.id/20sxDAoofR</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>Azarine
-Vitamin C 10% + Diamond Booster Serum</t>
+          <t>Whitelab
+Glow Booster C-dose+ Serum</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7650,25 +7648,25 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Ascorbyl Glucoside, Glycerin, Propanediol, Diamond Powder, Hydroxyresveratrol, Guaiazulene, Chlorphenesin, Polyacrylate Crosspolymer-6, Xanthan Gum, Polyglyceryl-10 Oleate, Potassium Hydroxide, Polyglyceryl-6 Laurate, Sorbitan Palmitate"</t>
+          <t>"Aqua, Methylpropanediol, Glycerin, Propylene Glycol, Butylene Glycol, 3-O-Ethyl Ascorbic Acid, Niacinamide, Ferulic Acid, Allantoin, Phenoxyethanol, Panthenol, Xanthan Gum, Polyglyceryl-6 Laurate, Polyglyceryl-10 Oleate, Sorbitan Palmitate, Soluble Collagen, Tetrasodium EDTA, Glycine Soja (Soybean) Oil, Ethylhexylglycerin, PEG-40 Hydrogenated Castor Oil, Sodium Bisulfite, Squalane, Centella Asiatica Leaf Extract, Honokiol, Magnolol, Dipotassium Glycyrrhizate, Pentylene Glycol, Glycyrrhiza Glabra Root Extract, Tris (Tetramethylhydroxypiperidinol) Citrate, Hydrogenated Lecithin, Tocopherol, Citric Acid, Sodium Hyaluronate, Sodium Benzoate, Ci 18965, Potassium Sorbate, Ascorbyl Propyl Hyaluronate, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Potassium Hyaluronate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate Crosspolymer, Dimethylsilanol Hyaluronate, Parfum, Ci 17200"</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>88000</v>
+        <v>75000</v>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-23030-h6k2wxu6neovd3.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0l-mcc3c6waxj9hc9@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/20sxDAoofR</t>
+          <t>https://s.shopee.co.id/2qS4ClPbur</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7674,7 @@
       <c r="A203" s="3" t="inlineStr">
         <is>
           <t>Whitelab
-Glow Booster C-dose+ Serum</t>
+Brightening Booster Serum - Niacinamide 5%</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -7686,7 +7684,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Methylpropanediol, Glycerin, Propylene Glycol, Butylene Glycol, 3-O-Ethyl Ascorbic Acid, Niacinamide, Ferulic Acid, Allantoin, Phenoxyethanol, Panthenol, Xanthan Gum, Polyglyceryl-6 Laurate, Polyglyceryl-10 Oleate, Sorbitan Palmitate, Soluble Collagen, Tetrasodium EDTA, Glycine Soja (Soybean) Oil, Ethylhexylglycerin, PEG-40 Hydrogenated Castor Oil, Sodium Bisulfite, Squalane, Centella Asiatica Leaf Extract, Honokiol, Magnolol, Dipotassium Glycyrrhizate, Pentylene Glycol, Glycyrrhiza Glabra Root Extract, Tris (Tetramethylhydroxypiperidinol) Citrate, Hydrogenated Lecithin, Tocopherol, Citric Acid, Sodium Hyaluronate, Sodium Benzoate, Ci 18965, Potassium Sorbate, Ascorbyl Propyl Hyaluronate, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Potassium Hyaluronate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate Crosspolymer, Dimethylsilanol Hyaluronate, Parfum, Ci 17200"</t>
+          <t>"Aqua, 1,2 Propanediol, Niacinamide, Methylpropanediol, Licorice (Glycyrrhiza Glabra) Extract, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Sodium Hyaluronate Crosspolymer, Sodium Hyaluronate, Sodium Carboxymethyl Hyaluronate, Sodium Acetylated Hyaluronate, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Sodium Hyaluronate, Dimethylsilanol Hyaluronate, Marine Collagen, Soluble Collagen, Allantoin, Dipotassium Glycyrrhizate, Glycerin, Carbomer, PEG-40 Hydrogenated Castor Oil, Triethanolamine, 1,2-Hexanediol, Pentylene Glycol, Phenoxyethanol, DMDM Hydantoin, Parfum"</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -7695,16 +7693,16 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>75000</v>
+        <v>73000</v>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0l-mcc3c6waxj9hc9@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztm-mf9nnlo8svt756@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/2qS4ClPbur</t>
+          <t xml:space="preserve">https://s.shopee.co.id/4qD8aTcE0g </t>
         </is>
       </c>
     </row>
@@ -7712,7 +7710,7 @@
       <c r="A204" s="3" t="inlineStr">
         <is>
           <t>Whitelab
-Brightening Booster Serum - Niacinamide 5%</t>
+N10 Dose Brightening Serum</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -7722,7 +7720,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, 1,2 Propanediol, Niacinamide, Methylpropanediol, Licorice (Glycyrrhiza Glabra) Extract, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Sodium Hyaluronate Crosspolymer, Sodium Hyaluronate, Sodium Carboxymethyl Hyaluronate, Sodium Acetylated Hyaluronate, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Sodium Hyaluronate, Dimethylsilanol Hyaluronate, Marine Collagen, Soluble Collagen, Allantoin, Dipotassium Glycyrrhizate, Glycerin, Carbomer, PEG-40 Hydrogenated Castor Oil, Triethanolamine, 1,2-Hexanediol, Pentylene Glycol, Phenoxyethanol, DMDM Hydantoin, Parfum"</t>
+          <t>"Aqua, Niacinamide, Glycerin, Methylpropanediol, Phenoxyethanol, Soluble Collagen, Allantoin, Glycine Soja (Soybean) Oil, Glycyrrhiza Glabra Root Extract, Disodium Succinate, Saccharomyces Lysate, Tributyl Citrate, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Potassium Hyaluronate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate Crosspolymer, Sodium Hyaluronate, Valine, Threonine, Glutamic Acid, Glycine, Tocopherol, Ascorbyl Propyl Hyaluronate, Dimethylsilanol Hyaluronate, PEG-40 Hydrogenated Castor Oil, Buteth-3, Dipotassium Glycyrrhizate, Tetrasodium EDTA, Ethylhexylglycerin, Sodium Benzotriazolyl Butylphenol Sulfonate, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Triethanolamine, Potassium Sorbate, Sodium Benzoate, Pentylene Glycol, Parfum"</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -7731,16 +7729,16 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>73000</v>
+        <v>82000</v>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztm-mf9nnlo8svt756@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0j-mcc3qu536fd1a5.webp</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://s.shopee.co.id/4qD8aTcE0g </t>
+          <t>https://s.shopee.co.id/8ATaYk858U</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7746,7 @@
       <c r="A205" s="3" t="inlineStr">
         <is>
           <t>Whitelab
-N10 Dose Brightening Serum</t>
+Acne Calming Serum</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -7758,25 +7756,25 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Glycerin, Methylpropanediol, Phenoxyethanol, Soluble Collagen, Allantoin, Glycine Soja (Soybean) Oil, Glycyrrhiza Glabra Root Extract, Disodium Succinate, Saccharomyces Lysate, Tributyl Citrate, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Potassium Hyaluronate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate Crosspolymer, Sodium Hyaluronate, Valine, Threonine, Glutamic Acid, Glycine, Tocopherol, Ascorbyl Propyl Hyaluronate, Dimethylsilanol Hyaluronate, PEG-40 Hydrogenated Castor Oil, Buteth-3, Dipotassium Glycyrrhizate, Tetrasodium EDTA, Ethylhexylglycerin, Sodium Benzotriazolyl Butylphenol Sulfonate, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Triethanolamine, Potassium Sorbate, Sodium Benzoate, Pentylene Glycol, Parfum"</t>
+          <t>"Aqua, Artemisia Capillaris (Mugwort) Extract, Methylpropanediol, Caprylic/​Capric Triglyceride, Propylene Glycol, Niacinamide, Aluminum Starch Octenylsuccinate, Centella Asiatica Extract, Salicylic Acid, Hexamidine Diisethionate, Melaleuca Alternifolia Leaf Extract, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Sodium Hyaluronate Crosspolymer, Sodium Hyaluronate, Sodium Carboxymethyl Hyaluronate, Sodium Acetylated Hyaluronate, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Sodium Hyaluronate, Dimethylsilanol Hyaluronate, Marine Collagen, Soluble Collagen, Dipotassium Glycyrrhizate, Allantoin, Glycerin, Sodium PCA, Trimethylpentanediol/​Adipic Acid Copolymer, PEG-6 Caprylic/​Capric Glycerides, Polyacrylamide, C13-14 Isoparaffin, C9-11 Pareth-6, 1,2-Hexanediol, DMDM Hydantoin, Xanthan Gum, Perfume"</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>82000</v>
+        <v>64000</v>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0j-mcc3qu536fd1a5.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0j-mcbru8zw92yv6f@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8ATaYk858U</t>
+          <t>https://s.shopee.co.id/4AxRnQoTtN</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7782,7 @@
       <c r="A206" s="3" t="inlineStr">
         <is>
           <t>Whitelab
-Acne Calming Serum</t>
+Hydrating Serum</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7794,12 +7792,12 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Artemisia Capillaris (Mugwort) Extract, Methylpropanediol, Caprylic/​Capric Triglyceride, Propylene Glycol, Niacinamide, Aluminum Starch Octenylsuccinate, Centella Asiatica Extract, Salicylic Acid, Hexamidine Diisethionate, Melaleuca Alternifolia Leaf Extract, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Sodium Hyaluronate Crosspolymer, Sodium Hyaluronate, Sodium Carboxymethyl Hyaluronate, Sodium Acetylated Hyaluronate, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Sodium Hyaluronate, Dimethylsilanol Hyaluronate, Marine Collagen, Soluble Collagen, Dipotassium Glycyrrhizate, Allantoin, Glycerin, Sodium PCA, Trimethylpentanediol/​Adipic Acid Copolymer, PEG-6 Caprylic/​Capric Glycerides, Polyacrylamide, C13-14 Isoparaffin, C9-11 Pareth-6, 1,2-Hexanediol, DMDM Hydantoin, Xanthan Gum, Perfume"</t>
+          <t>"Aqua, Glycerin, Galactomyces Ferment Filtrate, Saccharide Isomerate, Panthenol, Phenoxyethanol, Carbomer, 1,2-Hexanediol, Triethanolamine, Ammonium Acryloyldimethyl Taurate/​VP Copolymer, Tetrasodium EDTA, Allantoin, Soluble Collagen, Pentylene Glycol, Ethylhexylglycerin, Butylene Glycol, Betula Alba Juice, PEG-40 Hydrogenated Castor Oil, Sodium Hyaluronate, Citric Acid, Sodium Citrate, Laminaria Digitata Extract, Sodium Acetylated Hyaluronate, Hydrolyzed Hyaluronic Acid, Sodium Hyaluronate Crosspolymer, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Sodium Hyaluronate, Hyaluronic Acid, Perfume, Hydrogenated Lecithin, Cetyl-Pg Hydroxyethyl Palmitate, Cholesterol, Dimethylsilanol Hyaluronate, Ascorbyl Propyl Hyaluronate, Ceramide EOP, Ceramide NS, Ceramide NP, Ceramide AS, Ceramide AP"</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E206" s="3" t="n">
@@ -7807,12 +7805,12 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0j-mcbru8zw92yv6f@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasb-m4efdr2sjxdmb0.webp</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4AxRnQoTtN</t>
+          <t>https://s.shopee.co.id/4qD8ahT8If</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7818,7 @@
       <c r="A207" s="3" t="inlineStr">
         <is>
           <t>Whitelab
-Hydrating Serum</t>
+Retinol Treatment Serum</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -7830,33 +7828,33 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Galactomyces Ferment Filtrate, Saccharide Isomerate, Panthenol, Phenoxyethanol, Carbomer, 1,2-Hexanediol, Triethanolamine, Ammonium Acryloyldimethyl Taurate/​VP Copolymer, Tetrasodium EDTA, Allantoin, Soluble Collagen, Pentylene Glycol, Ethylhexylglycerin, Butylene Glycol, Betula Alba Juice, PEG-40 Hydrogenated Castor Oil, Sodium Hyaluronate, Citric Acid, Sodium Citrate, Laminaria Digitata Extract, Sodium Acetylated Hyaluronate, Hydrolyzed Hyaluronic Acid, Sodium Hyaluronate Crosspolymer, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Sodium Hyaluronate, Hyaluronic Acid, Perfume, Hydrogenated Lecithin, Cetyl-Pg Hydroxyethyl Palmitate, Cholesterol, Dimethylsilanol Hyaluronate, Ascorbyl Propyl Hyaluronate, Ceramide EOP, Ceramide NS, Ceramide NP, Ceramide AS, Ceramide AP"</t>
+          <t>"Aqua, Cyclopentasiloxane, Methylpropanediol, Polysorbate 20, Polyglutamic Acid, Retinol, Ferulic Acid, Glycerin, Sodium PCA, Bisabolol, Soluble Collagen, Dipotassium Glycyrrhizate, Allantoin, Glucosyl Ceramide, Ceramide NP, Ceramide AP, Ceramide EOP, Phospholipids, Cholesterol, Phytosphingosine, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-10, Dipeptide-1, Acetyl Tetrapeptide-9, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Sodium Hyaluronate Crosspolymer, Sodium Hyaluronate, Sodium Acetylated Hyaluronate, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Dimethylsilanol Hyaluronate, Hydrolyzed Sodium Hyaluronate, Ascorbyl Propyl Hyaluronate, Phenoxyethanol, C13-14 Alkane, Laureth-7, Polyacrylamide, Trimethylpentanediol/​Adipic Acid Copolymer, BHT, DMDM Hydantoin, Parfum, Iodopropynyl Butylcarbamate, Carbomer"</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>64000</v>
+        <v>73000</v>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasb-m4efdr2sjxdmb0.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztm-mergl6bor0n546@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4qD8ahT8If</t>
+          <t>https://s.shopee.co.id/3g1BCazyzo</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>Whitelab
-Retinol Treatment Serum</t>
+          <t>white story
+Acne Soothing Serum</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7866,7 +7864,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Cyclopentasiloxane, Methylpropanediol, Polysorbate 20, Polyglutamic Acid, Retinol, Ferulic Acid, Glycerin, Sodium PCA, Bisabolol, Soluble Collagen, Dipotassium Glycyrrhizate, Allantoin, Glucosyl Ceramide, Ceramide NP, Ceramide AP, Ceramide EOP, Phospholipids, Cholesterol, Phytosphingosine, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-10, Dipeptide-1, Acetyl Tetrapeptide-9, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Sodium Hyaluronate Crosspolymer, Sodium Hyaluronate, Sodium Acetylated Hyaluronate, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Dimethylsilanol Hyaluronate, Hydrolyzed Sodium Hyaluronate, Ascorbyl Propyl Hyaluronate, Phenoxyethanol, C13-14 Alkane, Laureth-7, Polyacrylamide, Trimethylpentanediol/​Adipic Acid Copolymer, BHT, DMDM Hydantoin, Parfum, Iodopropynyl Butylcarbamate, Carbomer"</t>
+          <t>"Aqua, Cyclopentasiloxane, Ethyl Alcohol, Niacinamide, Salicylic Acid, Centella Asiatica Extract, Propylene Glycol, Isononyl Isononanoate, Licorice (Glycyrrhiza Glabra) Extract, Glycerin, Polysorbate 20, Polyacrylamide, C13-14 Isoparaffin, C9-11 Pareth-6, Xanthan Gum, Parfum, Sodium Hyaluronate, Hexamidine Diisethionate"</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -7875,24 +7873,24 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>73000</v>
+        <v>48000</v>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztm-mergl6bor0n546@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk2-m9ijo5dvkw0t8a@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3g1BCazyzo</t>
+          <t>https://s.shopee.co.id/9pboXyJhDj</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>white story
-Acne Soothing Serum</t>
+          <t>Eiem Beauty
+Brightening Serum</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7902,7 +7900,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Cyclopentasiloxane, Ethyl Alcohol, Niacinamide, Salicylic Acid, Centella Asiatica Extract, Propylene Glycol, Isononyl Isononanoate, Licorice (Glycyrrhiza Glabra) Extract, Glycerin, Polysorbate 20, Polyacrylamide, C13-14 Isoparaffin, C9-11 Pareth-6, Xanthan Gum, Parfum, Sodium Hyaluronate, Hexamidine Diisethionate"</t>
+          <t>"Aqua, Niacinamide (10%), Palmitoyl Tripeptide-5, Resveratrol, Tocopheryl Acetate, Propanediol, Phenoxyethanol, Panthenol, Allantoin, Beeswax, Euphorbia Cerifera (Candelilla) Wax, PVOH, Lecithin, Ethylhexylglycerin, Niacin, Thioctic Acid, Theobroma Cacao (Cocoa) Seed Butter, Glycerin, Panax Ginseng Root Extract, Dimethyl Sulfone, Portulaca Oleracea Extract, Hydroxyethyl Cellulose, Sodium Coco-Glucoside Tartrate, Tetrasodium EDTA"</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -7911,16 +7909,16 @@
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>48000</v>
+        <v>39000</v>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk2-m9ijo5dvkw0t8a@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbkd-m86hjuo4vmy582@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9pboXyJhDj</t>
+          <t>https://s.shopee.co.id/50WYnAA1QA</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7926,7 @@
       <c r="A210" s="3" t="inlineStr">
         <is>
           <t>Eiem Beauty
-Brightening Serum</t>
+Hydration Booster Serum</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7938,7 +7936,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide (10%), Palmitoyl Tripeptide-5, Resveratrol, Tocopheryl Acetate, Propanediol, Phenoxyethanol, Panthenol, Allantoin, Beeswax, Euphorbia Cerifera (Candelilla) Wax, PVOH, Lecithin, Ethylhexylglycerin, Niacin, Thioctic Acid, Theobroma Cacao (Cocoa) Seed Butter, Glycerin, Panax Ginseng Root Extract, Dimethyl Sulfone, Portulaca Oleracea Extract, Hydroxyethyl Cellulose, Sodium Coco-Glucoside Tartrate, Tetrasodium EDTA"</t>
+          <t>"Aqua, Hydrolyzed Sodium Hyaluronate, Honey, Niacinamide, Hydrolyzed Collagen, Sodium Acetylated Hyaluronate, Panthenol, Hydroxypropyltrimonium Hyaluronate, Acetyl Glucosamine, Allantoin, Glucose, Pentylene Glycol, Lactobacillus/​Collagen/​Mesembryanthemum Crystallinum Leaf Extract Ferment Lysate, Glucuronolactone, Sodium Hyaluronate, Xanthan Gum, Glycine, Phenoxyethanol, Sodium PCA, Polyglutamic Acid, 1,2-Hexanediol, Urea, Lysine Hydrochloride, Glycerin, Propanediol, Fructose, Ethylhexylglycerin, Citric Acid, Tetrasodium EDTA"</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -7947,16 +7945,16 @@
         </is>
       </c>
       <c r="E210" s="3" t="n">
-        <v>39000</v>
+        <v>37000</v>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbkd-m86hjuo4vmy582@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk0-m86hjuo4n7jh0d@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/50WYnAA1QA</t>
+          <t>https://s.shopee.co.id/6L1wNdzBk8</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7962,7 @@
       <c r="A211" s="3" t="inlineStr">
         <is>
           <t>Eiem Beauty
-Hydration Booster Serum</t>
+Acne + Anti Aging Serum</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7974,7 +7972,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Hydrolyzed Sodium Hyaluronate, Honey, Niacinamide, Hydrolyzed Collagen, Sodium Acetylated Hyaluronate, Panthenol, Hydroxypropyltrimonium Hyaluronate, Acetyl Glucosamine, Allantoin, Glucose, Pentylene Glycol, Lactobacillus/​Collagen/​Mesembryanthemum Crystallinum Leaf Extract Ferment Lysate, Glucuronolactone, Sodium Hyaluronate, Xanthan Gum, Glycine, Phenoxyethanol, Sodium PCA, Polyglutamic Acid, 1,2-Hexanediol, Urea, Lysine Hydrochloride, Glycerin, Propanediol, Fructose, Ethylhexylglycerin, Citric Acid, Tetrasodium EDTA"</t>
+          <t>"Water, Glycerin, Propylene Glycol, Polysorbate 80, Sodium Carboxymethyl Cellulose, Retinol, Avena Sativa (Oat) Meal Extract, Allantoin, Tocopheryl Acetate, Panthenol, Phaseolus Radiatus Seed Extract, Hydrogenated Lecithin, Caprylic/​Capric Triglyceride, BHT, Ethylhexylglycerin, Cholesterol, Citric Acid, Phenoxyethanol, BHA, Methyl Methacrylate Crosspolymer, Tetrasodium EDTA"</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -7983,16 +7981,16 @@
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>37000</v>
+        <v>36000</v>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk0-m86hjuo4n7jh0d@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbkc-m86h8y6t86wd29.webp</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/6L1wNdzBk8</t>
+          <t>https://s.shopee.co.id/6femmHgxM1</t>
         </is>
       </c>
     </row>
@@ -8000,17 +7998,17 @@
       <c r="A212" s="3" t="inlineStr">
         <is>
           <t>Eiem Beauty
-Acne + Anti Aging Serum</t>
+Full Acid Peeling Solution</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Eksfoliasi</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycerin, Propylene Glycol, Polysorbate 80, Sodium Carboxymethyl Cellulose, Retinol, Avena Sativa (Oat) Meal Extract, Allantoin, Tocopheryl Acetate, Panthenol, Phaseolus Radiatus Seed Extract, Hydrogenated Lecithin, Caprylic/​Capric Triglyceride, BHT, Ethylhexylglycerin, Cholesterol, Citric Acid, Phenoxyethanol, BHA, Methyl Methacrylate Crosspolymer, Tetrasodium EDTA"</t>
+          <t>"Water, Glycolic Acid, Lactic Acid, Aloe Barbadensis Leaf Juice, Polyvinyl Alcohol, Trisodium Citrate, Triethanolamine, Propylene Glycol, Citric Acid, Salicylic Acid, Mandelic Acid, Maltodextrin, Tetrasodium EDTA, Gluconolactone, Bisabolol, Capryloyl Salicylic Acid, Propanediol, Sodium PCA, Mel (Honey), Urea, Fructose, Glucose, Centella Asiatica Extract, Pentylene Glycol, Glycine, Acetyl Glucosamine, Glucuronolactone, Lysine Hydrochloride, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Camellia Sinensis Leaf Extract, Glycyrrhiza Glabra (Licorice) Root Extract, Chamomilla Recutita (Matricaria) Flower Extract, Ci 27755, Rosmarinus Officinalis (Rosemary) Leaf Extract, Ci 16035, Hydrolyzed Collagen, 1,2-Hexanediol, Caprylyl Glycol, Tropolone, Phenoxyethanol, Parfum, Ethylhexylglycerin, Potassium Sorbate, Sodium Benzoate"</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -8019,52 +8017,52 @@
         </is>
       </c>
       <c r="E212" s="3" t="n">
-        <v>36000</v>
+        <v>42000</v>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbkc-m86h8y6t86wd29.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk3-m86i4fk8ed6g3b@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/6femmHgxM1</t>
+          <t>https://s.shopee.co.id/8V6QxhUMjI</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>Eiem Beauty
-Full Acid Peeling Solution</t>
+          <t>Emina
+Bright Stuff Face Serum</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycolic Acid, Lactic Acid, Aloe Barbadensis Leaf Juice, Polyvinyl Alcohol, Trisodium Citrate, Triethanolamine, Propylene Glycol, Citric Acid, Salicylic Acid, Mandelic Acid, Maltodextrin, Tetrasodium EDTA, Gluconolactone, Bisabolol, Capryloyl Salicylic Acid, Propanediol, Sodium PCA, Mel (Honey), Urea, Fructose, Glucose, Centella Asiatica Extract, Pentylene Glycol, Glycine, Acetyl Glucosamine, Glucuronolactone, Lysine Hydrochloride, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Camellia Sinensis Leaf Extract, Glycyrrhiza Glabra (Licorice) Root Extract, Chamomilla Recutita (Matricaria) Flower Extract, Ci 27755, Rosmarinus Officinalis (Rosemary) Leaf Extract, Ci 16035, Hydrolyzed Collagen, 1,2-Hexanediol, Caprylyl Glycol, Tropolone, Phenoxyethanol, Parfum, Ethylhexylglycerin, Potassium Sorbate, Sodium Benzoate"</t>
+          <t>"Aqua, Niacinamide, Glycerin, Propanediol, Phenoxyethanol, Allantoin, Sodium Polyacrylate Starch, Chlorphenesin, Xanthan Gum, Disodium EDTA, Butylene Glycol, Sodium Hyaluronate, Actinidia Polygama Fruit Extract"</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>42000</v>
+        <v>55000</v>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk3-m86i4fk8ed6g3b@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0g-mckh9j2eg6k789.webp</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8V6QxhUMjI</t>
+          <t>https://s.shopee.co.id/7KuTZbTCAS</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8070,7 @@
       <c r="A214" s="3" t="inlineStr">
         <is>
           <t>Emina
-Bright Stuff Face Serum</t>
+Glorad+ High-res Bright Glow Water-sphere Serum</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -8082,25 +8080,25 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Glycerin, Propanediol, Phenoxyethanol, Allantoin, Sodium Polyacrylate Starch, Chlorphenesin, Xanthan Gum, Disodium EDTA, Butylene Glycol, Sodium Hyaluronate, Actinidia Polygama Fruit Extract"</t>
+          <t>"Aqua, Diphenyl Dimethicone, Betaine, Dimethicone, Chlorella Vulgaris Extract, Niacinamide, Alpha-Arbutin, Glutathione, Ferulic Acid, Hydrolyzed Hyaluronic Acid, Tranexamic Acid, Geranium Robertianum Extract, Paeonia Suffruticosa Root Extract, Scutellaria Baicalensis Root Extract, Thymus Serpyllum Extract, Alpinia Katsumadai Seed Extract, Laurdimonium Hydroxypropyl Hydrolyzed Soy Protein, Tocopheryl Acetate, Lactic Acid, Glycerin, Butylene Glycol, PVP, Propanediol, Sodium Metabisulfite, Sodium Citrate, Citric Acid, Aminopropyl Ascorbyl Phosphate, Lecithin, Trideceth-9, PEG-40 Hydrogenated Castor Oil, Polysorbate 20, Hydroxyethylcellulose, PEG-35 Castor Oil, Phenoxyethanol, Sodium Chloride, Chlorphenesin, Disodium EDTA, Ci 26100"</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>55000</v>
+        <v>106000</v>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0g-mckh9j2eg6k789.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasm-m12lo06xn2203d.webp</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/7KuTZbTCAS</t>
+          <t>https://s.shopee.co.id/50WYnwcTmj</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8106,7 @@
       <c r="A215" s="3" t="inlineStr">
         <is>
           <t>Emina
-Glorad+ High-res Bright Glow Water-sphere Serum</t>
+Ms. Pimple Face Serum</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -8118,7 +8116,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Diphenyl Dimethicone, Betaine, Dimethicone, Chlorella Vulgaris Extract, Niacinamide, Alpha-Arbutin, Glutathione, Ferulic Acid, Hydrolyzed Hyaluronic Acid, Tranexamic Acid, Geranium Robertianum Extract, Paeonia Suffruticosa Root Extract, Scutellaria Baicalensis Root Extract, Thymus Serpyllum Extract, Alpinia Katsumadai Seed Extract, Laurdimonium Hydroxypropyl Hydrolyzed Soy Protein, Tocopheryl Acetate, Lactic Acid, Glycerin, Butylene Glycol, PVP, Propanediol, Sodium Metabisulfite, Sodium Citrate, Citric Acid, Aminopropyl Ascorbyl Phosphate, Lecithin, Trideceth-9, PEG-40 Hydrogenated Castor Oil, Polysorbate 20, Hydroxyethylcellulose, PEG-35 Castor Oil, Phenoxyethanol, Sodium Chloride, Chlorphenesin, Disodium EDTA, Ci 26100"</t>
+          <t>"Aqua, Glyserin, Niacinamide, Propanediol, Biosaccharide Gum-1, Zinc Pca, Phenoxyethanol, Salicylic Acid, Xanthan Gum, Chlorphenesin, Allantoin, Tetrasodium EDTA, Epilobium Angustifolium Extract, Sodium Metabisulfite"</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -8127,24 +8125,24 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>106000</v>
+        <v>62000</v>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasm-m12lo06xn2203d.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-xhd9rhfnjlov3e.webp</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/50WYnwcTmj</t>
+          <t>https://s.shopee.co.id/3LOKowVnSM</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>Emina
-Ms. Pimple Face Serum</t>
+          <t>Wardah
+Lightening Serum Ampoule</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -8154,7 +8152,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glyserin, Niacinamide, Propanediol, Biosaccharide Gum-1, Zinc Pca, Phenoxyethanol, Salicylic Acid, Xanthan Gum, Chlorphenesin, Allantoin, Tetrasodium EDTA, Epilobium Angustifolium Extract, Sodium Metabisulfite"</t>
+          <t>"Aqua, Butylene Glycol, Niacinamide, Cyclopentasiloxane, Glycerin, Biosaccharide Gum-1, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Phenoxyethanol, Bisabolol, Dimethicone, Chlorphenesin, Polyglyceryl-3 Methylglucose Distearate, Polysorbate 20, Disodium EDTA, Dimethicone/​Vinyl Dimethicone Crosspolymer, Fragrance, Sodium Hydroxide"</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -8163,16 +8161,16 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>62000</v>
+        <v>85000</v>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-xhd9rhfnjlov3e.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasl-m3bmg66buq3k87.webp</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3LOKowVnSM</t>
+          <t>https://s.shopee.co.id/20sxEWul05</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8178,7 @@
       <c r="A217" s="3" t="inlineStr">
         <is>
           <t>Wardah
-Lightening Serum Ampoule</t>
+Perfect Bright Perfectyl + Vitamin C Pore Perfecting C-glow Serum</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -8190,7 +8188,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Niacinamide, Cyclopentasiloxane, Glycerin, Biosaccharide Gum-1, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Phenoxyethanol, Bisabolol, Dimethicone, Chlorphenesin, Polyglyceryl-3 Methylglucose Distearate, Polysorbate 20, Disodium EDTA, Dimethicone/​Vinyl Dimethicone Crosspolymer, Fragrance, Sodium Hydroxide"</t>
+          <t>"Aqua, Niacinamide, Dipropylene Glycol, Propanediol, Phenoxyethanol, 3-O-Ethyl Ascorbic Acid, Xanthan Gum, Allantoin, Chlorphenesin, Disodium EDTA, Chamomilla Recutita Flower/​Leaf Extract, Fragrance, Ascorbyl Glucoside, Sodium Phytate, Potassium Sorbate, Sodium Benzoate"</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -8199,16 +8197,16 @@
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>85000</v>
+        <v>36000</v>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasl-m3bmg66buq3k87.webp</t>
+          <t>https://down-id.img.susercontent.com/file/sg-11134201-7rbk1-m5z2gctnwm0b6c@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/20sxEWul05</t>
+          <t>https://s.shopee.co.id/6VLMaqDK1Q</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8214,7 @@
       <c r="A218" s="3" t="inlineStr">
         <is>
           <t>Wardah
-Perfect Bright Perfectyl + Vitamin C Pore Perfecting C-glow Serum</t>
+Acnederm Acne Care Serum</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -8226,7 +8224,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Dipropylene Glycol, Propanediol, Phenoxyethanol, 3-O-Ethyl Ascorbic Acid, Xanthan Gum, Allantoin, Chlorphenesin, Disodium EDTA, Chamomilla Recutita Flower/​Leaf Extract, Fragrance, Ascorbyl Glucoside, Sodium Phytate, Potassium Sorbate, Sodium Benzoate"</t>
+          <t>"Aqua, Ethanol, Propanediol, Niacinamide, Methyl Gluceth-20, Potassium Azeloyl Diglycinate, Salicylic Acid, Xanthan Gum, 1,2-Hexanediol, Aminomethyl Propanol, Glyserin, Chlorphenesin, Allantoin, Polyacrylate Crosspolymer-6, Sclerotium Gum, Tetrasodium EDTA, Caprylyl Hydroxamic Acid, Melaleuca Alternifolia Leaf Oil, Sodium Hyaluronate, Potassium Chloride, Phenoxyethanol, Trideceth-9, PEG-40 Hydrogenated Castor Oil, Salix Alba Bark Extract, Caprylyl Glycol, Polysorbate 20, Potassium Sorbate, Sodium Benzoate"</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -8235,16 +8233,16 @@
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>36000</v>
+        <v>70000</v>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/sg-11134201-7rbk1-m5z2gctnwm0b6c@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98v-lm8lh1ysvc4k76@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/6VLMaqDK1Q</t>
+          <t>https://s.shopee.co.id/BRJ3P4gPi</t>
         </is>
       </c>
     </row>
@@ -8252,7 +8250,7 @@
       <c r="A219" s="3" t="inlineStr">
         <is>
           <t>Wardah
-Acnederm Acne Care Serum</t>
+Crystal Secret Dark Spot Brightening Serum</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -8262,7 +8260,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Ethanol, Propanediol, Niacinamide, Methyl Gluceth-20, Potassium Azeloyl Diglycinate, Salicylic Acid, Xanthan Gum, 1,2-Hexanediol, Aminomethyl Propanol, Glyserin, Chlorphenesin, Allantoin, Polyacrylate Crosspolymer-6, Sclerotium Gum, Tetrasodium EDTA, Caprylyl Hydroxamic Acid, Melaleuca Alternifolia Leaf Oil, Sodium Hyaluronate, Potassium Chloride, Phenoxyethanol, Trideceth-9, PEG-40 Hydrogenated Castor Oil, Salix Alba Bark Extract, Caprylyl Glycol, Polysorbate 20, Potassium Sorbate, Sodium Benzoate"</t>
+          <t>"Aqua, Glyserin, Niacinamide, Cyclopentasiloxane, Dimethicone, Tranexamoyl Dipeptide-23, Pentylene Glycol, Trehalose, Aluminium Starch Octenylsuccinate, Butylene Glycol, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Polymethyl Methacrylate, Bisabolol, Alpha-Arbutin, Leontopodium Alpinum Extract, Cetearyl Dimethicone Crosspolymer, Glyceryl Polyacrylate, Disodium EDTA, Sodium Hydroxide, Fragrance, Citric Acid, Potassium Sorbate, Sodium Benzoate, Phenoxyethanol, Chlorphenesin"</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -8271,16 +8269,16 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>70000</v>
+        <v>100000</v>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98v-lm8lh1ysvc4k76@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/sg-11134201-7rdws-m0u0is0hjr8wf2.webp</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/BRJ3P4gPi</t>
+          <t>https://s.shopee.co.id/20sxEpDGWy</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8286,7 @@
       <c r="A220" s="3" t="inlineStr">
         <is>
           <t>Wardah
-Crystal Secret Dark Spot Brightening Serum</t>
+Renew You Cell Renewal Serum</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -8298,7 +8296,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glyserin, Niacinamide, Cyclopentasiloxane, Dimethicone, Tranexamoyl Dipeptide-23, Pentylene Glycol, Trehalose, Aluminium Starch Octenylsuccinate, Butylene Glycol, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Polymethyl Methacrylate, Bisabolol, Alpha-Arbutin, Leontopodium Alpinum Extract, Cetearyl Dimethicone Crosspolymer, Glyceryl Polyacrylate, Disodium EDTA, Sodium Hydroxide, Fragrance, Citric Acid, Potassium Sorbate, Sodium Benzoate, Phenoxyethanol, Chlorphenesin"</t>
+          <t>"Aqua, Glycerin, Niacinamide, Propanediol, Dibutyl Adipate, Dimethicone, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Vinyl Dimethicone/​Methicone Silsesquioxane Crosspolymer, Phenoxyethanol, Allantoin, Caprylic/​Capric Triglyceride, Butylene Glycol, Chlorphenesin, Glycine Soja Oil, Deoxyphytantriyl Palmitamide Mea, Disodium EDTA, Hydrogenated Lecithin, Ceramide NP, Cholesterol, Fragrance, Pentylene Glycol, Retinol, Biosaccharide Gum-2, Bakuchiol, Sodium Hyaluronate, Carbomer, Acacia Senegal Gum, Tocopherol, Polysorbate 20, Propylene Glycol Alginate, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7"</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -8311,12 +8309,12 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/sg-11134201-7rdws-m0u0is0hjr8wf2.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasm-m1c20m9xtnwz12@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/20sxEpDGWy</t>
+          <t>https://s.shopee.co.id/8V6QyoG2I0</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8322,7 @@
       <c r="A221" s="3" t="inlineStr">
         <is>
           <t>Wardah
-Renew You Cell Renewal Serum</t>
+Hydra Rose Micro Gel Serum</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -8334,33 +8332,33 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Niacinamide, Propanediol, Dibutyl Adipate, Dimethicone, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Vinyl Dimethicone/​Methicone Silsesquioxane Crosspolymer, Phenoxyethanol, Allantoin, Caprylic/​Capric Triglyceride, Butylene Glycol, Chlorphenesin, Glycine Soja Oil, Deoxyphytantriyl Palmitamide Mea, Disodium EDTA, Hydrogenated Lecithin, Ceramide NP, Cholesterol, Fragrance, Pentylene Glycol, Retinol, Biosaccharide Gum-2, Bakuchiol, Sodium Hyaluronate, Carbomer, Acacia Senegal Gum, Tocopherol, Polysorbate 20, Propylene Glycol Alginate, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7"</t>
+          <t>"Aqua, Propanediol, Butylene Glycol, Glycerin, Trehalose, Saccharide Isomerate, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Phenoxyethanol, Chlorphenesin, PEG-32, 1.2-Hexanediol, Allantoin, Disodium EDTA, Trideceth-9, Diazolidinyl Urea, PEG-40 Hydrogenated Castor Oil, Sodium Hyaluronate, Synthetic Fluorphlogopite, Agar, Cetearyl Olivate, Sorbitan Olivate, Citric Acid, Sodium Citrate, Brassica Campestris (Rapeseed) Seed Oil, Polysorbate 20, Fragrance, Rose Extract, Ethylhexylglycerin, Tocopherol"</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>100000</v>
+        <v>118000</v>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasm-m1c20m9xtnwz12@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/sg-11134201-7rdwf-m1cfemmkrc7pa0@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8V6QyoG2I0</t>
+          <t>https://s.shopee.co.id/8ATaaFIZGz</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>Wardah
-Hydra Rose Micro Gel Serum</t>
+          <t>Viva Cosmetics
+Viva Glowing White Serum</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -8370,25 +8368,25 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Propanediol, Butylene Glycol, Glycerin, Trehalose, Saccharide Isomerate, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Phenoxyethanol, Chlorphenesin, PEG-32, 1.2-Hexanediol, Allantoin, Disodium EDTA, Trideceth-9, Diazolidinyl Urea, PEG-40 Hydrogenated Castor Oil, Sodium Hyaluronate, Synthetic Fluorphlogopite, Agar, Cetearyl Olivate, Sorbitan Olivate, Citric Acid, Sodium Citrate, Brassica Campestris (Rapeseed) Seed Oil, Polysorbate 20, Fragrance, Rose Extract, Ethylhexylglycerin, Tocopherol"</t>
+          <t>"Aqua, Niacinamide, Propylene Glycol, Glycyrrhiza Glabra Root Extract, Butylene Glycol, Propanediol, Phenoxyethanol, Cellulose Gum, Glycerin, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Triethylene Glycol, Ethylhexylglycerin, Sodium Hydroxide, Glutathione, Potassium Sorbate, Sodium Benzoate"</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>118000</v>
+        <v>26000</v>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/sg-11134201-7rdwf-m1cfemmkrc7pa0@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7qula-lgbo0ec46x0ofd@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8ATaaFIZGz</t>
+          <t>https://s.shopee.co.id/3qKbQLuPTD</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8394,7 @@
       <c r="A223" s="3" t="inlineStr">
         <is>
           <t>Viva Cosmetics
-Viva Glowing White Serum</t>
+Viva Anti Aging Serum</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -8406,7 +8404,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Propylene Glycol, Glycyrrhiza Glabra Root Extract, Butylene Glycol, Propanediol, Phenoxyethanol, Cellulose Gum, Glycerin, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Triethylene Glycol, Ethylhexylglycerin, Sodium Hydroxide, Glutathione, Potassium Sorbate, Sodium Benzoate"</t>
+          <t>"Aqua, Butylene Glycol, Sodium Hyaluronate, Hydrolyzed Collagen, PEG-40 Hydrogenated Castor Oil, Propanediol, Phenoxyethanol, Cellulose Gum, Disodium EDTA, Bakuchiol, Triethylene Glycol, Ethylhexylglycerin, Ci 19140, Ci 15985"</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -8415,16 +8413,16 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>26000</v>
+        <v>32000</v>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7qula-lgbo0ec46x0ofd@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7qula-lgbo0ecy4akzf7.webp</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3qKbQLuPTD</t>
+          <t>https://s.shopee.co.id/3LOKpU7PHt</t>
         </is>
       </c>
     </row>
@@ -8432,17 +8430,17 @@
       <c r="A224" s="3" t="inlineStr">
         <is>
           <t>Viva Cosmetics
-Viva Anti Aging Serum</t>
+Viva Peeling Serum</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Eksfoliasi</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Sodium Hyaluronate, Hydrolyzed Collagen, PEG-40 Hydrogenated Castor Oil, Propanediol, Phenoxyethanol, Cellulose Gum, Disodium EDTA, Bakuchiol, Triethylene Glycol, Ethylhexylglycerin, Ci 19140, Ci 15985"</t>
+          <t>"Aqua, Gluconolactone, Butylene Glycol, Glycolic Acid, Pentylene Glycol, PEG-40 Hydrogenated Castor Oil, Betaine, Sodium Citrate, Polyacrylate Crosspolymer-6, Salicylic Acid, Sodium Hydroxide, Phenoxyethanol, Allantoin, Hydrolyzed Jojoba Esters, Xanthan Gum, Aloe Barbadensis Leaf Juice, Triethylene Glycol, Ci 14720, Ci 42090, Ci 19140"</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -8451,16 +8449,16 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>32000</v>
+        <v>27000</v>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7qula-lgbo0ecy4akzf7.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7quky-lgbo0ec4dxuw87@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3LOKpU7PHt</t>
+          <t>https://s.shopee.co.id/1qZX2nPFbS</t>
         </is>
       </c>
     </row>
@@ -8468,17 +8466,17 @@
       <c r="A225" s="3" t="inlineStr">
         <is>
           <t>Viva Cosmetics
-Viva Peeling Serum</t>
+Acne Serum</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Gluconolactone, Butylene Glycol, Glycolic Acid, Pentylene Glycol, PEG-40 Hydrogenated Castor Oil, Betaine, Sodium Citrate, Polyacrylate Crosspolymer-6, Salicylic Acid, Sodium Hydroxide, Phenoxyethanol, Allantoin, Hydrolyzed Jojoba Esters, Xanthan Gum, Aloe Barbadensis Leaf Juice, Triethylene Glycol, Ci 14720, Ci 42090, Ci 19140"</t>
+          <t>"Aqua, Niacinamide, Betaine, Sodium Citrate, Propylene Glycol, Propanediol, Centella Asiatica Leaf Extract, Butylene Glycol, Salicylic Acid, Phenoxyethanol, Polyacrylate Crosspolymer-6, Glycerin, Xanthan Gum, Ethylhexylglycerin, Triethylene Glycol, Citric Acid, Potassium Sorbate, Sodium Benzoate"</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -8487,16 +8485,16 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>27000</v>
+        <v>24000</v>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7quky-lgbo0ec4dxuw87@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98u-loaud6ifyakc9a.webp</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/1qZX2nPFbS</t>
+          <t>https://s.shopee.co.id/3B4udIWENk</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8502,7 @@
       <c r="A226" s="3" t="inlineStr">
         <is>
           <t>Viva Cosmetics
-Acne Serum</t>
+Vit C Collagen Serum</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -8514,7 +8512,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Betaine, Sodium Citrate, Propylene Glycol, Propanediol, Centella Asiatica Leaf Extract, Butylene Glycol, Salicylic Acid, Phenoxyethanol, Polyacrylate Crosspolymer-6, Glycerin, Xanthan Gum, Ethylhexylglycerin, Triethylene Glycol, Citric Acid, Potassium Sorbate, Sodium Benzoate"</t>
+          <t>"Aqua, Niacinamide, Sodium Ascorbyl Phosphate, Butylene Glycol, Propanediol, Phenoxyethanol, Polyacrylate Crosspolymer-6, Hydrolyzed Collagen, Cellulose Gum, Disodium EDTA, Ethylhexylglycerin, Triethylene Glycol, Sodium Hyaluronate, Kappaphycus Alvarezii Extract"</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -8523,24 +8521,24 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>24000</v>
+        <v>28000</v>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98u-loaud6ifyakc9a.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasj-m0mfcc4855b40c.webp</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3B4udIWENk</t>
+          <t>https://s.shopee.co.id/7fXK28ynQI</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>Viva Cosmetics
-Vit C Collagen Serum</t>
+          <t xml:space="preserve">Viva Cosmetics
+Gold Whitening Serum </t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -8550,7 +8548,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Sodium Ascorbyl Phosphate, Butylene Glycol, Propanediol, Phenoxyethanol, Polyacrylate Crosspolymer-6, Hydrolyzed Collagen, Cellulose Gum, Disodium EDTA, Ethylhexylglycerin, Triethylene Glycol, Sodium Hyaluronate, Kappaphycus Alvarezii Extract"</t>
+          <t>"Aqua, Niacinamide, Sodium Ascorbyl Phosphate, Propanediol, Butylene Glycol, Polyacrylate Crosspolymer-6, Phenoxyethanol, Citric Acid, Cellulose Gum, Hydrolyzed Collagen, Palm (Elaeis Guineensis) Oil, Gossypium Herbaceum Seed Oil, Ci. 77019, Bidens Pilosa Extract, Disodium EDTA, Ethylhexylglycerin, Triethylene Glycol, Linum Usitatissimum Seed Oil, Ci 77891, Ci 77491, Caprylyl Glycol, Tocopherol, Colloidal Gold"</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -8559,24 +8557,24 @@
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>28000</v>
+        <v>27000</v>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasj-m0mfcc4855b40c.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rase-m0mfcc482cfyd9.webp</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/7fXK28ynQI</t>
+          <t>https://s.shopee.co.id/1gG6tAbPEd</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viva Cosmetics
-Gold Whitening Serum </t>
+          <t>Viva Cosmetics
+Viva Queen Whitening Advanced Face Serum</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -8586,7 +8584,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Sodium Ascorbyl Phosphate, Propanediol, Butylene Glycol, Polyacrylate Crosspolymer-6, Phenoxyethanol, Citric Acid, Cellulose Gum, Hydrolyzed Collagen, Palm (Elaeis Guineensis) Oil, Gossypium Herbaceum Seed Oil, Ci. 77019, Bidens Pilosa Extract, Disodium EDTA, Ethylhexylglycerin, Triethylene Glycol, Linum Usitatissimum Seed Oil, Ci 77891, Ci 77491, Caprylyl Glycol, Tocopherol, Colloidal Gold"</t>
+          <t>"Aqua, Propylene Glycol, PEG-12 Dimethicone, Betaine, Niacinamide, Ethyl Ascorbic Acid, Carbomer, Triethanolamine, Sodium Polyacrylate, Sodium Citrate, Allantoin, Methylparaben, Caprylic/​Capric Triglyceride, Mineral Oil, Citric Acid, Chamomile Recutita Flower Water, Tri-PPG- 3 Myristyl Ether Citrate, Disodium EDTA, Sorbitan Laurate, Trideceth-6, Bisabolol, Lactic Acid, Polysorbate 80, Potassium Sorbate, Sodium Benzoate"</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -8595,16 +8593,16 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>27000</v>
+        <v>72000</v>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rase-m0mfcc482cfyd9.webp</t>
+          <t>https://down-id.img.susercontent.com/file/7bb8be9c2e96aa52bd8b6d72d8676c9a@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/1gG6tAbPEd</t>
+          <t>https://s.shopee.co.id/4qD8fCFlhr</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8610,7 @@
       <c r="A229" s="3" t="inlineStr">
         <is>
           <t>Viva Cosmetics
-Viva Queen Whitening Advanced Face Serum</t>
+Viva Queen Pro-age Advanced Face Serum</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -8622,7 +8620,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Propylene Glycol, PEG-12 Dimethicone, Betaine, Niacinamide, Ethyl Ascorbic Acid, Carbomer, Triethanolamine, Sodium Polyacrylate, Sodium Citrate, Allantoin, Methylparaben, Caprylic/​Capric Triglyceride, Mineral Oil, Citric Acid, Chamomile Recutita Flower Water, Tri-PPG- 3 Myristyl Ether Citrate, Disodium EDTA, Sorbitan Laurate, Trideceth-6, Bisabolol, Lactic Acid, Polysorbate 80, Potassium Sorbate, Sodium Benzoate"</t>
+          <t>"Aqua, Butylene Glycol, Pentylene Glycol, Propanediol, Erythritol, Sodium Acrylates Copolymer, Triethanolamine, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Lecithin, Hdi/​Trimethylol Hexyllactone Crosspolymer, Glycerin, Ethylhexylglycerin, Sodium Lauroyl Lactylate, Snail Secretion Filtrate, Disodium EDTA, Sodium Hyaluronate, Lactic Acid, Serine, Sodium Lactate, Sorbitol, Urea, Hydrolyzed Collagen, Hydrolyzed Hyaluronic Acid, Ceramide NP, Ethyl Hexanediol, Sodium Chloride, Ceramide AP, Phytosphingosine, Cholesterol, Xanthan Gum, Phenoxyethanol, Silica, Carbomer, Allantoin, Ceramide EOP"</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -8631,24 +8629,24 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>72000</v>
+        <v>66000</v>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/7bb8be9c2e96aa52bd8b6d72d8676c9a@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r991-lxwdi661nessdf.webp</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4qD8fCFlhr</t>
+          <t>https://s.shopee.co.id/9zvEomXx5e</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>Viva Cosmetics
-Viva Queen Pro-age Advanced Face Serum</t>
+          <t>Mentholatum Acnes
+Acnes Derma Barrier Booster Essence</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -8658,7 +8656,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Pentylene Glycol, Propanediol, Erythritol, Sodium Acrylates Copolymer, Triethanolamine, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Lecithin, Hdi/​Trimethylol Hexyllactone Crosspolymer, Glycerin, Ethylhexylglycerin, Sodium Lauroyl Lactylate, Snail Secretion Filtrate, Disodium EDTA, Sodium Hyaluronate, Lactic Acid, Serine, Sodium Lactate, Sorbitol, Urea, Hydrolyzed Collagen, Hydrolyzed Hyaluronic Acid, Ceramide NP, Ethyl Hexanediol, Sodium Chloride, Ceramide AP, Phytosphingosine, Cholesterol, Xanthan Gum, Phenoxyethanol, Silica, Carbomer, Allantoin, Ceramide EOP"</t>
+          <t>"Aqua (Water), Propanediol, Glycerin, Niacinamide, Squalane, Isononyl Isononanoate, Betaine, PVP, PEG-60 Hydrogenated Castor Oil, Saccharide Isomerate, PEG-20 Sorbitan Isostearate, Glyceryl Stearate, PPG-10 Methyl Glucose Ether, Phenoxyethanol, Stearyl Alcohol, PEG-8, Cetyl Alcohol, Acrylates, Hexylglycerin, Butylene Glycol, Disodium EDTA, Ceramide NG, Hydrolyzed Royal Jelly Protein, Citric Acid, Sodium Citrate, Rosa Canina Fruit Extract, Sodium Acetylated Hyaluronate, Tocopherol"</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -8667,24 +8665,24 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>66000</v>
+        <v>94000</v>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r991-lxwdi661nessdf.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasm-m3a13iffv2vs8e.webp</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9zvEomXx5e</t>
+          <t>https://s.shopee.co.id/30lUU2jPJO</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>Mentholatum Acnes
-Acnes Derma Barrier Booster Essence</t>
+          <t>Scora
+3% Arbutin Serum</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -8694,7 +8692,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>"Aqua (Water), Propanediol, Glycerin, Niacinamide, Squalane, Isononyl Isononanoate, Betaine, PVP, PEG-60 Hydrogenated Castor Oil, Saccharide Isomerate, PEG-20 Sorbitan Isostearate, Glyceryl Stearate, PPG-10 Methyl Glucose Ether, Phenoxyethanol, Stearyl Alcohol, PEG-8, Cetyl Alcohol, Acrylates, Hexylglycerin, Butylene Glycol, Disodium EDTA, Ceramide NG, Hydrolyzed Royal Jelly Protein, Citric Acid, Sodium Citrate, Rosa Canina Fruit Extract, Sodium Acetylated Hyaluronate, Tocopherol"</t>
+          <t>"Aqua, Niacinamide, Alpha-Arbutin, Butylene Glycol, Glycerin, Allantoin, DMDM Hydantoin, Xanthan Gum, Disodium EDTA, PEG-12 Dimethicone, PEG-12 Allyl Ether, Cystoseira TamariscIfolia Extract, Phenoxyethanol, PEG-12"</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -8703,24 +8701,24 @@
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>94000</v>
+        <v>58000</v>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasm-m3a13iffv2vs8e.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0h-mbrkirscfyzi21.webp</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/30lUU2jPJO</t>
+          <t>https://s.shopee.co.id/3LOKshst7w</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>Scora
-3% Arbutin Serum</t>
+          <t>Pond's
+Bright Miracle Ultimate Clarity Serum</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -8730,7 +8728,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Alpha-Arbutin, Butylene Glycol, Glycerin, Allantoin, DMDM Hydantoin, Xanthan Gum, Disodium EDTA, PEG-12 Dimethicone, PEG-12 Allyl Ether, Cystoseira TamariscIfolia Extract, Phenoxyethanol, PEG-12"</t>
+          <t>"Water, Glycerin, Dimethicone, Pentylene Glycol, Niacinamide, Butylene Glycol, Caprylic/​Capric Triglyceride, Polysorbate 20, Phenoxyethanol, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Xanthan Gum, Ammonium Acryloyldimethyltaurate/​Beheneth-25 Methacrylate Crosspolymer, Allantoin, Cystine, Glycine, Methylparaben, Tocopheryl Acetate, Disodium EDTA, Fragrance, Propylparaben, Sodium PCA, Stearic Acid, Citric Acid, Sodium Hydroxide, BHT, T-Butyl Alcohol, Cetyl Alcohol, Bifida Ferment Lysate, Sodium Carbonate, Sodium Acetylated Hyaluronate, 3-O-Ethyl Ascorbic Acid, Sodium Hyaluronate, Sodium Hyaluronate Crosspolymer, Hydrolyzed Sodium Hyaluronate, Ethylhexylglycerin, 4-Ethylresorcinol, Ceramide NP, Ceramide AP, Phytosphingosine, Cholesterol, Ceramide EOP, Ci 19140"</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -8739,16 +8737,16 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>58000</v>
+        <v>92000</v>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0h-mbrkirscfyzi21.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98y-lom0gwgr5b6pb1.webp</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3LOKshst7w</t>
+          <t>https://s.shopee.co.id/1qZX60NeCm</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8754,7 @@
       <c r="A233" s="3" t="inlineStr">
         <is>
           <t>Pond's
-Bright Miracle Ultimate Clarity Serum</t>
+Age Miracle Ultimate Youth Day Serum</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -8766,7 +8764,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycerin, Dimethicone, Pentylene Glycol, Niacinamide, Butylene Glycol, Caprylic/​Capric Triglyceride, Polysorbate 20, Phenoxyethanol, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Xanthan Gum, Ammonium Acryloyldimethyltaurate/​Beheneth-25 Methacrylate Crosspolymer, Allantoin, Cystine, Glycine, Methylparaben, Tocopheryl Acetate, Disodium EDTA, Fragrance, Propylparaben, Sodium PCA, Stearic Acid, Citric Acid, Sodium Hydroxide, BHT, T-Butyl Alcohol, Cetyl Alcohol, Bifida Ferment Lysate, Sodium Carbonate, Sodium Acetylated Hyaluronate, 3-O-Ethyl Ascorbic Acid, Sodium Hyaluronate, Sodium Hyaluronate Crosspolymer, Hydrolyzed Sodium Hyaluronate, Ethylhexylglycerin, 4-Ethylresorcinol, Ceramide NP, Ceramide AP, Phytosphingosine, Cholesterol, Ceramide EOP, Ci 19140"</t>
+          <t>"Water, Isodecyl Neopentanoate, Butylene Glycol, Glycerin, Niacinamide, Sodium Starch Octenylsuccinate, Hexylresorcinol, Retinyl Propionate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate, Cetyl Alcohol, Hydroxypropyl Starch Phosphate, 1,2-Hexanediol, Ethylhexylglycerin, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Dilauryl Thiodipropionate, Pentaerythrityl Tetra-Di-T-Butyl Hydroxyhydrocinnamate, Bisabolol, Decyl Glucoside, Potassium Hydroxide, Zingiber Officinale (Ginger) Root Extract, Tocopherol, Bifida Ferment Lysate, Betaine, Lecithin, Retinol, Acetyl Dipeptide-1 Cetyl Ester, Sodium Hyaluronate Crosspolymer, Hydrolyzed Sodium Hyaluronate, Ascorbyl Palmitate, Fragrance, Disodium EDTA, BHT, Phenoxyethanol, Ci 14700, Ci 19140"</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -8775,16 +8773,16 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>92000</v>
+        <v>69000</v>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98y-lom0gwgr5b6pb1.webp</t>
+          <t>https://down-id.img.susercontent.com/file/sg-11134301-7rd5k-lvskfsk7ziok70@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/1qZX60NeCm</t>
+          <t>https://s.shopee.co.id/9pbocmVefs</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8790,7 @@
       <c r="A234" s="3" t="inlineStr">
         <is>
           <t>Pond's
-Age Miracle Ultimate Youth Day Serum</t>
+Age Miracle Ultimate Youth Night Serum</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -8802,7 +8800,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>"Water, Isodecyl Neopentanoate, Butylene Glycol, Glycerin, Niacinamide, Sodium Starch Octenylsuccinate, Hexylresorcinol, Retinyl Propionate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate, Cetyl Alcohol, Hydroxypropyl Starch Phosphate, 1,2-Hexanediol, Ethylhexylglycerin, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Dilauryl Thiodipropionate, Pentaerythrityl Tetra-Di-T-Butyl Hydroxyhydrocinnamate, Bisabolol, Decyl Glucoside, Potassium Hydroxide, Zingiber Officinale (Ginger) Root Extract, Tocopherol, Bifida Ferment Lysate, Betaine, Lecithin, Retinol, Acetyl Dipeptide-1 Cetyl Ester, Sodium Hyaluronate Crosspolymer, Hydrolyzed Sodium Hyaluronate, Ascorbyl Palmitate, Fragrance, Disodium EDTA, BHT, Phenoxyethanol, Ci 14700, Ci 19140"</t>
+          <t>"Water, Isodecyl Neopentanoate, Butylene Glycol, Glycerin, Niacinamide, Sodium Starch Octenylsuccinate, Hexylresorcinol, Tocopherol, Squalane, Retinyl Propionate, Hydroxypropyl Starch Phosphate, 1,2-Hexanediol, Ethylhexylglycerin, Cetyl Alcohol, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Dilauryl Thiodipropionate, Pentaerythrityl Tetra-Di-T-Butyl Hydroxyhydrocinnamate, Bisabolol, Decyl Glucoside, Disodium EDTA, Potassium Hydroxide, Zingiber Officinale (Ginger) Root Extract, Bifida Ferment Lysate, Betaine, Lecithin, Retinol, Sodium Acetylated Hyaluronate, Sodium Hyaluronate, Acetyl Dipeptide-1 Cetyl Ester, Sodium Hyaluronate Crosspolymer, Hydrolyzed Sodium Hyaluronate, Ascorbyl Palmitate, Fragrance, BHT, Phenoxyethanol, Ci 14700, Ci 19140"</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -8811,24 +8809,24 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>69000</v>
+        <v>81000</v>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/sg-11134301-7rd5k-lvskfsk7ziok70@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/sg-11134301-7rd6b-lvskfp1f3oiq42@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9pbocmVefs</t>
+          <t>https://s.shopee.co.id/2BCNUku8Fa</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>Pond's
-Age Miracle Ultimate Youth Night Serum</t>
+          <t>True to Skin
+Niacinamide Txa Brightening Serum</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -8838,7 +8836,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>"Water, Isodecyl Neopentanoate, Butylene Glycol, Glycerin, Niacinamide, Sodium Starch Octenylsuccinate, Hexylresorcinol, Tocopherol, Squalane, Retinyl Propionate, Hydroxypropyl Starch Phosphate, 1,2-Hexanediol, Ethylhexylglycerin, Cetyl Alcohol, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Dilauryl Thiodipropionate, Pentaerythrityl Tetra-Di-T-Butyl Hydroxyhydrocinnamate, Bisabolol, Decyl Glucoside, Disodium EDTA, Potassium Hydroxide, Zingiber Officinale (Ginger) Root Extract, Bifida Ferment Lysate, Betaine, Lecithin, Retinol, Sodium Acetylated Hyaluronate, Sodium Hyaluronate, Acetyl Dipeptide-1 Cetyl Ester, Sodium Hyaluronate Crosspolymer, Hydrolyzed Sodium Hyaluronate, Ascorbyl Palmitate, Fragrance, BHT, Phenoxyethanol, Ci 14700, Ci 19140"</t>
+          <t>"Water, Rosa Damascena Flower Water, Niacinamide, Glycerin, Methylpropanediol, Tranexamic Acid, Pentylene Glycol, 1,2-Hexanediol, Hydroxyacetophenone, Xanthan Gum, Disodium EDTA, Ethylhexylglycerin, Butylene Glycol, Octanediol, Cyanocobalamin"</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -8847,24 +8845,24 @@
         </is>
       </c>
       <c r="E235" s="3" t="n">
-        <v>81000</v>
+        <v>64000</v>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/sg-11134301-7rd6b-lvskfp1f3oiq42@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0r-md41kfx468qde6.webp</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/2BCNUku8Fa</t>
+          <t>https://s.shopee.co.id/80AARbXEoI</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>True to Skin
-Niacinamide Txa Brightening Serum</t>
+          <t>Mireya
+Retinol Biostine Booster</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -8874,25 +8872,25 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>"Water, Rosa Damascena Flower Water, Niacinamide, Glycerin, Methylpropanediol, Tranexamic Acid, Pentylene Glycol, 1,2-Hexanediol, Hydroxyacetophenone, Xanthan Gum, Disodium EDTA, Ethylhexylglycerin, Butylene Glycol, Octanediol, Cyanocobalamin"</t>
+          <t>"Aqua, Caprylic/​Capric Triglyceride, Glycerin, Euglena Gracilis Polysaccharide, Glyceryl Stearate, Niacinamide, Ceteareth-24, Cetearyl Alcohol, Polysorbate 80, Hydrolyzed Collagen, Tocopheryl Acetate, Retinol, Allantoin, Citric Acid, Acetyl Hexapeptide-8, Phenoxyethanol, Xanthan Gum, EDTA, Caprylyl Glycol"</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>64000</v>
+        <v>41000</v>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0r-md41kfx468qde6.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0g-mdd0xy2qgv5ka0.webp</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/80AARbXEoI</t>
+          <t>https://s.shopee.co.id/3g1BHfVKLN</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8898,7 @@
       <c r="A237" s="3" t="inlineStr">
         <is>
           <t>Mireya
-Retinol Biostine Booster</t>
+Unicorn Serum</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -8910,25 +8908,25 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Caprylic/​Capric Triglyceride, Glycerin, Euglena Gracilis Polysaccharide, Glyceryl Stearate, Niacinamide, Ceteareth-24, Cetearyl Alcohol, Polysorbate 80, Hydrolyzed Collagen, Tocopheryl Acetate, Retinol, Allantoin, Citric Acid, Acetyl Hexapeptide-8, Phenoxyethanol, Xanthan Gum, EDTA, Caprylyl Glycol"</t>
+          <t>"Aqua Demineralisata, Niacinamide, Methylpropanediol, Ethyl Ascorbic Acid, Euglena Gracilis Polysaccharide, Hydrolyzed Collagen, Phenoxyethanol, Xanthan Gum, Ci. 77019, Tin Oxide, Ci 77891, Salicylic Acid, Aloe Barbadensis Leaf Powder, PEG-40 Hydrogenated Castor Oil, EDTA, Titanium Dioxide, Parfum"</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>41000</v>
+        <v>20000</v>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0g-mdd0xy2qgv5ka0.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0i-mcq0732pwg1b21.webp</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3g1BHfVKLN</t>
+          <t>https://s.shopee.co.id/qgzuUszAq</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8934,7 @@
       <c r="A238" s="3" t="inlineStr">
         <is>
           <t>Mireya
-Unicorn Serum</t>
+Mochi Gold Serum</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -8946,7 +8944,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>"Aqua Demineralisata, Niacinamide, Methylpropanediol, Ethyl Ascorbic Acid, Euglena Gracilis Polysaccharide, Hydrolyzed Collagen, Phenoxyethanol, Xanthan Gum, Ci. 77019, Tin Oxide, Ci 77891, Salicylic Acid, Aloe Barbadensis Leaf Powder, PEG-40 Hydrogenated Castor Oil, EDTA, Titanium Dioxide, Parfum"</t>
+          <t>"Aqua, Niacinamide, Methylpropanediol, Ethyl Ascorbic Acid, Euglena Gracilis Polysaccharide, Hydrolyzed Collagen, Phenoxyethanol, Xanthan Gum, Ci. 77019, Ci 77015, Ci 74160, Salicylic Acid, Aloe Barbadensis Leaf Powder, PEG-40 Hydrogenated Castor Oil, Mica, EDTA, Titanium Dioxide, Hydrolyzed Collagen, Perfume"</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -8955,24 +8953,24 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0i-mcq0732pwg1b21.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0j-md4a0mw8tnc334@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/qgzuUszAq</t>
+          <t>https://s.shopee.co.id/902hdXifr3</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>Mireya
-Mochi Gold Serum</t>
+          <t xml:space="preserve">Mireya
+Bright Boost Serum </t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -8982,33 +8980,33 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Methylpropanediol, Ethyl Ascorbic Acid, Euglena Gracilis Polysaccharide, Hydrolyzed Collagen, Phenoxyethanol, Xanthan Gum, Ci. 77019, Ci 77015, Ci 74160, Salicylic Acid, Aloe Barbadensis Leaf Powder, PEG-40 Hydrogenated Castor Oil, Mica, EDTA, Titanium Dioxide, Hydrolyzed Collagen, Perfume"</t>
+          <t>"Aqua/​Water, Niacinamide, Nicotinamide, Propylene Glycol, Glycerin, Panthenol, Dexpanthenol, Anthemis Nobilis Flower Extract, DMDM Hydantoin, Butylene Glycol, Ethyl Ascorbic Acid, Allantoin, Sodium Hyaluronate, EDTA, Prunus Serrulata Flower Extract, Dictyopteris Polypodioides Extract, Phenoxyethanol, Formaldehyde"</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>26000</v>
+        <v>31000</v>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0j-md4a0mw8tnc334@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0k-mcpxee7uwpif6d.webp</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/902hdXifr3</t>
+          <t>https://s.shopee.co.id/AKY5E1caGp</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mireya
-Bright Boost Serum </t>
+          <t>Mireya
+Glow-c Serum</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -9018,72 +9016,72 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>"Aqua/​Water, Niacinamide, Nicotinamide, Propylene Glycol, Glycerin, Panthenol, Dexpanthenol, Anthemis Nobilis Flower Extract, DMDM Hydantoin, Butylene Glycol, Ethyl Ascorbic Acid, Allantoin, Sodium Hyaluronate, EDTA, Prunus Serrulata Flower Extract, Dictyopteris Polypodioides Extract, Phenoxyethanol, Formaldehyde"</t>
+          <t>"Aqua Demineralisata, Glycerin, Ceteareth-20, PEG-40 Hydrogenated Castor Oil, Propylene Glycol, Ethyl Ascorbic Acid, Niacinamide, Phenoxyethanol, Anthemis Nobilis Flower Extract, Allantoin, Tocopheryl Acetate, Xanthan Gum, Citric Acid, Acetyl Hexapeptide-38, Caprylyl Glycol"</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0k-mcpxee7uwpif6d.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0h-mcpwgru9lq9o1c.webp</t>
         </is>
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/AKY5E1caGp</t>
+          <t>https://s.shopee.co.id/qgzubHAOA</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
-        <is>
-          <t>Mireya
-Glow-c Serum</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>Serum</t>
-        </is>
-      </c>
-      <c r="C241" s="3" t="inlineStr">
-        <is>
-          <t>"Aqua Demineralisata, Glycerin, Ceteareth-20, PEG-40 Hydrogenated Castor Oil, Propylene Glycol, Ethyl Ascorbic Acid, Niacinamide, Phenoxyethanol, Anthemis Nobilis Flower Extract, Allantoin, Tocopheryl Acetate, Xanthan Gum, Citric Acid, Acetyl Hexapeptide-38, Caprylyl Glycol"</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>Cair</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F241" s="4" t="inlineStr">
-        <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0h-mcpwgru9lq9o1c.webp</t>
-        </is>
-      </c>
-      <c r="G241" s="4" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.id/qgzubHAOA</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">
 TheActives.
 Ethyl Ascorbic Acid 20% Serum</t>
         </is>
       </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>"Aqua, 3-O-Ethyl Ascorbic Acid, Propanediol, Glycerin, Ethoxydiglycol, Panthenol, Allantoin, Polyacrylate Crosspolymer-6, Phenoxyethanol, Chlorphenesin"</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Cair</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztg-mf3q85w4ynm21a@resize_w900_nl.webp</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.id/5Apz4xTxCh</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>TheActives.
+Salicylic Acid 2% + Zinc 0,5% Serum</t>
+        </is>
+      </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
           <t>Serum</t>
@@ -9091,7 +9089,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, 3-O-Ethyl Ascorbic Acid, Propanediol, Glycerin, Ethoxydiglycol, Panthenol, Allantoin, Polyacrylate Crosspolymer-6, Phenoxyethanol, Chlorphenesin"</t>
+          <t>"Aqua, Propanediol, Salicylic Acid, Trisodium Citrate, Panthenol, Glycerin, Zinc Pca, Xanthan Gum, Phenoxyethanol, Chlorphenesin"</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -9100,16 +9098,16 @@
         </is>
       </c>
       <c r="E242" s="3" t="n">
-        <v>75000</v>
+        <v>61000</v>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztg-mf3q85w4ynm21a@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztn-mf3qnnfk6jgv06.webp</t>
         </is>
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/5Apz4xTxCh</t>
+          <t>https://s.shopee.co.id/9UyyEyh2l1</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9115,7 @@
       <c r="A243" s="3" t="inlineStr">
         <is>
           <t>TheActives.
-Salicylic Acid 2% + Zinc 0,5% Serum</t>
+Niacinamide 10% + Nag 2% Serum</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -9127,7 +9125,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Propanediol, Salicylic Acid, Trisodium Citrate, Panthenol, Glycerin, Zinc Pca, Xanthan Gum, Phenoxyethanol, Chlorphenesin"</t>
+          <t>"Aqua, Niacinamide, Butylene Glycol, N-Acetyl Glucosamine, Ethoxydiglycol, Dimethyl Isosorbide, Sodium Hyaluronate, Xanthan Gum, Phenoxyethanol, Chlorphenesin"</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -9136,24 +9134,24 @@
         </is>
       </c>
       <c r="E243" s="3" t="n">
-        <v>61000</v>
+        <v>64000</v>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztn-mf3qnnfk6jgv06.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztc-mf3qd0ou96oef4@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9UyyEyh2l1</t>
+          <t>https://s.shopee.co.id/8fPrFUjlCJ</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>TheActives.
-Niacinamide 10% + Nag 2% Serum</t>
+          <t>All Perfect
+Whitening Serum</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -9163,7 +9161,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Butylene Glycol, N-Acetyl Glucosamine, Ethoxydiglycol, Dimethyl Isosorbide, Sodium Hyaluronate, Xanthan Gum, Phenoxyethanol, Chlorphenesin"</t>
+          <t>"Aqua, Niacinamide, Propylene Glycol, Alpha-Arbutin, Ethyl Ascorbic Acid, Hamamelis Virginiana Extract, Ethoxydiglycol, Euglena Gracilis Polysaccharide, Hydrolyzed Collagen, Glycerin, Alcohol, Xanthan Gum, Phenoxyethanol, Aloe Barbadensis Leaf Extract, Disodium EDTA, PEG-40 Hydrogenated Castor Oil, Fragrance, Goat Milk Extract, Farnesol, Ethylhexyl-Glycerin, Sodium Metabisulphite, Arbutin, Lecithin, Linoleic Acid, Sodium Ascorbyl Phosphate, Tocopheryl Acetate, Linalool, Glutathione, Tocopherol, Vitis Vinifera Extract"</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -9172,34 +9170,34 @@
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>64000</v>
+        <v>68000</v>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztc-mf3qd0ou96oef4@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztk-mf7xt21yapzda6@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8fPrFUjlCJ</t>
+          <t>https://s.shopee.co.id/3B52BBlp1a</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>All Perfect
-Whitening Serum</t>
+          <t>Real White
+AHA BHA Face Serum</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Eksfoliasi</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Propylene Glycol, Alpha-Arbutin, Ethyl Ascorbic Acid, Hamamelis Virginiana Extract, Ethoxydiglycol, Euglena Gracilis Polysaccharide, Hydrolyzed Collagen, Glycerin, Alcohol, Xanthan Gum, Phenoxyethanol, Aloe Barbadensis Leaf Extract, Disodium EDTA, PEG-40 Hydrogenated Castor Oil, Fragrance, Goat Milk Extract, Farnesol, Ethylhexyl-Glycerin, Sodium Metabisulphite, Arbutin, Lecithin, Linoleic Acid, Sodium Ascorbyl Phosphate, Tocopheryl Acetate, Linalool, Glutathione, Tocopherol, Vitis Vinifera Extract"</t>
+          <t>"Aqua, PPG-40-PEG-60 Lanolin Oil, Butylene Glycol, Glycolic Acid, Salicylic Acid, Polyacrylate Crosspolymer-11, Phenoxyethanol"</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -9208,52 +9206,52 @@
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>68000</v>
+        <v>90000</v>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztk-mf7xt21yapzda6@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasa-m12jepmcobf917@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3B52BBlp1a</t>
+          <t>https://s.shopee.co.id/4AxZNIS0MU</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>Real White
-AHA BHA Face Serum</t>
+          <t>Avoskin
+Your Skin Bae Lactic Acid 10% + Kiwi Fruit 5% + Niacinamide 2,5% High Dose Serum</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, PPG-40-PEG-60 Lanolin Oil, Butylene Glycol, Glycolic Acid, Salicylic Acid, Polyacrylate Crosspolymer-11, Phenoxyethanol"</t>
+          <t>"Aqua, L-Lactic Acid, Glycerin, Actinidia Chinensis (Kiwi) Fruit Extract, Biosaccharide Gum-1, Butylene Glycol, Niacinamide, NaOH (48%), Butylene Glycol, Hydroxyethyl Cellulose, Phenoxyethanol, Allantoin, Chlorphenesin, Disodium EDTA, Sodium Bisulfite"</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>90000</v>
+        <v>89000</v>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasa-m12jepmcobf917@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7qul1-lhspohs9od7o03@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4AxZNIS0MU</t>
+          <t>https://s.shopee.co.id/7pqrk6nD1x</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9259,7 @@
       <c r="A247" s="3" t="inlineStr">
         <is>
           <t>Avoskin
-Your Skin Bae Lactic Acid 10% + Kiwi Fruit 5% + Niacinamide 2,5% High Dose Serum</t>
+Your Skin Bae Serum Tea Tree + Witch Hazel + Glycolic Acid + Rosemary</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -9271,7 +9269,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, L-Lactic Acid, Glycerin, Actinidia Chinensis (Kiwi) Fruit Extract, Biosaccharide Gum-1, Butylene Glycol, Niacinamide, NaOH (48%), Butylene Glycol, Hydroxyethyl Cellulose, Phenoxyethanol, Allantoin, Chlorphenesin, Disodium EDTA, Sodium Bisulfite"</t>
+          <t>"Aqua, Propylene Glycol, Glycerin, Niacinamide (2%), Xanthan Gum, Phenoxyethanol, Glycolic Acid (0.5%), Rosmarinus Officinalis Extract, Melaleuca Alternifolia Leaf Extract, Hamamelis Virginiana Leaf Extract (0.3%), Butylene Glycol, Chlorphenesin, Sodium Bisulfite, Tetrasodium EDTA, Biosaccharide Gum-1, 1,2-Hexanediol, Sodium Hydroxide, Tea Tree, Witch Hazel, Glycolic Acid, Rosemary Extract"</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -9280,16 +9278,16 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>89000</v>
+        <v>75000</v>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7qul1-lhspohs9od7o03@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/sg-11134201-22100-58qb9gqh26iv08@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/7pqrk6nD1x</t>
+          <t>https://s.shopee.co.id/AUrcv4BO3Y</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9295,7 @@
       <c r="A248" s="3" t="inlineStr">
         <is>
           <t>Avoskin
-Your Skin Bae Serum Tea Tree + Witch Hazel + Glycolic Acid + Rosemary</t>
+Ysb Serum Mandelic Acid 5% + Panthenol + Perilla Extract</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -9307,7 +9305,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Propylene Glycol, Glycerin, Niacinamide (2%), Xanthan Gum, Phenoxyethanol, Glycolic Acid (0.5%), Rosmarinus Officinalis Extract, Melaleuca Alternifolia Leaf Extract, Hamamelis Virginiana Leaf Extract (0.3%), Butylene Glycol, Chlorphenesin, Sodium Bisulfite, Tetrasodium EDTA, Biosaccharide Gum-1, 1,2-Hexanediol, Sodium Hydroxide, Tea Tree, Witch Hazel, Glycolic Acid, Rosemary Extract"</t>
+          <t>"Aqua, Propylene Glycol, Mandelic Acid (5%), Glycerin, Xanthan Gum, Phenoxyethanol, Sodium Hydroxide, Panthenol (0.5%), Chlorphenesin, Sodium Bisulfite, Tetrasodium EDTA, Perilla Ocymoides Seed Extract, Biosaccharide Gum-1, Benzaldehyde, Benzoic Acid, Potassium Sorbate, Sodium Benzoate"</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -9316,24 +9314,24 @@
         </is>
       </c>
       <c r="E248" s="3" t="n">
-        <v>75000</v>
+        <v>125000</v>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/sg-11134201-22100-58qb9gqh26iv08@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/sg-11134201-22100-2ohwh7rn26iv75@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/AUrcv4BO3Y</t>
+          <t>https://s.shopee.co.id/60PDYt38LH</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>Avoskin
-Ysb Serum Mandelic Acid 5% + Panthenol + Perilla Extract</t>
+          <t>Reluvie
+Acne Serum</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -9343,33 +9341,32 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Propylene Glycol, Mandelic Acid (5%), Glycerin, Xanthan Gum, Phenoxyethanol, Sodium Hydroxide, Panthenol (0.5%), Chlorphenesin, Sodium Bisulfite, Tetrasodium EDTA, Perilla Ocymoides Seed Extract, Biosaccharide Gum-1, Benzaldehyde, Benzoic Acid, Potassium Sorbate, Sodium Benzoate"</t>
+          <t>"Aqua, Alcohol, Ethoxydiglycol, Glycerin, Salicylic Acid, Phenoxyethanol, Amylopectin, Hydroxyethylcellulose, Dextrin, Xanthan Gum, Triethanolamine, Ethylhexyl Glycerine"</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E249" s="3" t="n">
-        <v>125000</v>
+        <v>75000</v>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/sg-11134201-22100-2ohwh7rn26iv75@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasf-m5cfri1w66dvde@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/60PDYt38LH</t>
+          <t>https://s.shopee.co.id/5L9WlnEoX0</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>Reluvie
-Acne Serum</t>
+          <t>Kagary Brightening Serum 10% Niacinamide 5% Vitamin C 1% Zinc Brightening &amp; Anti-aging Serum</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -9379,32 +9376,33 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Alcohol, Ethoxydiglycol, Glycerin, Salicylic Acid, Phenoxyethanol, Amylopectin, Hydroxyethylcellulose, Dextrin, Xanthan Gum, Triethanolamine, Ethylhexyl Glycerine"</t>
+          <t>"Aqua, Niacinamide, Butylene Glycol, Glycerin, 3-0-Ethyl Ascorbic Acid, Methylpropanediol, Carbomer, Arginine, Hydroxyacetophenone, Panthenol, Sodium Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Stephania Tetrandra Extract, Hydroxyethylcellulose, Isohexadecane, Caprylhydroxamic Acid, Disodium EDTA, Citric Acid, Centella Asiatica Extract, Polysorbate 80, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Sorbitan Oleate, Camellia Sinensis Leaf Extract, Glycyrrhiza Glabra (Licorice) Root Extract, Titanium Dioxide, Glyceryl Caprylate, Phenoxyethanol, PEG-40 Hydrogenated Castor Oil, Chamomilla Recutita (Matricaria) Flower Extract, Rosmarinus Officinalis (Rosemar Y) Leaf Extract, Fragrance, Zinc Pca, PEG-10, Alumina, Ci 15985, Silica, Sodium Chloride, Ci 19140"</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>75000</v>
+        <v>19000</v>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasf-m5cfri1w66dvde@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rase-m2g6tisar98q7d@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/5L9WlnEoX0</t>
+          <t>https://s.shopee.co.id/1VwoCnWWhA</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>Kagary Brightening Serum 10% Niacinamide 5% Vitamin C 1% Zinc Brightening &amp; Anti-aging Serum</t>
+          <t>PURE DEW
+3x Retinol Anti-wrinkle Serum</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -9414,25 +9412,25 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Niacinamide, Butylene Glycol, Glycerin, 3-0-Ethyl Ascorbic Acid, Methylpropanediol, Carbomer, Arginine, Hydroxyacetophenone, Panthenol, Sodium Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Stephania Tetrandra Extract, Hydroxyethylcellulose, Isohexadecane, Caprylhydroxamic Acid, Disodium EDTA, Citric Acid, Centella Asiatica Extract, Polysorbate 80, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Sorbitan Oleate, Camellia Sinensis Leaf Extract, Glycyrrhiza Glabra (Licorice) Root Extract, Titanium Dioxide, Glyceryl Caprylate, Phenoxyethanol, PEG-40 Hydrogenated Castor Oil, Chamomilla Recutita (Matricaria) Flower Extract, Rosmarinus Officinalis (Rosemar Y) Leaf Extract, Fragrance, Zinc Pca, PEG-10, Alumina, Ci 15985, Silica, Sodium Chloride, Ci 19140"</t>
+          <t>"Aqua, Dipropylene Glycol, Butylene Glycol, Glycereth-26, 1,2-Hexanediol, Niacinamide, Phenoxyethanol, Trehalose, Carnosine, Carbomer, Arginine, Chlorphenesin, Glycerin, Disodium EDTA, PEG-40 Hydrogenated Castor Oil, Sodium Hyaluronate, Aroma, Palmitoyl Tripeptide-5, Dipeptide Diaminobutyroyl Benzylamide Diacetate, Ci 19140, Ci 15985, Caprylic/​Capric Triglyceride, Polysorbate 80, Retinyl Propionate, Retinol, Polysorbate 20, Ethyl Lauroyl Arginate Hcl, Hydroxypinacolone Retinoate"</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E251" s="3" t="n">
-        <v>19000</v>
+        <v>39000</v>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rase-m2g6tisar98q7d@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-82250-mfw9njumuwwbb3@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/1VwoCnWWhA</t>
+          <t>https://s.shopee.co.id/AUrcvTd1tr</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9438,7 @@
       <c r="A252" s="3" t="inlineStr">
         <is>
           <t>PURE DEW
-3x Retinol Anti-wrinkle Serum</t>
+ARBUTIN-BRIGHTEN VITAMIN C SERUM</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -9450,7 +9448,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Dipropylene Glycol, Butylene Glycol, Glycereth-26, 1,2-Hexanediol, Niacinamide, Phenoxyethanol, Trehalose, Carnosine, Carbomer, Arginine, Chlorphenesin, Glycerin, Disodium EDTA, PEG-40 Hydrogenated Castor Oil, Sodium Hyaluronate, Aroma, Palmitoyl Tripeptide-5, Dipeptide Diaminobutyroyl Benzylamide Diacetate, Ci 19140, Ci 15985, Caprylic/​Capric Triglyceride, Polysorbate 80, Retinyl Propionate, Retinol, Polysorbate 20, Ethyl Lauroyl Arginate Hcl, Hydroxypinacolone Retinoate"</t>
+          <t>"Aqua, Glycerin, Butylene Glycol, Niacinamide, Glycereth-26, Betaine, 1,2-Hexanediol, Diethoxyethyl Succinate, Phenoxyethanol, Saccharide Isomerate, Carbomer, Arginine, Panthenol, Chlorphenesin, Sodium Hyaluronate, Sodium Polyacrylate, PEG-40 Hydrogenated Castor Oil, Disodium EDTA, Aroma, Sodium Citrate, Citric Acid, Arbutin, Tranexamic Acid, 3-0-Ethyl Ascorbic Acid, Glutathione"</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -9459,24 +9457,24 @@
         </is>
       </c>
       <c r="E252" s="3" t="n">
-        <v>39000</v>
+        <v>48000</v>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-82250-mfw9njumuwwbb3@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-8224p-mfw9njuistu620@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/AUrcvTd1tr</t>
+          <t>https://s.shopee.co.id/70HklBJmDP</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>PURE DEW
-ARBUTIN-BRIGHTEN VITAMIN C SERUM</t>
+          <t>Implora
+Bakuchiol Serum</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -9486,25 +9484,25 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Butylene Glycol, Niacinamide, Glycereth-26, Betaine, 1,2-Hexanediol, Diethoxyethyl Succinate, Phenoxyethanol, Saccharide Isomerate, Carbomer, Arginine, Panthenol, Chlorphenesin, Sodium Hyaluronate, Sodium Polyacrylate, PEG-40 Hydrogenated Castor Oil, Disodium EDTA, Aroma, Sodium Citrate, Citric Acid, Arbutin, Tranexamic Acid, 3-0-Ethyl Ascorbic Acid, Glutathione"</t>
+          <t>"Aqua, Butylene Glycol, Propylene Glycol, Glyserin, Ethoxydiglycol, Psoralea Corylifolia Fruit Extract, Silanediol Salicylate, Sodium Lactate, Sodium PCA, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, DMDM Hydantoin, Hydroxypropyl Methylcellulose, Tetrasodium EDTA, 1,2-Hexanediol, Sodium Hydroxide, Triethanolamine, Euterpe Oleracea Fruit Extract, Fragaria Vesca Fruit Extract, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Ribes Nigrum Fruit Extract, Rubus Fruticosus Fruit Extract, Rubus Idaeus Fruit Extract, Urea, Vaccinium Angustifolium Fruit Extract, Vaccinium Macrocarpon Fruit Extract, Iodopropynyl Butylcarbamate, Sodium Benzoate, Aloe Barbadensis Leaf Extract, Sodium Chloride, Sodium Methylparaben, Benzoic Acid, Bakuchiol, Propyl Paraben"</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E253" s="3" t="n">
-        <v>48000</v>
+        <v>25000</v>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-8224p-mfw9njuistu620@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-jicyy1c7rpov02@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/70HklBJmDP</t>
+          <t>https://s.shopee.co.id/902p8yyH8n</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9510,7 @@
       <c r="A254" s="3" t="inlineStr">
         <is>
           <t>Implora
-Bakuchiol Serum</t>
+Acne Serum</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -9522,7 +9520,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Propylene Glycol, Glyserin, Ethoxydiglycol, Psoralea Corylifolia Fruit Extract, Silanediol Salicylate, Sodium Lactate, Sodium PCA, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, DMDM Hydantoin, Hydroxypropyl Methylcellulose, Tetrasodium EDTA, 1,2-Hexanediol, Sodium Hydroxide, Triethanolamine, Euterpe Oleracea Fruit Extract, Fragaria Vesca Fruit Extract, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Ribes Nigrum Fruit Extract, Rubus Fruticosus Fruit Extract, Rubus Idaeus Fruit Extract, Urea, Vaccinium Angustifolium Fruit Extract, Vaccinium Macrocarpon Fruit Extract, Iodopropynyl Butylcarbamate, Sodium Benzoate, Aloe Barbadensis Leaf Extract, Sodium Chloride, Sodium Methylparaben, Benzoic Acid, Bakuchiol, Propyl Paraben"</t>
+          <t>"Aqua, Centella Asiatica Extract, Butylene Glycol, Propylene Glycol, Glyserin, Silanediol Salicylate, Propanediol, Ethoxydiglycol, 1,2-Hexanediol, Sodium Lactate, Sodium PCA, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, DMDM Hydantoin, Fomes Officinalis Extract, Hydroxypropyl Methylcellulose, Tetrasodium EDTA, Sodium Hydroxide, Triethanolamine, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Urea, Iodopropynyl Butylcarbamate, Sodium Benzoate, Sodium Methylparaben, Terry-Dry Freeze Dried Or Spray Dried Aloevera Powders, Sodium Chloride, Benzoic Acid, Propyl Paraben"</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -9531,16 +9529,16 @@
         </is>
       </c>
       <c r="E254" s="3" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-jicyy1c7rpov02@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-wn75gxm6rpovd6@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/902p8yyH8n</t>
+          <t>https://s.shopee.co.id/30lc0EaWWy</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9546,7 @@
       <c r="A255" s="3" t="inlineStr">
         <is>
           <t>Implora
-Acne Serum</t>
+Midnight Serum</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -9558,7 +9556,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Centella Asiatica Extract, Butylene Glycol, Propylene Glycol, Glyserin, Silanediol Salicylate, Propanediol, Ethoxydiglycol, 1,2-Hexanediol, Sodium Lactate, Sodium PCA, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, DMDM Hydantoin, Fomes Officinalis Extract, Hydroxypropyl Methylcellulose, Tetrasodium EDTA, Sodium Hydroxide, Triethanolamine, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Urea, Iodopropynyl Butylcarbamate, Sodium Benzoate, Sodium Methylparaben, Terry-Dry Freeze Dried Or Spray Dried Aloevera Powders, Sodium Chloride, Benzoic Acid, Propyl Paraben"</t>
+          <t>"Aqua, Galactomyces Ferment Filtrate, Butylene Glycol, Propylene Glycol, Glycerine, Ethoxydiglycol, Hydrolyzed Pea Protein, Pentylene Glycol, Sodium Lactate, Sodium PCA, DMDM Hydantoin, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Hydroxypropyl Methylcellulose, Hamamelis Virginiana (Witch Hazel) Extract, Polysorbate 20, Phenoxyethanol, Tetrasodium EDTA, Coriandrum Sativum Fruit Extract, Sodium Hydroxide, Olea Europaea Fruit Extract, Triethanolamine, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Urea, Iodopropynyl Butylcarbamate, Sodium Benzoate, Terry-Dry Freeze Dried Or Spray Dried Aloe Vera Powders, Sodium Chloride, Benzoic Acid"</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -9567,16 +9565,16 @@
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-wn75gxm6rpovd6@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-ohczgvt6rpovd5@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/30lc0EaWWy</t>
+          <t>https://s.shopee.co.id/20t4om5t4O</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9582,7 @@
       <c r="A256" s="3" t="inlineStr">
         <is>
           <t>Implora
-Midnight Serum</t>
+Hydrating Serum</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -9594,7 +9592,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Galactomyces Ferment Filtrate, Butylene Glycol, Propylene Glycol, Glycerine, Ethoxydiglycol, Hydrolyzed Pea Protein, Pentylene Glycol, Sodium Lactate, Sodium PCA, DMDM Hydantoin, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Hydroxypropyl Methylcellulose, Hamamelis Virginiana (Witch Hazel) Extract, Polysorbate 20, Phenoxyethanol, Tetrasodium EDTA, Coriandrum Sativum Fruit Extract, Sodium Hydroxide, Olea Europaea Fruit Extract, Triethanolamine, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Urea, Iodopropynyl Butylcarbamate, Sodium Benzoate, Terry-Dry Freeze Dried Or Spray Dried Aloe Vera Powders, Sodium Chloride, Benzoic Acid"</t>
+          <t>"Aqua, Butylene Glycol, Propylene Glycol, Glyserin, Chenopodium Quinoa Seed Extract, Ethoxydiglycol, Sodium Hyaluronate, Sodium Lactate, Sodium PCA, DMDM Hydantoin, Tetrasodium EDTA, Triethanolamine, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Urea, Iodopropynyl Butylcarbamate, Sodium Benzoate, Aloe Barbadensis Leaf Extract, Benzoic Acid"</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -9603,59 +9601,59 @@
         </is>
       </c>
       <c r="E256" s="3" t="n">
-        <v>22000</v>
+        <v>37000</v>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-ohczgvt6rpovd5@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-p3rynr36rpov68@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/20t4om5t4O</t>
+          <t>https://s.shopee.co.id/W4H2BbBhQ</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>Implora
-Hydrating Serum</t>
+          <t>COSRX AHA/BHA Clarifying Treatment Toner</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Eksfoliasi</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Propylene Glycol, Glyserin, Chenopodium Quinoa Seed Extract, Ethoxydiglycol, Sodium Hyaluronate, Sodium Lactate, Sodium PCA, DMDM Hydantoin, Tetrasodium EDTA, Triethanolamine, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Urea, Iodopropynyl Butylcarbamate, Sodium Benzoate, Aloe Barbadensis Leaf Extract, Benzoic Acid"</t>
+          <t xml:space="preserve">"Water, Salix Alba (Willow) Bark Water, Pyrus Malus (Apple) Fruit Water, Butylene Glycol, 1,2-Hexanediol, Sodium Lactate, Glycolic Acid, Betaine Salicylate, Allantoin, Panthenol, Ethyl Hexanediol"
+</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E257" s="3" t="n">
-        <v>37000</v>
+        <v>130000</v>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134201-23030-p3rynr36rpov68@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98u-lw56siywgtjhfe.webp</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/W4H2BbBhQ</t>
+          <t>https://s.shopee.co.id/4LGzbKYXRd</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>COSRX AHA/BHA Clarifying Treatment Toner</t>
+          <t>Somethinc Glow Maker AHA BHA PHA Clarifying Treatment Toner</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -9665,8 +9663,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Water, Salix Alba (Willow) Bark Water, Pyrus Malus (Apple) Fruit Water, Butylene Glycol, 1,2-Hexanediol, Sodium Lactate, Glycolic Acid, Betaine Salicylate, Allantoin, Panthenol, Ethyl Hexanediol"
-</t>
+          <t>"Water, Butylene Glycol, Glycolic Acid, Arginine, 1,2-Hexanediol, Betaine, Allantoin, Lactobionic Acid, Anthemis Nobilis Flower Extract, Salicylic Acid, Caffeine"</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -9675,23 +9672,23 @@
         </is>
       </c>
       <c r="E258" s="3" t="n">
-        <v>130000</v>
+        <v>135000</v>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98u-lw56siywgtjhfe.webp</t>
+          <t>https://down-bs-id.img.susercontent.com/id-11134207-8224u-ml7fl9fyzfnn41.webp</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4LGzbKYXRd</t>
+          <t>https://s.shopee.co.id/40e9CuuBp1</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>Somethinc Glow Maker AHA BHA PHA Clarifying Treatment Toner</t>
+          <t>Avoskin Miraculous Refining Toner (AHA/BHA/PHA)</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -9701,7 +9698,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>"Water, Butylene Glycol, Glycolic Acid, Arginine, 1,2-Hexanediol, Betaine, Allantoin, Lactobionic Acid, Anthemis Nobilis Flower Extract, Salicylic Acid, Caffeine"</t>
+          <t>"Water, Glycerin, Glycolic Acid, Butylene Glycol, Propylene Glycol, Gluconolactone, Melaleuca Alternifolia (Tea Tree) Leaf Extract, Hamamelis Virginiana (Witch Hazel) Leaf Extract, Niacinamide, Chamomilla Recutita (Matricaria) Flower Extract, Rubus Idaeus (Raspberry Fruit) Extract, Citrus Limon (Lemon) Fruit Extract, Salicylic Acid, Acer Saccharum (Sugar Maple) Extract, Portulaca Oleracea Extract, Aloe Barbadensis Leaf Juice, Amylopectin, Dextrin, Xanthan Gum, Tetrasodium EDTA, Sodium Hydroxymethylglycinate, Polyglutamic Acid"</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -9710,23 +9707,23 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>135000</v>
+        <v>100000</v>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>https://down-bs-id.img.susercontent.com/id-11134207-8224u-ml7fl9fyzfnn41.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/49192457-83b4-4d97-bb6e-4737a78eb782/products/avoskin-miraculous-refining-toner/avoskin-miraculous-refining-toner_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/40e9CuuBp1</t>
+          <t>https://s.shopee.co.id/8pjOxuCHAK</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>Avoskin Miraculous Refining Toner (AHA/BHA/PHA)</t>
+          <t>Emina Ms. Pimple Acne Solution Exfoliating Toner</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -9736,7 +9733,8 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycerin, Glycolic Acid, Butylene Glycol, Propylene Glycol, Gluconolactone, Melaleuca Alternifolia (Tea Tree) Leaf Extract, Hamamelis Virginiana (Witch Hazel) Leaf Extract, Niacinamide, Chamomilla Recutita (Matricaria) Flower Extract, Rubus Idaeus (Raspberry Fruit) Extract, Citrus Limon (Lemon) Fruit Extract, Salicylic Acid, Acer Saccharum (Sugar Maple) Extract, Portulaca Oleracea Extract, Aloe Barbadensis Leaf Juice, Amylopectin, Dextrin, Xanthan Gum, Tetrasodium EDTA, Sodium Hydroxymethylglycinate, Polyglutamic Acid"</t>
+          <t xml:space="preserve">"Aqua, Glyserin, Biosaccharide Gum-1, Zinc Gluconate, Butylene Glycol, Phenoxyethanol, Salicylic Acid, Amylopectin, Dextrin, Xanthan Gum, Chlorphenesin, Allantoin, Disodium EDTA, Aminomethyl Propanol, Trideceth-9, Hamamelis Virginiana Witch Hazel Extract, PEG-40 Hydrogenated Castor Oil, Fragrance, Polysorbate 20, Epilobium Angustifolium Extract, Sodium Metabisulfite"
+</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -9745,23 +9743,23 @@
         </is>
       </c>
       <c r="E260" s="3" t="n">
-        <v>100000</v>
+        <v>43000</v>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/49192457-83b4-4d97-bb6e-4737a78eb782/products/avoskin-miraculous-refining-toner/avoskin-miraculous-refining-toner_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/1aa0c6dd-2277-45a8-bbea-e6295a858f26/products/emina-ms-pimple-exfoliating-toner/emina-ms-pimple-exfoliating-toner_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8pjOxuCHAK</t>
+          <t>https://s.shopee.co.id/BRQe1whTO</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>Emina Ms. Pimple Acne Solution Exfoliating Toner</t>
+          <t>Azarine Daily Beginner Exfoliating Toner</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -9771,7 +9769,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Aqua, Glyserin, Biosaccharide Gum-1, Zinc Gluconate, Butylene Glycol, Phenoxyethanol, Salicylic Acid, Amylopectin, Dextrin, Xanthan Gum, Chlorphenesin, Allantoin, Disodium EDTA, Aminomethyl Propanol, Trideceth-9, Hamamelis Virginiana Witch Hazel Extract, PEG-40 Hydrogenated Castor Oil, Fragrance, Polysorbate 20, Epilobium Angustifolium Extract, Sodium Metabisulfite"
+          <t xml:space="preserve">"Aqua, Glycerin, Portulaca Oleracea Extract, Lactic Acid, Potassium Azeloyl Diglycinate, Allantoin, Lactobionic Acid, Bacillus Ferment, Propylene Glycol, Chlorphenesin, Salicylic Acid, Sodium Hyaluronate, Xanthan Gum, Phenoxyethanol, Citric Acid"
 </t>
         </is>
       </c>
@@ -9781,23 +9779,23 @@
         </is>
       </c>
       <c r="E261" s="3" t="n">
-        <v>43000</v>
+        <v>60000</v>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/1aa0c6dd-2277-45a8-bbea-e6295a858f26/products/emina-ms-pimple-exfoliating-toner/emina-ms-pimple-exfoliating-toner_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/0683b808-0900-419e-81ff-5cb9b829fbc5/products/azarine-daily-beginner-exfoliating-toner/azarine-daily-beginner-exfoliating-toner_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/BRQe1whTO</t>
+          <t>https://s.shopee.co.id/5fmNCYr2U0</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>Azarine Daily Beginner Exfoliating Toner</t>
+          <t>SOME BY MI AHA BHA PHA 30 Days Miracle Toner</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -9807,8 +9805,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Aqua, Glycerin, Portulaca Oleracea Extract, Lactic Acid, Potassium Azeloyl Diglycinate, Allantoin, Lactobionic Acid, Bacillus Ferment, Propylene Glycol, Chlorphenesin, Salicylic Acid, Sodium Hyaluronate, Xanthan Gum, Phenoxyethanol, Citric Acid"
-</t>
+          <t>"Water, Butylene Glycol, Dipropylene Glycol, Glycerin, Niacinamide, Melaleuca Alternifolia (Tea Tree) Leaf Water, Polyglyceryl-4 Caprate, Carica Papaya (Papaya) Fruit Extract, Lens Esculenta (Lentil) Seed Extract, Hamamelis Virginiana (Witch Hazel) Extract, Nelumbo Nucifera Flower Extract, Swiftlet Nest Extract, Sodium Hyaluronate, Fructan, Allantoin, Adenosine, Hydroxyethyl Urea, Xylitol, Salicylic Acid, Lactobionic Acid, Citric Acid, Sodium Citrate, 1,2-Hexanediol, Benzyl Glycol, Ethylhexylglycerin, Raspberry Ketone, Mentha Piperita (Peppermint) Oil"</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -9821,19 +9818,19 @@
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/0683b808-0900-419e-81ff-5cb9b829fbc5/products/azarine-daily-beginner-exfoliating-toner/azarine-daily-beginner-exfoliating-toner_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/798588a4-c1dd-45f4-873f-ba55f805c942/products/some-by-mi-aha-bha-pha-30days-miracle-toner/some-by-mi-aha-bha-pha-30days-miracle-toner_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/5fmNCYr2U0</t>
+          <t>https://s.shopee.co.id/2g8ldBOjVh</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>SOME BY MI AHA BHA PHA 30 Days Miracle Toner</t>
+          <t>The Originote H-llow Clarifying Toner</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -9843,7 +9840,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>"Water, Butylene Glycol, Dipropylene Glycol, Glycerin, Niacinamide, Melaleuca Alternifolia (Tea Tree) Leaf Water, Polyglyceryl-4 Caprate, Carica Papaya (Papaya) Fruit Extract, Lens Esculenta (Lentil) Seed Extract, Hamamelis Virginiana (Witch Hazel) Extract, Nelumbo Nucifera Flower Extract, Swiftlet Nest Extract, Sodium Hyaluronate, Fructan, Allantoin, Adenosine, Hydroxyethyl Urea, Xylitol, Salicylic Acid, Lactobionic Acid, Citric Acid, Sodium Citrate, 1,2-Hexanediol, Benzyl Glycol, Ethylhexylglycerin, Raspberry Ketone, Mentha Piperita (Peppermint) Oil"</t>
+          <t>"Water, Glycerin, Butylene Glycol, Phenoxyethanol, Lactobionic Acid, Niacinamide, Methylparaben, Allantoin, Glycolic Acid, Sodium Hydroxide, Ethylhexylglycerin, Disodium EDTA, Salicylic Acid, Xanthan Gum, Sodium Hyaluronate, Salix Alba (Willow) Bark Extract, Propanediol 1,3, 1,2-Hexanediol, Centella Asiatica Extract, Dextrin, Artemisia Argyi Leaf Extract, Caprylhydroxamic Acid"</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -9852,23 +9849,23 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>60000</v>
+        <v>36000</v>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/798588a4-c1dd-45f4-873f-ba55f805c942/products/some-by-mi-aha-bha-pha-30days-miracle-toner/some-by-mi-aha-bha-pha-30days-miracle-toner_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/ebe451cb-dcde-4576-b196-3dc4b094a77d/products/the-originote-h-llow-clarifying-toner-aha-bha-pha-with-willow-bark/the-originote-h-llow-clarifying-toner-aha-bha-pha-with-willow-bark_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G263" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/2g8ldBOjVh</t>
+          <t>https://s.shopee.co.id/902pAugjm4</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>The Originote H-llow Clarifying Toner</t>
+          <t>NPURE Cica Clear Pad</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -9878,7 +9875,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycerin, Butylene Glycol, Phenoxyethanol, Lactobionic Acid, Niacinamide, Methylparaben, Allantoin, Glycolic Acid, Sodium Hydroxide, Ethylhexylglycerin, Disodium EDTA, Salicylic Acid, Xanthan Gum, Sodium Hyaluronate, Salix Alba (Willow) Bark Extract, Propanediol 1,3, 1,2-Hexanediol, Centella Asiatica Extract, Dextrin, Artemisia Argyi Leaf Extract, Caprylhydroxamic Acid"</t>
+          <t>"Water, Butylene Glycol, Methylpropanediol, 1,2-Hexanediol, Acetyl Glucosamine, Glycerin, Phenoxyethanol, Hydroxyacetophenone, Betaine, PEG-60 Hydrogenated Castor Oil, Sodium Citrate, Caffeine, Octyldodeceth-16, Panthenol, Allantoin, Capryl Glycol, Ethylhexylglycerin, Disodium EDTA, Xanthan Gum, Rosmarinus Officinalis (Rosemary) Leaf Oil, Melia Azadirachta Leaf Extract, Citric Acid, Salix Alba (Willow) Bark Extract, Centella Asiatica Leaf Extract, Centella Asiatica Root Extract, Saccharomyces Ferment, Madecassoside, Madecassic Acid, Asiaticoside, Asiatic Acid, Centella Asiatica Leaf Water, Melia Azadirachta Flower Extract, Lactobionic Acid, Helianthus Annuus (Sunflower) Seed Oil, Glycolic Acid, Centella Asiatica Extract, Tocopherol, Propanediol"</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -9887,23 +9884,23 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>36000</v>
+        <v>85000</v>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/ebe451cb-dcde-4576-b196-3dc4b094a77d/products/the-originote-h-llow-clarifying-toner-aha-bha-pha-with-willow-bark/the-originote-h-llow-clarifying-toner-aha-bha-pha-with-willow-bark_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/ebafe400-f12f-46fe-8a13-a0eaf9979b2e/products/npure-npure-cica-acne-clear-pad/npure-npure-cica-acne-clear-pad_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/902pAugjm4</t>
+          <t>https://s.shopee.co.id/W4H3MKD93</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>NPURE Cica Clear Pad</t>
+          <t>Elsheskin Exfolicare Solution</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -9913,7 +9910,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>"Water, Butylene Glycol, Methylpropanediol, 1,2-Hexanediol, Acetyl Glucosamine, Glycerin, Phenoxyethanol, Hydroxyacetophenone, Betaine, PEG-60 Hydrogenated Castor Oil, Sodium Citrate, Caffeine, Octyldodeceth-16, Panthenol, Allantoin, Capryl Glycol, Ethylhexylglycerin, Disodium EDTA, Xanthan Gum, Rosmarinus Officinalis (Rosemary) Leaf Oil, Melia Azadirachta Leaf Extract, Citric Acid, Salix Alba (Willow) Bark Extract, Centella Asiatica Leaf Extract, Centella Asiatica Root Extract, Saccharomyces Ferment, Madecassoside, Madecassic Acid, Asiaticoside, Asiatic Acid, Centella Asiatica Leaf Water, Melia Azadirachta Flower Extract, Lactobionic Acid, Helianthus Annuus (Sunflower) Seed Oil, Glycolic Acid, Centella Asiatica Extract, Tocopherol, Propanediol"</t>
+          <t>"Water, Mandelic Acid (4%), Lactic Acid (4%), Sodium Hydroxide, Actinidia Chinensis Fruit Water, Glycolic Acid (1%), Glycerin, Pentylene Glycol, Salicylic Acid (1%), Aloe Barbadensis Leaf Juice, Propylene Glycol, Phenoxyethanol, Chlorphenesin, Hydroxyethylcellulose, Butylene Glycol, Panthenol, Allantoin, Cucumis Sativus Fruit Extract, Ethylhexylglycerin, Sodium Hyaluronate, Glucose, Arctostaphylos Uva-Ursi Leaf Extract, Butylene Glycol, Calendula Officinalis Flower Extract, Papain, Potassium Sorbate, Sodium Benzoate, Rosa Roxburghii Fruit Extract"</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -9922,23 +9919,23 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>85000</v>
+        <v>150000</v>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/ebafe400-f12f-46fe-8a13-a0eaf9979b2e/products/npure-npure-cica-acne-clear-pad/npure-npure-cica-acne-clear-pad_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/ac95a6c8-7cb5-4799-a423-749b4281787c/products/elsheskin-exfolicare-solution-toner/elsheskin-exfolicare-solution-toner_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/W4H3MKD93</t>
+          <t>https://s.shopee.co.id/3qKj1ci5qs</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>Elsheskin Exfolicare Solution</t>
+          <t>Benton Aloe BHA Skin Toner</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -9948,7 +9945,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>"Water, Mandelic Acid (4%), Lactic Acid (4%), Sodium Hydroxide, Actinidia Chinensis Fruit Water, Glycolic Acid (1%), Glycerin, Pentylene Glycol, Salicylic Acid (1%), Aloe Barbadensis Leaf Juice, Propylene Glycol, Phenoxyethanol, Chlorphenesin, Hydroxyethylcellulose, Butylene Glycol, Panthenol, Allantoin, Cucumis Sativus Fruit Extract, Ethylhexylglycerin, Sodium Hyaluronate, Glucose, Arctostaphylos Uva-Ursi Leaf Extract, Butylene Glycol, Calendula Officinalis Flower Extract, Papain, Potassium Sorbate, Sodium Benzoate, Rosa Roxburghii Fruit Extract"</t>
+          <t>"Aloe Barbadensis Leaf Water, Water, Butylene Glycol, Glycerin, Dipropylene Glycol, Pentylene Glycol, 1,2-Hexanediol, Aloe Barbadensis Leaf Juice, Sodium Hyaluronate, Portulaca Oleracea Extract, Psidium Guajava Fruit Extract, Aspalathus Linearis Extract, Cynanchum Atratum Extract, Salicylic Acid, Perilla Ocymoides Leaf Extract, Schisandra Chinensis Fruit Extract, Acorus Calamus Root Extract, Aloe Barbadensis Leaf Extract, Althaea Rosea Root Extract, Polyglutamic Acid, Beta-Glucan, Arginine, Allantoin, Citrus Paradisi (Grapefruit) Fruit Extract, Caprylyl Glycol, C12-14 Pareth-12, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Xanthan Gum"</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -9957,23 +9954,23 @@
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>150000</v>
+        <v>154000</v>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/ac95a6c8-7cb5-4799-a423-749b4281787c/products/elsheskin-exfolicare-solution-toner/elsheskin-exfolicare-solution-toner_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/f4f74e87-a35a-4621-ae0a-dcbed8141303/products/benton-aloe-bha-skin-toner-9/benton-aloe-bha-skin-toner-9_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G266" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3qKj1ci5qs</t>
+          <t>https://s.shopee.co.id/9AMFNYC29j</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>Benton Aloe BHA Skin Toner</t>
+          <t>Whitelab Peeling Serum AHA BHA PHA</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -9983,7 +9980,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>"Aloe Barbadensis Leaf Water, Water, Butylene Glycol, Glycerin, Dipropylene Glycol, Pentylene Glycol, 1,2-Hexanediol, Aloe Barbadensis Leaf Juice, Sodium Hyaluronate, Portulaca Oleracea Extract, Psidium Guajava Fruit Extract, Aspalathus Linearis Extract, Cynanchum Atratum Extract, Salicylic Acid, Perilla Ocymoides Leaf Extract, Schisandra Chinensis Fruit Extract, Acorus Calamus Root Extract, Aloe Barbadensis Leaf Extract, Althaea Rosea Root Extract, Polyglutamic Acid, Beta-Glucan, Arginine, Allantoin, Citrus Paradisi (Grapefruit) Fruit Extract, Caprylyl Glycol, C12-14 Pareth-12, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Xanthan Gum"</t>
+          <t>"Aqua, Butylene Glycol, Mandelic Acid (5%), Ethyl Alcohol, Niacinamide (2%), Salicylic Acid (2%), Lactobionic Acid (2%), Glycerin, Glycyrrhiza Glabra Root Extract, PEG-40 Hydrogenated Castor Oil, Dipotassium Glycyrrhizate, Allantoin, Xanthan Gum, Parfum"</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -9992,23 +9989,23 @@
         </is>
       </c>
       <c r="E267" s="3" t="n">
-        <v>154000</v>
+        <v>77000</v>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/f4f74e87-a35a-4621-ae0a-dcbed8141303/products/benton-aloe-bha-skin-toner-9/benton-aloe-bha-skin-toner-9_front_photo_300x300@2x.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0i-mcsrfxcao8jbe0@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G267" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9AMFNYC29j</t>
+          <t>https://s.shopee.co.id/6AidoNEQCw</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>The Originote Peeling Solution</t>
+          <t>Implora Peeling Serum</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -10018,7 +10015,8 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycolic Acid, Sodium Hydroxide, Pentylene Glycol, Gluconolactone, Glycerin, Propanediol, Xanthan Gum, 1,2-Hexanediol, Salicylic Acid, Acacia Senegal Gum, C12-14 Alketh-12, Caprylyl Glycol, Hydrolyzed Gardenia Florida Extract, Maltodextrin, Ethylhexylglycerin, Sodium Phytate, Butylene Glycol, Centella Asiatica Extract, Glycine, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Serine, Glutamic Acid, Glycyrrhiza Glabra (Licorice) Root Extract, Camellia Sinensis Leaf Extract, Aspartic Acid, Leucine, Rosmarinus Officinalis (Rosemary) Leaf Extract, Chamomilla Recutita (Matricaria) Flower Extract, Alanine, Lysine, Arginine, Tyrosine, Phenylalanine, Valine, Threonine, Proline, Isoleucine, Tocopherol, Histidine, Methionine, Cysteine"</t>
+          <t>"Aqua, Butylene Glycol, Propylene Glycol, Glycolic Acid, Glycerin, Succinic Acid, Silanediol Salicylate, Ethoxydiglycol, PEG-40 Hydrogenated Castor Oil, Trideceth-9, Sodium Lactate, Sodium PCA, Hydroxypropyl Methylcellulose, DMDM Hydantoin, Glycyrrhiza Glabra Root Extract, Triethanolamine, Sodium Hydroxide, Tetrasodium EDTA, Iodopropynyl Butylcarbamate, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Urea, Glabridin, Benzoic Acid, Sodium Benzoate, Sodium Methylparaben, Sodium Chloride, Terry-Dry Freeze Dried Or Spray Dried Aloe Vera Powders, Propylparaben
+May Contain: Ci 14720, Ci 15985, Ci 42090"</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -10027,23 +10025,23 @@
         </is>
       </c>
       <c r="E268" s="3" t="n">
-        <v>48000</v>
+        <v>24000</v>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/64372bbb-a3c1-4f27-84eb-8e1bd61e113b/products/the-originote-b5-peeling-solution/the-originote-b5-peeling-solution_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/26eb5af8-cec1-4862-8869-d55a1ba817a1/products/implora-peeling-serum/implora-peeling-serum_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/2g8ldjXGwV</t>
+          <t>https://s.shopee.co.id/60PDcByYZq</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>Whitelab Peeling Serum AHA BHA PHA</t>
+          <t>Hanasui Power Peeling Serum</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -10053,7 +10051,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Mandelic Acid (5%), Ethyl Alcohol, Niacinamide (2%), Salicylic Acid (2%), Lactobionic Acid (2%), Glycerin, Glycyrrhiza Glabra Root Extract, PEG-40 Hydrogenated Castor Oil, Dipotassium Glycyrrhizate, Allantoin, Xanthan Gum, Parfum"</t>
+          <t>"Aqua, Lactic Acid, Glycerin, Gluconolactone, Butylene Glycol, Glycolic Acid, Mandelic Acid, Pentylene Glycol, Succinic Acid, Salicylic Acid, Sodium Hydroxide, Phenoxyethanol, Tranexamic Acid, Xanthan Gum, Vaccinium Myrtillus (Bilberry) Fruit Extract, Allantoin, Panthenol, Sodium Hyaluronate, Arginine, Propylene Glycol, Saccharum Officinarum (Sugar Cane) Extract, Disodium EDTA, Aloe Barbadensis Extract, Centella Asiatica (Cica) Leaf Extract, Triethylene Glycol, Citrus Aurantium Dulcis (Orange) Fruit Extract, Citrus Limon (Lemon) Fruit Extract, Acer Saccharum (Sugar Maple) Extract, Artemisia Vulgaris (Mugwort) Extract, Citric Acid, Potassium Sorbate, Sodium Benzoate"</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -10062,23 +10060,23 @@
         </is>
       </c>
       <c r="E269" s="3" t="n">
-        <v>77000</v>
+        <v>28000</v>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0i-mcsrfxcao8jbe0@resize_w900_nl.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/a766fde6-6f0f-4dfb-8a50-a9780f57f66a/products/hanasui-power-peeling-serum/hanasui-power-peeling-serum_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G269" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/6AidoNEQCw</t>
+          <t>https://s.shopee.co.id/5fmNDlLuyo</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>Implora Peeling Serum</t>
+          <t>Scarlett Whitening Peeling So Good</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -10088,33 +10086,32 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Propylene Glycol, Glycolic Acid, Glycerin, Succinic Acid, Silanediol Salicylate, Ethoxydiglycol, PEG-40 Hydrogenated Castor Oil, Trideceth-9, Sodium Lactate, Sodium PCA, Hydroxypropyl Methylcellulose, DMDM Hydantoin, Glycyrrhiza Glabra Root Extract, Triethanolamine, Sodium Hydroxide, Tetrasodium EDTA, Iodopropynyl Butylcarbamate, Fructose, Glycine, Inositol, Lactic Acid, Niacinamide, Urea, Glabridin, Benzoic Acid, Sodium Benzoate, Sodium Methylparaben, Sodium Chloride, Terry-Dry Freeze Dried Or Spray Dried Aloe Vera Powders, Propylparaben
-May Contain: Ci 14720, Ci 15985, Ci 42090"</t>
+          <t>"Aqua, Glyserin, Gluconolactone, Succinic Acid, Behentrimonium Chloride, Galactomyces Ferment Filtrate, Phenoxyethanol, Aloe Barbadensis Leaf Water, Centella Asiatica Extract, Lactic Acid, Cetrimonium Chloride, Allantoin, Aloe Barbadensis Leaf Extract, Isopropyl Alcohol, Vaccinium Myrtillus Fruit Extract, DMDM Hydantoin, Ethylhexylglycerin, Saccharum Officinarum (Sugar Cane) Extract, 1,2-Hexanediol, Pentylene Glycol, Butylene Glycol, Citrus Aurantium Dulcis Fruit Extract, Citrus Limon Fruit Extract, Glyceryl Acrylate/​Acrylic Acid Copolymer, Acer Saccharum (Sugar Maple) Extract, Pvm/​Ma Copolymer"</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E270" s="3" t="n">
-        <v>24000</v>
+        <v>75000</v>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/26eb5af8-cec1-4862-8869-d55a1ba817a1/products/implora-peeling-serum/implora-peeling-serum_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/6c469271-1e69-4dd3-8e07-6af9994ff22f/products/scarlett-peeling-so-good-brightening-peeling-gel/scarlett-peeling-so-good-brightening-peeling-gel_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/60PDcByYZq</t>
+          <t>https://s.shopee.co.id/3qKj2VZYaE</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>Hanasui Power Peeling Serum</t>
+          <t>Azarine AHA-BHA-PHA Peeling Serum</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -10124,7 +10121,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Lactic Acid, Glycerin, Gluconolactone, Butylene Glycol, Glycolic Acid, Mandelic Acid, Pentylene Glycol, Succinic Acid, Salicylic Acid, Sodium Hydroxide, Phenoxyethanol, Tranexamic Acid, Xanthan Gum, Vaccinium Myrtillus (Bilberry) Fruit Extract, Allantoin, Panthenol, Sodium Hyaluronate, Arginine, Propylene Glycol, Saccharum Officinarum (Sugar Cane) Extract, Disodium EDTA, Aloe Barbadensis Extract, Centella Asiatica (Cica) Leaf Extract, Triethylene Glycol, Citrus Aurantium Dulcis (Orange) Fruit Extract, Citrus Limon (Lemon) Fruit Extract, Acer Saccharum (Sugar Maple) Extract, Artemisia Vulgaris (Mugwort) Extract, Citric Acid, Potassium Sorbate, Sodium Benzoate"</t>
+          <t>"Aqua, Glycolic Acid, Lactic Acid, Mandelic Acid, Salicylic Acid, Portulaca Oleracea Extract, Carica Papaya Fruit Extract, Sodium Hyaluronate, Lactobionic Acid, Aloe Barbadensis Leaf Juice, Allantoin, Royal Jelly, Chlorphenesin, Phenoxyethanol, Xanthan Gum, Gluconobacter/​Honey Ferment Filtrate"</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -10133,23 +10130,23 @@
         </is>
       </c>
       <c r="E271" s="3" t="n">
-        <v>28000</v>
+        <v>48000</v>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/a766fde6-6f0f-4dfb-8a50-a9780f57f66a/products/hanasui-power-peeling-serum/hanasui-power-peeling-serum_front_photo_300x300@2x.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/024941f1-5b19-4826-a343-0db198b0572b/products/azarine-aha-bha-pha-peeling-serum-marvel-edition/azarine-aha-bha-pha-peeling-serum-marvel-edition_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/5fmNDlLuyo</t>
+          <t>https://s.shopee.co.id/7fXRbe0nsA</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>Scarlett Whitening Peeling So Good</t>
+          <t>WARDAH Lightening Gentle Exfoliator</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -10159,32 +10156,32 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glyserin, Gluconolactone, Succinic Acid, Behentrimonium Chloride, Galactomyces Ferment Filtrate, Phenoxyethanol, Aloe Barbadensis Leaf Water, Centella Asiatica Extract, Lactic Acid, Cetrimonium Chloride, Allantoin, Aloe Barbadensis Leaf Extract, Isopropyl Alcohol, Vaccinium Myrtillus Fruit Extract, DMDM Hydantoin, Ethylhexylglycerin, Saccharum Officinarum (Sugar Cane) Extract, 1,2-Hexanediol, Pentylene Glycol, Butylene Glycol, Citrus Aurantium Dulcis Fruit Extract, Citrus Limon Fruit Extract, Glyceryl Acrylate/​Acrylic Acid Copolymer, Acer Saccharum (Sugar Maple) Extract, Pvm/​Ma Copolymer"</t>
+          <t>"Aqua, Sodium Laureth Sulfate, Niacinamide, PEG-3 Distearate, Hydrated Silica, Glycerin, Acrylates Copolymer, Hydroxyethylcellulose, Cocamidopropyl Betaine, Phenoxyethanol, Sodium Lauroyl Sarcosinate, Sodium Chloride, Ethylhexylglycerin, Fragrance, Sodium Nitrate, Citric Acid, Propylene Glycol, Disodium Phosphate, Polysorbate 60, Glycyrrhiza Glabra (Root) Extract, Sodium Phosphate, Ci 74160"</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Scrub</t>
         </is>
       </c>
       <c r="E272" s="3" t="n">
-        <v>75000</v>
+        <v>27000</v>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/6c469271-1e69-4dd3-8e07-6af9994ff22f/products/scarlett-peeling-so-good-brightening-peeling-gel/scarlett-peeling-so-good-brightening-peeling-gel_front_photo_300x300@2x.webp</t>
+          <t>https://down-id.img.susercontent.com/file/sg-11134201-7rbmf-m5jluo6zzdmo5c@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3qKj2VZYaE</t>
+          <t>https://s.shopee.co.id/3Vhse4OkeO</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>Azarine AHA-BHA-PHA Peeling Serum</t>
+          <t>Emina 2 in 1 Scrub Mask</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -10194,32 +10191,32 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycolic Acid, Lactic Acid, Mandelic Acid, Salicylic Acid, Portulaca Oleracea Extract, Carica Papaya Fruit Extract, Sodium Hyaluronate, Lactobionic Acid, Aloe Barbadensis Leaf Juice, Allantoin, Royal Jelly, Chlorphenesin, Phenoxyethanol, Xanthan Gum, Gluconobacter/​Honey Ferment Filtrate"</t>
+          <t>"Aqua, Propanediol, Glycerin, Kaolin, Dipropylene Glycol, Hydrated Silica, Glycereth-26, Juglans Regia (Walnut) Shell Powder, Sodium Polyacrylate, Phenoxyethanol, Silica, Xanthan Gum, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Chlorphenesin, Sodium Hydroxide, Vaccinium Myrtillus Fruit Extract, Carbomer, Disodium EDTA, Saccharum Officinarum (Sugar Cane) Extract, Butylene Glycol, Citrus Aurantium Dulcis (Orange) Fruit Extract, Citrus Limon (Lemon) Fruit Extract, Acer Saccharum (Sugar Maple) Extract, Actinidia Polygama Fruit Extract"</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Scrub</t>
         </is>
       </c>
       <c r="E273" s="3" t="n">
-        <v>48000</v>
+        <v>49000</v>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/024941f1-5b19-4826-a343-0db198b0572b/products/azarine-aha-bha-pha-peeling-serum-marvel-edition/azarine-aha-bha-pha-peeling-serum-marvel-edition_front_photo_300x300@2x.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7qukw-lfkj5vocci1uf9@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/7fXRbe0nsA</t>
+          <t>https://s.shopee.co.id/8pjOzuuMrx</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>WARDAH Lightening Gentle Exfoliator</t>
+          <t>Himalaya Purifying Neem Scrub</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -10229,7 +10226,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Sodium Laureth Sulfate, Niacinamide, PEG-3 Distearate, Hydrated Silica, Glycerin, Acrylates Copolymer, Hydroxyethylcellulose, Cocamidopropyl Betaine, Phenoxyethanol, Sodium Lauroyl Sarcosinate, Sodium Chloride, Ethylhexylglycerin, Fragrance, Sodium Nitrate, Citric Acid, Propylene Glycol, Disodium Phosphate, Polysorbate 60, Glycyrrhiza Glabra (Root) Extract, Sodium Phosphate, Ci 74160"</t>
+          <t>"Aqua, Stearic Acid, Caprylic/​Capric Triglyceride, Cetyl Alcohol, Crystalline Cellulose, Sorbitan, Sorbitan Stearate, Sucrose Cocoate, Ethanol, Ethylhexylglycerin, Fragrance, Carbomer, Prunus Armeniaca (Apricot) Seed Powder, Sodium Hydroxide, Benzyl Alcohol, Tocopheryl Acetate, Disodium EDTA, Melia Azadirachta Leaf Extract, Curcuma Longa Root Extract, Ci 77891, Ci 77289, Ci 7749"</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -10238,23 +10235,23 @@
         </is>
       </c>
       <c r="E274" s="3" t="n">
-        <v>27000</v>
+        <v>25000</v>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/sg-11134201-7rbmf-m5jluo6zzdmo5c@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztp-mfjics7tx1qk5e@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3Vhse4OkeO</t>
+          <t>https://s.shopee.co.id/2g8leeIlu6</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>Emina 2 in 1 Scrub Mask</t>
+          <t>Safi White Expert Deep Exfoliator</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -10264,7 +10261,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Propanediol, Glycerin, Kaolin, Dipropylene Glycol, Hydrated Silica, Glycereth-26, Juglans Regia (Walnut) Shell Powder, Sodium Polyacrylate, Phenoxyethanol, Silica, Xanthan Gum, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Chlorphenesin, Sodium Hydroxide, Vaccinium Myrtillus Fruit Extract, Carbomer, Disodium EDTA, Saccharum Officinarum (Sugar Cane) Extract, Butylene Glycol, Citrus Aurantium Dulcis (Orange) Fruit Extract, Citrus Limon (Lemon) Fruit Extract, Acer Saccharum (Sugar Maple) Extract, Actinidia Polygama Fruit Extract"</t>
+          <t>"Aqua, Glyceryl Stearate, Glycerin, Caprylic/​Capric Triglyceride, Olea Europaea Oil Unsaponifiables, Sodium Cocoamphoacetate, Stearic Acid, PEG-100 Stearate, Prunus Armeniaca Seed Powder, Olive Oil PEG-7 Esters, Carbomer, Aminomethyl Propanol, Tetrasodium EDTA, Fragrance, Nigella Sativa Seed Oil, Perfluorodecalin, 4-Butylresorcinol, Phenoxyethanol, Methylparaben"</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -10273,23 +10270,23 @@
         </is>
       </c>
       <c r="E275" s="3" t="n">
-        <v>49000</v>
-      </c>
-      <c r="F275" s="4" t="inlineStr">
-        <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7qukw-lfkj5vocci1uf9@resize_w900_nl.webp</t>
+        <v>44000</v>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>52ca8a22a65c35ad727b000d0548346e@resize_w900_nl.webp (900×900)</t>
         </is>
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8pjOzuuMrx</t>
+          <t>https://s.shopee.co.id/80AI0VFTRL</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>Himalaya Purifying Neem Scrub</t>
+          <t>Herborist Juice for Skin Face Scrub</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -10299,7 +10296,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Stearic Acid, Caprylic/​Capric Triglyceride, Cetyl Alcohol, Crystalline Cellulose, Sorbitan, Sorbitan Stearate, Sucrose Cocoate, Ethanol, Ethylhexylglycerin, Fragrance, Carbomer, Prunus Armeniaca (Apricot) Seed Powder, Sodium Hydroxide, Benzyl Alcohol, Tocopheryl Acetate, Disodium EDTA, Melia Azadirachta Leaf Extract, Curcuma Longa Root Extract, Ci 77891, Ci 77289, Ci 7749"</t>
+          <t>"Aqua, Cetyl Alcohol, Corn (Zea Mays) Starch, Glycerin, Cetearyl Alcohol, Glyceryl Stearate, Isopropyl Myristate, Olive (Olea Europaea) Oil, Silica, Sodium Laureth Sulfate, PEG-100 Stearate, Juglans Regia Shell Powder, Phenoxyethanol, Synthetic Wax, Triethanolamine, Salicylic Acid, Allantoin, Perfume, Disodium EDTA, Tocopheryl Acetate, Avena Sativa Kernel Extract, Pyrus Malus Fruit Extract, Propylene Glycol, Brassica Oleracea Italica Extract, DMDM Hydantoin"</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -10308,23 +10305,23 @@
         </is>
       </c>
       <c r="E276" s="3" t="n">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztp-mfjics7tx1qk5e@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134201-7rasg-m20oe7w5pvd513@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/2g8leeIlu6</t>
+          <t>https://s.shopee.co.id/4LGzdshrNr</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>Safi White Expert Deep Exfoliator</t>
+          <t>Viva Queen Peeling Cream</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -10334,32 +10331,33 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glyceryl Stearate, Glycerin, Caprylic/​Capric Triglyceride, Olea Europaea Oil Unsaponifiables, Sodium Cocoamphoacetate, Stearic Acid, PEG-100 Stearate, Prunus Armeniaca Seed Powder, Olive Oil PEG-7 Esters, Carbomer, Aminomethyl Propanol, Tetrasodium EDTA, Fragrance, Nigella Sativa Seed Oil, Perfluorodecalin, 4-Butylresorcinol, Phenoxyethanol, Methylparaben"</t>
+          <t>"Aqua, Synthetic Wax, Cetearyl Alcohol, Mineral Oil, Propylene Glycol, Ceteareth-20, Parfum, Methylparaben, Propylparaben, BHT"</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>Scrub</t>
+          <t>krim</t>
         </is>
       </c>
       <c r="E277" s="3" t="n">
-        <v>44000</v>
-      </c>
-      <c r="F277" s="3" t="inlineStr">
-        <is>
-          <t>52ca8a22a65c35ad727b000d0548346e@resize_w900_nl.webp (900×900)</t>
+        <v>9000</v>
+      </c>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r992-lxm8z5ejxqx9c3.webp</t>
         </is>
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/80AI0VFTRL</t>
+          <t>https://s.shopee.co.id/7KubDSDDzF</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>Herborist Juice for Skin Face Scrub</t>
+          <t>Eiem Beauty
+Full Acid Exfoliating Solution</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -10369,32 +10367,33 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Cetyl Alcohol, Corn (Zea Mays) Starch, Glycerin, Cetearyl Alcohol, Glyceryl Stearate, Isopropyl Myristate, Olive (Olea Europaea) Oil, Silica, Sodium Laureth Sulfate, PEG-100 Stearate, Juglans Regia Shell Powder, Phenoxyethanol, Synthetic Wax, Triethanolamine, Salicylic Acid, Allantoin, Perfume, Disodium EDTA, Tocopheryl Acetate, Avena Sativa Kernel Extract, Pyrus Malus Fruit Extract, Propylene Glycol, Brassica Oleracea Italica Extract, DMDM Hydantoin"</t>
+          <t>"Water, Propylene Glycol, Lactic Acid, Glycolic Acid, Potassium Hydroxide, Salicylic Acid, Sodium Citrate, Triethanolamine, Citric Acid, Gluconolactone, Mandelic Acid, Capryloyl Salicylic Acid, Camellia Sinensis Leaf Extract, Propanediol, Aloe Barbadensis Leaf Juice, Phenoxyethanol, Potassium Sorbate, Bisabolol, Sodium PCA, Mel (Honey), Urea, Fructose, Glucose, Centella Asiatica Extract, Pentylene Glycol, Acetyl Glucosamine, Glucuronolactone, Glycine, Sodium Carboxymethyl Cellulose, Lysine Hydrochloride, Ci 16035, Xanthan Gum, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Glycyrrhiza Glabra (Licorice) Root Extract, Ci 27755, Chamomilla Recutita (Matricaria) Flower Extract, Maltodextrin, Rosmarinus Officinalis (Rosemary) Leaf Extract, Hydrolyzed Collagen, 1,2-Hexanediol, Parfum, Sodium Benzoate, Caprylyl Glycol, Tropolone, Ethylhexylglycerin, Tetrasodium EDTA"</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Scrub</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E278" s="3" t="n">
-        <v>23000</v>
+        <v>39000</v>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134201-7rasg-m20oe7w5pvd513@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk0-m86i4fk8plq0bd@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4LGzdshrNr</t>
+          <t>https://s.shopee.co.id/4qDGEuemLm</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>Viva Queen Peeling Cream</t>
+          <t>Hanasui
+Advance Exfoliating Serum</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -10404,33 +10403,33 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Synthetic Wax, Cetearyl Alcohol, Mineral Oil, Propylene Glycol, Ceteareth-20, Parfum, Methylparaben, Propylparaben, BHT"</t>
+          <t>"Aqua, Butylene Glycol, Glycerin, Acetyl Glycyl Beta-Alanine, Gluconolactone, Glycolic Acid, Lactic Acid, Biosaccharide Gum-1, Succinic Acid, Phenoxyethanol, Methyl Gluceth-20, Sodium Hydroxide, Tranexamic Acid, Xanthan Gum, Panthenol, Carbomer, PEG-40 Hydrogenated Castor Oil, Vaccinium Myrtillus Fruit Extract, Allantoin, Disodium EDTA, Tocopheryl Acetate, Arginine, Triethylene Glycol, Saccharum Officinarum (Sugar Cane) Extract, Citrus Aurantium Dulcis (Orange) Fruit Extract, Citrus Limon (Lemon) Fruit Extract, Formic Acid, 1,2-Hexanediol, Acer Saccharum (Sugar Maple) Extract, Sodium Hyaluronate, Niacinamide, Arachis Hypogaea (Peanut) Oil, Ascorbic Acid, Biotin, Folic Acid, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Hyaluronate Na, Hydroxypropyltrimonium, Pentylene Glycol, Potassium Hyaluronate, Pyridoxine Hcl, Retinyl Palmitate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate Crosspolymer, Tocopherol"</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>krim</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E279" s="3" t="n">
-        <v>9000</v>
+        <v>33000</v>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r992-lxm8z5ejxqx9c3.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk8-m7vphjhlreisbe@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/7KubDSDDzF</t>
+          <t>https://s.shopee.co.id/8fPyo3R8AL</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>Eiem Beauty
-Full Acid Exfoliating Solution</t>
+          <t>ELFormula
+Intensive Peeling Solution</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -10440,7 +10439,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>"Water, Propylene Glycol, Lactic Acid, Glycolic Acid, Potassium Hydroxide, Salicylic Acid, Sodium Citrate, Triethanolamine, Citric Acid, Gluconolactone, Mandelic Acid, Capryloyl Salicylic Acid, Camellia Sinensis Leaf Extract, Propanediol, Aloe Barbadensis Leaf Juice, Phenoxyethanol, Potassium Sorbate, Bisabolol, Sodium PCA, Mel (Honey), Urea, Fructose, Glucose, Centella Asiatica Extract, Pentylene Glycol, Acetyl Glucosamine, Glucuronolactone, Glycine, Sodium Carboxymethyl Cellulose, Lysine Hydrochloride, Ci 16035, Xanthan Gum, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Glycyrrhiza Glabra (Licorice) Root Extract, Ci 27755, Chamomilla Recutita (Matricaria) Flower Extract, Maltodextrin, Rosmarinus Officinalis (Rosemary) Leaf Extract, Hydrolyzed Collagen, 1,2-Hexanediol, Parfum, Sodium Benzoate, Caprylyl Glycol, Tropolone, Ethylhexylglycerin, Tetrasodium EDTA"</t>
+          <t>"Water, Glycolic Acid, Sodium Hydroxide, Pentylene Glycol, Gluconolactone, Glycerin, Propanediol, Xanthan Gum, 1,2-Hexanediol, Salicylic Acid, Acacia Senegal Gum, C12-14 Alketh-12, Caprylyl Glycol, Hydrolyzed Gardenia Florida Extract, Maltodextrin, Ethylhexylglycerin, Sodium Phytate, Butylene Glycol, Centella Asiatica Extract, Glycine, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Serine, Glutamic Acid, Glycyrrhiza Glabra (Licorice) Root Extract, Camellia Sinensis Leaf Extract, Aspartic Acid, Leucine, Rosmarinus Officinalis (Rosemary) Leaf Extract, Chamomilla Recutita (Matricaria) Flower Extract, Alanine, Lysine, Arginine, Tyrosine, Phenylalanine, Valine, Threonine, Proline, Isoleucine, Tocopherol, Histidine, Methionine, Cysteine"</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -10449,70 +10448,68 @@
         </is>
       </c>
       <c r="E280" s="3" t="n">
-        <v>39000</v>
+        <v>91000</v>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk0-m86i4fk8plq0bd@resize_w900_nl.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztl-mf1eoja1cdfueb@resize_w900_nl.webp</t>
         </is>
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4qDGEuemLm</t>
+          <t>https://s.shopee.co.id/9fIVzwIKZE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>Hanasui
-Advance Exfoliating Serum</t>
+          <t>Kahf Gentle Facial Wash</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Facial Wash</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Glycerin, Acetyl Glycyl Beta-Alanine, Gluconolactone, Glycolic Acid, Lactic Acid, Biosaccharide Gum-1, Succinic Acid, Phenoxyethanol, Methyl Gluceth-20, Sodium Hydroxide, Tranexamic Acid, Xanthan Gum, Panthenol, Carbomer, PEG-40 Hydrogenated Castor Oil, Vaccinium Myrtillus Fruit Extract, Allantoin, Disodium EDTA, Tocopheryl Acetate, Arginine, Triethylene Glycol, Saccharum Officinarum (Sugar Cane) Extract, Citrus Aurantium Dulcis (Orange) Fruit Extract, Citrus Limon (Lemon) Fruit Extract, Formic Acid, 1,2-Hexanediol, Acer Saccharum (Sugar Maple) Extract, Sodium Hyaluronate, Niacinamide, Arachis Hypogaea (Peanut) Oil, Ascorbic Acid, Biotin, Folic Acid, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Hyaluronate Na, Hydroxypropyltrimonium, Pentylene Glycol, Potassium Hyaluronate, Pyridoxine Hcl, Retinyl Palmitate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate Crosspolymer, Tocopherol"</t>
+          <t>"Aqua, Glycerin, Myristic Acid, Potassium Hydroxide, Stearic Acid, Butylene Glycol, Lauric Acid, Glyceryl Stearate, PEG-3 Distearate, Decyl Glucoside, Phenoxyethanol, Saccharide Isomerate, Potassium Cocoyl Glycinate, Kaolin, Niacinamide, Fragrance, Menthol, Potassium Cocoate, Allantoin, Disodium EDTA, Hydroxypropyl Methylcellulose, Ethylhexylglycerin, Menthyl Lactate, PEG-40 Hydrogenated Castor Oil, PPG-26-Buteth-26, Propylene Glycol, Citric Acid, Mentha Viridis (Spearmint) Leaf Extract, Sodium Citrate, Citrus Grandis (Grapefruit) Fruit Extract"</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="E281" s="3" t="n">
-        <v>33000</v>
+        <v>38000</v>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk8-m7vphjhlreisbe@resize_w900_nl.webp</t>
+          <t>https://incidecoder-content.storage.googleapis.com/b4e54a5a-2f70-4321-abed-a3653153999b/products/kahf-skin-energizing-and-brightening-face-wash/kahf-skin-energizing-and-brightening-face-wash_front_photo_300x300@2x.webp</t>
         </is>
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8fPyo3R8AL</t>
+          <t>https://shopee.co.id/-READY-Kahf-Facewash-Gentle-Exfoliating-series-men-sabun-cuci-muka-kahf-50ml-100ml-i.1035888002.29129907683?extraParams=%7B%22display_model_id%22%3A177239579779%2C%22model_selection_logic%22%3A3%7D&amp;sp_atk=a5d1cccf-5195-4c7e-8966-1f9ca43b23d3&amp;xptdk=a5d1cccf-5195-4c7e-8966-1f9ca43b23d3</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>ELFormula
-Intensive Peeling Solution</t>
+          <t>Glow fx Beauty Serum Glow Bomb</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycolic Acid, Sodium Hydroxide, Pentylene Glycol, Gluconolactone, Glycerin, Propanediol, Xanthan Gum, 1,2-Hexanediol, Salicylic Acid, Acacia Senegal Gum, C12-14 Alketh-12, Caprylyl Glycol, Hydrolyzed Gardenia Florida Extract, Maltodextrin, Ethylhexylglycerin, Sodium Phytate, Butylene Glycol, Centella Asiatica Extract, Glycine, Polygonum Cuspidatum Root Extract, Scutellaria Baicalensis Root Extract, Serine, Glutamic Acid, Glycyrrhiza Glabra (Licorice) Root Extract, Camellia Sinensis Leaf Extract, Aspartic Acid, Leucine, Rosmarinus Officinalis (Rosemary) Leaf Extract, Chamomilla Recutita (Matricaria) Flower Extract, Alanine, Lysine, Arginine, Tyrosine, Phenylalanine, Valine, Threonine, Proline, Isoleucine, Tocopherol, Histidine, Methionine, Cysteine"</t>
+          <t>"Air, Niasinamida (8%), Butilena GlikolEkstrak Akar Glycyrrhiza Uralensis (6% ) , Siklopentasiloksan, Alpha-Arbutin (3%)Asam Traneksamat ( 2%)Digliserin​Dimetikon​, Ekstrak Bunga Anthemis Nobilis, Tokoferil Asetat, Pati Jagung TerhidrolisisEkstrak Akar Beta Vulgaris , GliserinFenoksietanol​, Aluminium Pati Oktensuksinat, Amonium Poliakriloildimetil TauratPoliakrilamida​, Asetil Glisil Beta-Alanin, Allantoin, Kalium Glisirizinat, C13-14 IsoparafinAsam Glikolat Asam Laktat Metilpropanediol​Klorfenesin​Asam Poliglutamat Ekstrak Daun Camellia Sinensis Asam Laurik Natrium Magnesium SilikatAsam Sitrat , Dinatrium EDTA, Laureth-7, Asam Difosfonat Alkohol Lauril , 1,2-Heksanediol, SiklotetrasiloksanEkstrak Cystoseira TamariscIfolia, Xanthan GumNatrium HialuronatAsam P -AnisatAsam Hialuronat Asam Hialuronat Terhidrolisis , Natrium Hialuronat TerhidrolisisHidroksipropiltrimonium Hialuronat , Pentilen GlikolKalium Hialuronat , Natrium Asetilasi Hialuronat, Sodium Hyaluronate Crosspolymer"</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -10521,163 +10518,163 @@
         </is>
       </c>
       <c r="E282" s="3" t="n">
-        <v>91000</v>
+        <v>64000</v>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-81ztl-mf1eoja1cdfueb@resize_w900_nl.webp</t>
+          <t>https://down-bs-id.img.susercontent.com/id-11134207-822wt-mowb2pe08feqea.webp</t>
         </is>
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9fIVzwIKZE</t>
+          <t>https://s.shopee.co.id/6febZZW6Bn</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>Kahf Gentle Facial Wash</t>
+          <t>Wardah Sunscreen UV Shield Acne Calming Serum SPF 35 PA++++</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>Facial Wash</t>
+          <t>Sunscreen</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Myristic Acid, Potassium Hydroxide, Stearic Acid, Butylene Glycol, Lauric Acid, Glyceryl Stearate, PEG-3 Distearate, Decyl Glucoside, Phenoxyethanol, Saccharide Isomerate, Potassium Cocoyl Glycinate, Kaolin, Niacinamide, Fragrance, Menthol, Potassium Cocoate, Allantoin, Disodium EDTA, Hydroxypropyl Methylcellulose, Ethylhexylglycerin, Menthyl Lactate, PEG-40 Hydrogenated Castor Oil, PPG-26-Buteth-26, Propylene Glycol, Citric Acid, Mentha Viridis (Spearmint) Leaf Extract, Sodium Citrate, Citrus Grandis (Grapefruit) Fruit Extract"</t>
+          <t>Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Butyl Methoxydibenzoylmethane, Aluminium Starch Octenylsuccinate, Phenoxyethanol, Cetearyl Olivate, Propanediol, Butylene Glycol, Octocrylene, Acrylates C10-30 Alkyl Acrylate Crosspolymer, Sorbitan Olivate, Polymethyl Methacrylate, Aminomethyl Propanol, Allantoin, Salicylic Acid, Xanthan Gum, Triethylene Glycol, Ethylhexyl Triazone, Tetrasodium EDTA, Lecithin, BHT</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E283" s="3" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>https://incidecoder-content.storage.googleapis.com/b4e54a5a-2f70-4321-abed-a3653153999b/products/kahf-skin-energizing-and-brightening-face-wash/kahf-skin-energizing-and-brightening-face-wash_front_photo_300x300@2x.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-8224p-mi9jj64a2ubk0e.webp</t>
         </is>
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>https://shopee.co.id/-READY-Kahf-Facewash-Gentle-Exfoliating-series-men-sabun-cuci-muka-kahf-50ml-100ml-i.1035888002.29129907683?extraParams=%7B%22display_model_id%22%3A177239579779%2C%22model_selection_logic%22%3A3%7D&amp;sp_atk=a5d1cccf-5195-4c7e-8966-1f9ca43b23d3&amp;xptdk=a5d1cccf-5195-4c7e-8966-1f9ca43b23d3</t>
+          <t>https://s.shopee.co.id/3g1Ir3jiXg</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>Glow fx Beauty Serum Glow Bomb</t>
+          <t xml:space="preserve">SCARLETT Acne Peace Daily Sunscreen SPF 35 PA++++ </t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>Sunscreen</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>"Air, Niasinamida (8%), Butilena GlikolEkstrak Akar Glycyrrhiza Uralensis (6% ) , Siklopentasiloksan, Alpha-Arbutin (3%)Asam Traneksamat ( 2%)Digliserin​Dimetikon​, Ekstrak Bunga Anthemis Nobilis, Tokoferil Asetat, Pati Jagung TerhidrolisisEkstrak Akar Beta Vulgaris , GliserinFenoksietanol​, Aluminium Pati Oktensuksinat, Amonium Poliakriloildimetil TauratPoliakrilamida​, Asetil Glisil Beta-Alanin, Allantoin, Kalium Glisirizinat, C13-14 IsoparafinAsam Glikolat Asam Laktat Metilpropanediol​Klorfenesin​Asam Poliglutamat Ekstrak Daun Camellia Sinensis Asam Laurik Natrium Magnesium SilikatAsam Sitrat , Dinatrium EDTA, Laureth-7, Asam Difosfonat Alkohol Lauril , 1,2-Heksanediol, SiklotetrasiloksanEkstrak Cystoseira TamariscIfolia, Xanthan GumNatrium HialuronatAsam P -AnisatAsam Hialuronat Asam Hialuronat Terhidrolisis , Natrium Hialuronat TerhidrolisisHidroksipropiltrimonium Hialuronat , Pentilen GlikolKalium Hialuronat , Natrium Asetilasi Hialuronat, Sodium Hyaluronate Crosspolymer"</t>
+          <t>Aqua, Ethylhexyl Methoxycinnamate, Butyl Methoxydibenzoylmethane, Glycerin, Octocrylene, Centella Asiatica Extract, Methyl Methacrylate Crosspolymer, Aluminum Starch Octenylsuccinate, Propanediol, Allantoin, Aloe Barbadensis Leaf Extract, Dryopteris Filix-Mas Root Extract, Potassium Azeloyl Diglycinate, Theobroma Cacao Seed Extract, Biosaccharide Gum-4, Butylene Glycol, Phenoxyethanol, Ammonium Acryloyldimethyltaurate/​VP Copolymer, PEG-100 Stearate, BHT, Fragrance, Silica, Ethylhexylglycerin, 1,2-Hexanediol, Xanthan Gum, Zinc Oxide (Nano), Triethoxycaprylylsilane, Caprylyl Glycol, Chlorphenesin</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E284" s="3" t="n">
-        <v>64000</v>
+        <v>45000</v>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>https://down-bs-id.img.susercontent.com/id-11134207-822wt-mowb2pe08feqea.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-822wk-mntny8wuhse8d0.webp</t>
         </is>
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/6febZZW6Bn</t>
+          <t>https://s.shopee.co.id/5fmFWV82da</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>Wardah Sunscreen UV Shield Acne Calming Serum SPF 35 PA++++</t>
+          <t>Cleora Red Saviour Exfoliating Serum</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Sunscreen</t>
+          <t>Eksfoliasi</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Butyl Methoxydibenzoylmethane, Aluminium Starch Octenylsuccinate, Phenoxyethanol, Cetearyl Olivate, Propanediol, Butylene Glycol, Octocrylene, Acrylates C10-30 Alkyl Acrylate Crosspolymer, Sorbitan Olivate, Polymethyl Methacrylate, Aminomethyl Propanol, Allantoin, Salicylic Acid, Xanthan Gum, Triethylene Glycol, Ethylhexyl Triazone, Tetrasodium EDTA, Lecithin, BHT</t>
+          <t>"Aqua, Butylene Glycol, Glycolic Acid, Salicylic Acid, Niacinamide, Artemisia Vulgaris Extract, Houttuynia Cordata Leaf Extract, Aloe Vera Leaf Juice, Glycerine, PEG-40 Hydrogenated Castor Oil, Lactobionic Acid, Tranexamic Acid, Allantoin, Dipotassium Glycyrrhizate, Xanthan Gum, Styrene/​Acrylates Copolymer, Caramel, Phenoxyethanol, Ci 17200, Ci 77266"</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E285" s="3" t="n">
-        <v>35000</v>
+        <v>66000</v>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-8224p-mi9jj64a2ubk0e.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0p-mdndgmgw1ryjec.webp</t>
         </is>
       </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3g1Ir3jiXg</t>
+          <t>https://s.shopee.co.id/185Oz1dp5</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCARLETT Acne Peace Daily Sunscreen SPF 35 PA++++ </t>
+          <t>Skintific Lactic Acid Exfoliating Serum</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Sunscreen</t>
+          <t>Eksfoliasi</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>Aqua, Ethylhexyl Methoxycinnamate, Butyl Methoxydibenzoylmethane, Glycerin, Octocrylene, Centella Asiatica Extract, Methyl Methacrylate Crosspolymer, Aluminum Starch Octenylsuccinate, Propanediol, Allantoin, Aloe Barbadensis Leaf Extract, Dryopteris Filix-Mas Root Extract, Potassium Azeloyl Diglycinate, Theobroma Cacao Seed Extract, Biosaccharide Gum-4, Butylene Glycol, Phenoxyethanol, Ammonium Acryloyldimethyltaurate/​VP Copolymer, PEG-100 Stearate, BHT, Fragrance, Silica, Ethylhexylglycerin, 1,2-Hexanediol, Xanthan Gum, Zinc Oxide (Nano), Triethoxycaprylylsilane, Caprylyl Glycol, Chlorphenesin</t>
+          <t>"Aqua, Glycerin, Lactic Acid, Butylene Glycol, Gluconolactone, Propylene Glycol, Propanediol, Sodium Hydroxide, Albizia Julibrissin Bark Extract, Succinic Acid, Hydrolyzed Collagen, Enantia Chlorantha Bark Extract, Citrus Paradisi Fruit Extract, Xanthan Gum, Hydroxyacetophenone, Salicylic Acid, Lactobionic Acid, Mandelic Acid, Hydroxycinnamic Acid, Rutin, Glycerophosphoinositol Choline, Niacinamide, Alpha-Arbutin, 1,2-Hexanediol, PEG-40 Hydrogenated Castor Oil, Acrylamide/​Sodium Acryloyldimethyltaurate Copolymer, Ammonium Sulfate, Sodium Sulfate, Citric Acid, Amylopectin, Ethylhexylglycerin, Oleanolic Acid, Dextrin, Phenoxyethanol, Sodium Benzoate, Aroma, Ci 16035, Ci 60730"</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E286" s="3" t="n">
-        <v>45000</v>
+        <v>150000</v>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-822wk-mntny8wuhse8d0.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk8-m8yxjywgrivy5e.webp</t>
         </is>
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/5fmFWV82da</t>
+          <t>https://s.shopee.co.id/9zvRJQVNfu</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>Cleora Red Saviour Exfoliating Serum</t>
+          <t xml:space="preserve">Brighty Multipurpose Exfoliating Toner </t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -10687,7 +10684,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Butylene Glycol, Glycolic Acid, Salicylic Acid, Niacinamide, Artemisia Vulgaris Extract, Houttuynia Cordata Leaf Extract, Aloe Vera Leaf Juice, Glycerine, PEG-40 Hydrogenated Castor Oil, Lactobionic Acid, Tranexamic Acid, Allantoin, Dipotassium Glycyrrhizate, Xanthan Gum, Styrene/​Acrylates Copolymer, Caramel, Phenoxyethanol, Ci 17200, Ci 77266"</t>
+          <t>"Aqua, Glycolic Acid, Rose Extract, Propylene Glycol, Sodium Hydroxide, Glycerin, Propanediol, Phenoxyethanol, Butylene Glycol, Urea, Aloe Barbadensis Leaf Extract, Polysorbate 60, Disodium EDTA, Panax Ginseng Extract, Ethylhexylglycerin, Sodium PCA, Sodium Lactate, Hydroxyethylcellulose, Arginine, Aspartic Acid, Pca, Citric Acid, Potassium Sorbate, Sodium Benzoate, Glycine, Alanine, Serine, Valine, Isoleucine, Proline, Threonine, Sodium Nitrate, Histidine, Phenylalanine, Ci 16255, Ci 19140"</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -10696,23 +10693,23 @@
         </is>
       </c>
       <c r="E287" s="3" t="n">
-        <v>66000</v>
+        <v>75000</v>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0p-mdndgmgw1ryjec.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0p-mcua2c6r2psn1f.webp</t>
         </is>
       </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/185Oz1dp5</t>
+          <t>https://s.shopee.co.id/2VpQNj8yUa</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>Skintific Lactic Acid Exfoliating Serum</t>
+          <t>Glad2Glow Apricot Glycolic Acid Exfo Smooth Peeling Gel</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -10722,32 +10719,32 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Lactic Acid, Butylene Glycol, Gluconolactone, Propylene Glycol, Propanediol, Sodium Hydroxide, Albizia Julibrissin Bark Extract, Succinic Acid, Hydrolyzed Collagen, Enantia Chlorantha Bark Extract, Citrus Paradisi Fruit Extract, Xanthan Gum, Hydroxyacetophenone, Salicylic Acid, Lactobionic Acid, Mandelic Acid, Hydroxycinnamic Acid, Rutin, Glycerophosphoinositol Choline, Niacinamide, Alpha-Arbutin, 1,2-Hexanediol, PEG-40 Hydrogenated Castor Oil, Acrylamide/​Sodium Acryloyldimethyltaurate Copolymer, Ammonium Sulfate, Sodium Sulfate, Citric Acid, Amylopectin, Ethylhexylglycerin, Oleanolic Acid, Dextrin, Phenoxyethanol, Sodium Benzoate, Aroma, Ci 16035, Ci 60730"</t>
+          <t>"Aqua, Cellulose, Glycerin, Methylpropanediol, 1,2-Hexanediol, Glycolic Acid, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Malic Acid, Citric Acid, Hydroxyacetophenone, Malva Sylvestris Flower Extract, Paeonia Lactiflora Root Extract, Aloe Barbadensis Leaf Juice, Prunus Armeniaca Kernel Extract, Lonicera Japonica Flower Extract, Taraxacum Officinale Rhizome/​Root Extract, Chamomilla Recutita (Matricaria) Flower Extract, Hydrolyzed Rhodophyceae Extract, Tocopheryl Acetate, Ascorbyl Palmitate, Viola Yedoensis Extract, Maris Aqua, Ci 77492, Hydroxypropyl Methylcellulose, Sodium Hydroxide, Tartaric Acid, Aroma, Ethylhexyl-Glycerin, Phenoxyethanol, Sodium Benzoate, Potassium Sorbate"</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Scrub</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
-        <v>150000</v>
+        <v>49000</v>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rbk8-m8yxjywgrivy5e.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-8224u-mft19zfgrzf3dc.webp</t>
         </is>
       </c>
       <c r="G288" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9zvRJQVNfu</t>
+          <t>https://s.shopee.co.id/9pc17EybXG</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>Emina 2 in 1 Scrub &amp; Mask</t>
+          <t>BASE Daily Renewal Natural Exfoliating Pads</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -10757,32 +10754,32 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Propanediol, Glycerin, Kaolin, Dipropylene Glycol, Hydrated Silica, Glycereth-26, Juglans Regia (Walnut) Shell Powder, Sodium Polyacrylate, Phenoxyethanol, Silica, Xanthan Gum, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Chlorphenesin, Sodium Hydroxide, Vaccinium Myrtillus Fruit Extract, Carbomer, Disodium EDTA, Saccharum Officinarum (Sugar Cane) Extract, Butylene Glycol, Citrus Aurantium Dulcis (Orange) Fruit Extract, Citrus Limon (Lemon) Fruit Extract, Acer Saccharum (Sugar Maple) Extract, Actinidia Polygama Fruit Extract"</t>
+          <t>"Water, Glycerin, Camellia Sinensis Leaf Extract, Butylene Glycol, Niacinamide, Salix Alba (Willow) Bark Extract, Methylpropanediol, Panthenol, 1,2-Hexanediol, Phenoxyethanol, PEG-60 Hydrogenated Castor Oil, Allantoin, Octyldodeceth-16, Sodium Citrate, Caprylyl Glycol, Citrus Limon (Lemon) Peel Oil, Citric Acid, Ethylhexylglycerin, Disodium EDTA, Xanthan Gum, Tocopherol"</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>Scrub</t>
+          <t>Pads</t>
         </is>
       </c>
       <c r="E289" s="3" t="n">
-        <v>49000</v>
+        <v>85000</v>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7qukw-lfkj5vocci1uf9.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasm-m1wou5rrw6xqee.webp</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8ATn86jk2K</t>
+          <t>https://s.shopee.co.id/1BK2nLYMfk</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brighty Multipurpose Exfoliating Toner </t>
+          <t>CETAPHIL Daily Exfoliating Cleanser</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -10792,32 +10789,32 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycolic Acid, Rose Extract, Propylene Glycol, Sodium Hydroxide, Glycerin, Propanediol, Phenoxyethanol, Butylene Glycol, Urea, Aloe Barbadensis Leaf Extract, Polysorbate 60, Disodium EDTA, Panax Ginseng Extract, Ethylhexylglycerin, Sodium PCA, Sodium Lactate, Hydroxyethylcellulose, Arginine, Aspartic Acid, Pca, Citric Acid, Potassium Sorbate, Sodium Benzoate, Glycine, Alanine, Serine, Valine, Isoleucine, Proline, Threonine, Sodium Nitrate, Histidine, Phenylalanine, Ci 16255, Ci 19140"</t>
+          <t>"Aqua, Cocamidopropyl Betaine, Disodium Cocoamphodiacetate, Glycerin, Coco-Glucoside, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Bambusa Arundinacea Stem Extract, Citric Acid, Heliotropine, Panthenol, Parfum, Phenoxyethanol, Polyquaternium-10, Sodium Benzoate, Sodium Chloride, Sodium Citrate, Sodium Cocoamphoacetate, Sodium Hydroxide, Tocopheryl Acetate, Xanthan Gum"</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E290" s="3" t="n">
-        <v>75000</v>
+        <v>91000</v>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0p-mcua2c6r2psn1f.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7qukx-lh5okc0pq1nw78.webp</t>
         </is>
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/2VpQNj8yUa</t>
+          <t>https://s.shopee.co.id/9fIav4UNdS</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>Glad2Glow Apricot Glycolic Acid Exfo Smooth Peeling Gel</t>
+          <t>Erha21 Exfoliating Cleansing Scrub</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -10827,7 +10824,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Cellulose, Glycerin, Methylpropanediol, 1,2-Hexanediol, Glycolic Acid, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Malic Acid, Citric Acid, Hydroxyacetophenone, Malva Sylvestris Flower Extract, Paeonia Lactiflora Root Extract, Aloe Barbadensis Leaf Juice, Prunus Armeniaca Kernel Extract, Lonicera Japonica Flower Extract, Taraxacum Officinale Rhizome/​Root Extract, Chamomilla Recutita (Matricaria) Flower Extract, Hydrolyzed Rhodophyceae Extract, Tocopheryl Acetate, Ascorbyl Palmitate, Viola Yedoensis Extract, Maris Aqua, Ci 77492, Hydroxypropyl Methylcellulose, Sodium Hydroxide, Tartaric Acid, Aroma, Ethylhexyl-Glycerin, Phenoxyethanol, Sodium Benzoate, Potassium Sorbate"</t>
+          <t>"Aqua, Glycerin, Myristic Acid, Lauric Acid, Niacinamide, Cocamidopropyl Hydroxysultaine, PEG-120 Methyl Glucose Dioleate, Sodium Cocoamphoacetate, Potassium Cocoyl Glycinate, Potassium Hydroxide, Lactic Acid (2952%), Cocamidopropyl Betaine, Sodium Lauroyl Sarcosinate, Dimethyl Sulfone, Salicylic Acid, Stearic Acid, Synthetic Wax, Sodium Chloride, Propylene Glycol, Panthenol, Fragrance (Parfum) Components, Finished Fragrances, Sodium PEG-7 Olive Oil Carboxylate, Diazolidinyl Urea, Xanthan Gum, BHT, Tetrasodium EDTA, Methylparaben, Caprylic/​Capric Glycerides, Propylparaben, Ci 42090:2, Methylchloroisothiazolinone, Methylisothiazolinone"</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -10836,23 +10833,23 @@
         </is>
       </c>
       <c r="E291" s="3" t="n">
-        <v>49000</v>
+        <v>102000</v>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-8224u-mft19zfgrzf3dc.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98o-lxgmb65s5pqla0.webp</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9pc17EybXG</t>
+          <t>https://s.shopee.co.id/AAErW3DjMf</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>BASE Daily Renewal Natural Exfoliating Pads</t>
+          <t>NPURE Peeling Gel Licorice</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -10862,32 +10859,32 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycerin, Camellia Sinensis Leaf Extract, Butylene Glycol, Niacinamide, Salix Alba (Willow) Bark Extract, Methylpropanediol, Panthenol, 1,2-Hexanediol, Phenoxyethanol, PEG-60 Hydrogenated Castor Oil, Allantoin, Octyldodeceth-16, Sodium Citrate, Caprylyl Glycol, Citrus Limon (Lemon) Peel Oil, Citric Acid, Ethylhexylglycerin, Disodium EDTA, Xanthan Gum, Tocopherol"</t>
+          <t>"Water, Glycerin, Cellulose, Dipropylene Glycol, Butylene Glycol, Propylene Glycol, Carica Papaya (Papaya) Fruit Water, Pentylene Glycol, 1,2-Hexanediol, Carbomer, Tromethamine, Caprylyl Glycol, Polysorbate 20, Betaine, Disodium EDTA, Dipotassium Glycyrrhizate, Niacinamide, Tocopheryl Acetate, Palmitoyl Tetrapeptide-10, Galactomyces Ferment Filtrate, Mannitol, Hydrogenated Lecithin, Cholesterol, Glycyrrhiza Uralensis (Licorice) Root Extract, Caprylic/​Capric Triglyceride, Cetyl Palmitate, Chitosan, Sorbitan Stearate, Polysorbate 80, Bromelain, Ceramide NP, Papain, Phenoxyethanol, Sodium Benzoate, Citric Acid, Tocopherol, Ethylhexylglycerin, Fragrance (Parfum)"</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Pads</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E292" s="3" t="n">
-        <v>85000</v>
+        <v>69000</v>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasm-m1wou5rrw6xqee.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0h-mcingy82ygcc22.webp</t>
         </is>
       </c>
       <c r="G292" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/1BK2nLYMfk</t>
+          <t>https://s.shopee.co.id/7fXWXb2Z0D</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>CETAPHIL Daily Exfoliating Cleanser</t>
+          <t>Implora How Does It Peel</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -10897,7 +10894,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Cocamidopropyl Betaine, Disodium Cocoamphodiacetate, Glycerin, Coco-Glucoside, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Bambusa Arundinacea Stem Extract, Citric Acid, Heliotropine, Panthenol, Parfum, Phenoxyethanol, Polyquaternium-10, Sodium Benzoate, Sodium Chloride, Sodium Citrate, Sodium Cocoamphoacetate, Sodium Hydroxide, Tocopheryl Acetate, Xanthan Gum"</t>
+          <t>"Aqua, Propylene Glycol, Glycerin, Carbomer, Succinic Acid, Phenoxyethanol, Polyglyceryl-4 Caprate, Ethylhexylglycerin, Behentrimonium Chloride, Fragrance, Glycolic Acid, Silanediol Salicylate, Pentylene Glycol, Isopropyl Alcohol, Methyl Diisopropyl Propionamide, Aloe Barbadensis Leaf Extract, Soluble Collagen, Benzoic Acid, Sodium Methylparaben, Hydrolyzed Caviar Extract, Hydrolyzed Pearl, Propylparaben, Ci 19140, Ci 42090"</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -10906,23 +10903,23 @@
         </is>
       </c>
       <c r="E293" s="3" t="n">
-        <v>91000</v>
+        <v>22000</v>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7qukx-lh5okc0pq1nw78.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasg-m20r08jkukn1b3.webp</t>
         </is>
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9fIav4UNdS</t>
+          <t>https://s.shopee.co.id/7Kug91haI7</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>Erha21 Exfoliating Cleansing Scrub</t>
+          <t>Hanasui Ceramide Probiotics Peeling Gel</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -10932,32 +10929,32 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glycerin, Myristic Acid, Lauric Acid, Niacinamide, Cocamidopropyl Hydroxysultaine, PEG-120 Methyl Glucose Dioleate, Sodium Cocoamphoacetate, Potassium Cocoyl Glycinate, Potassium Hydroxide, Lactic Acid (2952%), Cocamidopropyl Betaine, Sodium Lauroyl Sarcosinate, Dimethyl Sulfone, Salicylic Acid, Stearic Acid, Synthetic Wax, Sodium Chloride, Propylene Glycol, Panthenol, Fragrance (Parfum) Components, Finished Fragrances, Sodium PEG-7 Olive Oil Carboxylate, Diazolidinyl Urea, Xanthan Gum, BHT, Tetrasodium EDTA, Methylparaben, Caprylic/​Capric Glycerides, Propylparaben, Ci 42090:2, Methylchloroisothiazolinone, Methylisothiazolinone"</t>
+          <t>"Aqua, Glyserin, Prunus Avium (Sweet Cherry) Fruit Extract, Carbomer, Lactic Acid, Vaccinium Angustifolium Fruit Extract, Glycolic Acid, Propanediol, Galactomyces Ferment Filtrate, Gluconolactone, Methyl Gluceth-20, Tranexamic Acid, Phenoxyethanol, Ethanol, PEG-20, Caprylic/​Capric Triglyceride, Salicylic Acid, Butylene Glycol, Lactobacillus Ferment, Lecithin, Allantoin, Cetrimonium Chloride, Ethylhexylglycerin, Fragrance, 1,2-Hexanediol, Ascorbic Acid, Hydrogenated Lecithin, Sucrose Stearate, Ceramide NP, Sodium Hyaluronate, Ceramide AP, Ceramide AS, Ceramide NG, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Pentylene Glycol, Potassium Hyaluronate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate Crosspolymer, Glycosphingolipids"</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>Scrub</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E294" s="3" t="n">
-        <v>102000</v>
+        <v>33000</v>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r98o-lxgmb65s5pqla0.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7r992-lvx1nnymmr174e.webp</t>
         </is>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/AAErW3DjMf</t>
+          <t>https://s.shopee.co.id/3g1NmJUkW8</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>NPURE Peeling Gel Licorice</t>
+          <t xml:space="preserve">Hada Labo Tamagohada Mild Peeling Lotion </t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -10967,32 +10964,32 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycerin, Cellulose, Dipropylene Glycol, Butylene Glycol, Propylene Glycol, Carica Papaya (Papaya) Fruit Water, Pentylene Glycol, 1,2-Hexanediol, Carbomer, Tromethamine, Caprylyl Glycol, Polysorbate 20, Betaine, Disodium EDTA, Dipotassium Glycyrrhizate, Niacinamide, Tocopheryl Acetate, Palmitoyl Tetrapeptide-10, Galactomyces Ferment Filtrate, Mannitol, Hydrogenated Lecithin, Cholesterol, Glycyrrhiza Uralensis (Licorice) Root Extract, Caprylic/​Capric Triglyceride, Cetyl Palmitate, Chitosan, Sorbitan Stearate, Polysorbate 80, Bromelain, Ceramide NP, Papain, Phenoxyethanol, Sodium Benzoate, Citric Acid, Tocopherol, Ethylhexylglycerin, Fragrance (Parfum)"</t>
+          <t>"Water, Gluconic Acid, Pentylene Glycol, Butylene Glycol, Tranexamic Acid, Polyquaternium-51, Sodium Metabisulfite"</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E295" s="3" t="n">
-        <v>69000</v>
+        <v>61000</v>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0h-mcingy82ygcc22.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0t-mby41zrr4o6cb1.webp</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/7fXWXb2Z0D</t>
+          <t>https://s.shopee.co.id/6VLZ9bli6Z</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>Implora How Does It Peel</t>
+          <t>Sariayu Bright Skin Putih Langsat Face Scrub</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -11002,32 +10999,32 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Propylene Glycol, Glycerin, Carbomer, Succinic Acid, Phenoxyethanol, Polyglyceryl-4 Caprate, Ethylhexylglycerin, Behentrimonium Chloride, Fragrance, Glycolic Acid, Silanediol Salicylate, Pentylene Glycol, Isopropyl Alcohol, Methyl Diisopropyl Propionamide, Aloe Barbadensis Leaf Extract, Soluble Collagen, Benzoic Acid, Sodium Methylparaben, Hydrolyzed Caviar Extract, Hydrolyzed Pearl, Propylparaben, Ci 19140, Ci 42090"</t>
+          <t>"Water, Glycerin, Cetearyl Alcohol, Coco-Betaine, Sodium Chloride, PEG-100 Stearate, Glyceryl Stearate, Lansium Domesticum Fruit Extract, Chlorphenesin, Hibiscus Rosa-Sinensis Flower Extract, Ocimum Basilicum Flower/​Leaf/​Stem Extract, Sodium Benzoate, Stearic Acid, PEG-20 Stearate, Cetyl Palmitate, Caprylic/​Capric Triglyceride, Microcrystalline Cellulose, Polyethylene, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Panthenol, Sodium Lauroyl Glutamate, Ascorbyl Dipalmitate, Glycyrrhiza Glabra Root Extract, Tocopheryl Acetate, Allantoin, Phenoxyethanol, Aminomethyl Propanol, Pentaerythrityl Tetra-Di-T-Butyl Hydroxyhydrocinnamate, Tetrasodium EDTA, Fragrance"</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Scrub</t>
         </is>
       </c>
       <c r="E296" s="3" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7rasg-m20r08jkukn1b3.webp</t>
+          <t>https://down-id.img.susercontent.com/file/f8cea501446cf3183f430231992f9286.webp</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/7Kug91haI7</t>
+          <t>https://s.shopee.co.id/1qZjb6AJez</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>Hanasui Ceramide Probiotics Peeling Gel</t>
+          <t>Freeman Face Scrub Exfoliating Indonesia Coconut Tube</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -11037,32 +11034,32 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Glyserin, Prunus Avium (Sweet Cherry) Fruit Extract, Carbomer, Lactic Acid, Vaccinium Angustifolium Fruit Extract, Glycolic Acid, Propanediol, Galactomyces Ferment Filtrate, Gluconolactone, Methyl Gluceth-20, Tranexamic Acid, Phenoxyethanol, Ethanol, PEG-20, Caprylic/​Capric Triglyceride, Salicylic Acid, Butylene Glycol, Lactobacillus Ferment, Lecithin, Allantoin, Cetrimonium Chloride, Ethylhexylglycerin, Fragrance, 1,2-Hexanediol, Ascorbic Acid, Hydrogenated Lecithin, Sucrose Stearate, Ceramide NP, Sodium Hyaluronate, Ceramide AP, Ceramide AS, Ceramide NG, Hyaluronic Acid, Hydrolyzed Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Pentylene Glycol, Potassium Hyaluronate, Sodium Acetylated Hyaluronate, Sodium Hyaluronate Crosspolymer, Glycosphingolipids"</t>
+          <t>"Sucrose, Propylene Glycol, Titanium Dioxide, Cocos Nucifera (Coconut) Oil, Musa Sapientum (Banana) Fruit Extract, Cocos Nucifera (Coconut) Fruit Extract, Aleurites Moluccanus Seed Extract, Zingiber Officinale (Ginger) Root Extract, Psidium Guajava Fruit Extract, Cymbopogon Schoenanthus Extract, Carica Papaya (Papaya) Fruit Extract, Rubus Idaeus (Raspberry) Fruit Extract, Santalum Album (Sandalwood) Extract, Macrocystis Pyrifera (Kelp) Extract, Nasturtium Officinale Extract, Maranta Arundinacea Root Extract, Lavandula Angustifolia (Lavender) Oil, Carbomer, Phenoxyethanol, Fragrance (Parfum), Yellow 5 (Ci 19140, Blue 1 (Ci 42090)"</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Scrub</t>
         </is>
       </c>
       <c r="E297" s="3" t="n">
-        <v>33000</v>
+        <v>108000</v>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7r992-lvx1nnymmr174e.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134201-7rasm-m0ywet7fnkmgbf.webp</t>
         </is>
       </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3g1NmJUkW8</t>
+          <t>https://s.shopee.co.id/8V6dXPAKS9</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hada Labo Tamagohada Mild Peeling Lotion </t>
+          <t>Kahf Gentle Exfoliating Face Scrub</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -11072,32 +11069,32 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>"Water, Gluconic Acid, Pentylene Glycol, Butylene Glycol, Tranexamic Acid, Polyquaternium-51, Sodium Metabisulfite"</t>
+          <t>"Aqua, Myristic Acid, Glycerin, Butylene Glycol, Stearic Acid, Potassium Hydroxide, Lauric Acid, Decyl Glucoside, Glyceryl Stearate, Hydrated Silica, Olive Oil PEG-7 Esters, Phenoxyethanol, Saccharide Isomerate, Niacinamide, Fragrance, Allantoin, Disodium EDTA, Menthyl Lactate, Hydroxypropyl Methylcellulose, PEG-40 Hydrogenated Castor Oil, PPG-26-Buteth-26, Ethylhexylglycerin, Propylene Glycol, Citric Acid, Sodium Citrate, Coffea Arabica (Coffee) Seedcake Extract, Glucose, Trideceth-9, Lactic Acid, Potassium Sorbate, Benzyl Alcohol, Panax Ginseng Root Extract, Sodium Benzoate, Hamamelis Virginiana (Witch Hazel) Leaf Extract, Caramel"</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Scrub</t>
         </is>
       </c>
       <c r="E298" s="3" t="n">
-        <v>61000</v>
+        <v>32000</v>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0t-mby41zrr4o6cb1.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0t-mcbs8dszfufyf1.webp</t>
         </is>
       </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/6VLZ9bli6Z</t>
+          <t>https://s.shopee.co.id/4LH4Zn7Ndz</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>Sariayu Bright Skin Putih Langsat Face Scrub</t>
+          <t>GLAD2GLOW Centella Salicylic Acid Exfoliating Acne Pads</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -11107,137 +11104,140 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>"Water, Glycerin, Cetearyl Alcohol, Coco-Betaine, Sodium Chloride, PEG-100 Stearate, Glyceryl Stearate, Lansium Domesticum Fruit Extract, Chlorphenesin, Hibiscus Rosa-Sinensis Flower Extract, Ocimum Basilicum Flower/​Leaf/​Stem Extract, Sodium Benzoate, Stearic Acid, PEG-20 Stearate, Cetyl Palmitate, Caprylic/​Capric Triglyceride, Microcrystalline Cellulose, Polyethylene, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Panthenol, Sodium Lauroyl Glutamate, Ascorbyl Dipalmitate, Glycyrrhiza Glabra Root Extract, Tocopheryl Acetate, Allantoin, Phenoxyethanol, Aminomethyl Propanol, Pentaerythrityl Tetra-Di-T-Butyl Hydroxyhydrocinnamate, Tetrasodium EDTA, Fragrance"</t>
+          <t>"Aqua, Potassium Cocoyl Glycinate, Hydrogenated Starch Hydrolysate, Acrylates/​Steareth-20 Methacrylate Crosspolymer, Centella Asiatica Extract, Potassium Cocoate, Salicylic Acid, Sodium Lauroamphoacetate, Lauryl Hydroxysultaine, Erythritol, Caprylyl Glycol, Potassium Hydroxide, Sodium Chloride, Disodium EDTA, Glycosyl Trehalose, Hydroxypropyl Cyclodextrin, Aroma, Phenoxyethanol"</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>Scrub</t>
+          <t>Pads</t>
         </is>
       </c>
       <c r="E299" s="3" t="n">
-        <v>45000</v>
+        <v>59000</v>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/f8cea501446cf3183f430231992f9286.webp</t>
+          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0p-mbotnjq28oswbc.webp</t>
         </is>
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/1qZjb6AJez</t>
+          <t>https://s.shopee.co.id/9fIavdQcf6</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>Freeman Face Scrub Exfoliating Indonesia Coconut Tube</t>
+          <t xml:space="preserve"> Azarine Hydrasoothe Sunscreen Gel SPF45 PA++++</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Sunscreen</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>"Sucrose, Propylene Glycol, Titanium Dioxide, Cocos Nucifera (Coconut) Oil, Musa Sapientum (Banana) Fruit Extract, Cocos Nucifera (Coconut) Fruit Extract, Aleurites Moluccanus Seed Extract, Zingiber Officinale (Ginger) Root Extract, Psidium Guajava Fruit Extract, Cymbopogon Schoenanthus Extract, Carica Papaya (Papaya) Fruit Extract, Rubus Idaeus (Raspberry) Fruit Extract, Santalum Album (Sandalwood) Extract, Macrocystis Pyrifera (Kelp) Extract, Nasturtium Officinale Extract, Maranta Arundinacea Root Extract, Lavandula Angustifolia (Lavender) Oil, Carbomer, Phenoxyethanol, Fragrance (Parfum), Yellow 5 (Ci 19140, Blue 1 (Ci 42090)"</t>
+          <t xml:space="preserve">"Aqua, Glycerin, Propanediol, Ethylhexyl Methoxycinnamate, Butyl Methoxydibenzoylmethane, Aloe Barbadensis Juice Extract, Portulaca Oleracea Extract, Sodium Hyaluronate, Cucumis Sativus Fruit Extract, Camellia Sinensis Extract, Punica Granatum Fruit Extract, Phenoxyethanol, Octocrylene, Butylene Glycol, Sodium Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Propolis, Picea Abies Extract, Allantoin, Xanthan Gum, Panthenol, Fragrance, Lecithin"
+</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Scrub</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E300" s="3" t="n">
-        <v>108000</v>
+        <v>65000</v>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134201-7rasm-m0ywet7fnkmgbf.webp</t>
+          <t>https://down-aka-id.img.susercontent.com/id-11134207-822wg-monfr5c8zguk51.webp</t>
         </is>
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/8V6dXPAKS9</t>
+          <t>https://s.shopee.co.id/110cc7067A</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>Kahf Gentle Exfoliating Face Scrub</t>
+          <t>Facetology Triple Care Sunscreen For Acne &amp; Oily Skin SPF 40 PA+++</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Sunscreen</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Myristic Acid, Glycerin, Butylene Glycol, Stearic Acid, Potassium Hydroxide, Lauric Acid, Decyl Glucoside, Glyceryl Stearate, Hydrated Silica, Olive Oil PEG-7 Esters, Phenoxyethanol, Saccharide Isomerate, Niacinamide, Fragrance, Allantoin, Disodium EDTA, Menthyl Lactate, Hydroxypropyl Methylcellulose, PEG-40 Hydrogenated Castor Oil, PPG-26-Buteth-26, Ethylhexylglycerin, Propylene Glycol, Citric Acid, Sodium Citrate, Coffea Arabica (Coffee) Seedcake Extract, Glucose, Trideceth-9, Lactic Acid, Potassium Sorbate, Benzyl Alcohol, Panax Ginseng Root Extract, Sodium Benzoate, Hamamelis Virginiana (Witch Hazel) Leaf Extract, Caramel"</t>
+          <t xml:space="preserve">"Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Centella Asiatica Extract, Methylene Bis-Benzotriazolyl Tetramethyl, Butyl Methoxydibenzoylmethane, Titanium Dioxide, Octocrylene, Zinc Oxide, Madecassoside, Artemisia Vulgaris Extract, Camellia Japonica Flower Extract, Morus Alba Bark Extract, Broussonetia Papyrifera Bark Extract, Camellia Sinensis Leaf Extract, Rhus Semialata Extract, Pyrus Malus Fruit Extract, Tricholoma Matsutake Extract, Phragmites Communis Extract, Poria Cocos Extract, Tranexamic Acid, Salicylic Acid, Butylene Glycol, Cyclopentasiloxane, Glycerin, Propylene Glycol, Carbomer, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Triethoxycaprylylsilane, Acetyl Glucosamine, Pectin, Hydrogenated Lecithin, Polysorbate 60, Sorbitan Isostearate, Citric Acid, Aluminum Hydroxide, Caprylhydroxamic Acid, Decyl Glucoside, PEG-40 Hydrogenated Castor Oil, Sodium Benzoate, Phenoxyethanol, Ethylhexylglycerin"
+</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>Scrub</t>
+          <t xml:space="preserve">Gel </t>
         </is>
       </c>
       <c r="E301" s="3" t="n">
-        <v>32000</v>
+        <v>80000</v>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0t-mcbs8dszfufyf1.webp</t>
+          <t>https://down-tx-id.img.susercontent.com/id-11134207-822wu-mlpv1aphagox6d.webp</t>
         </is>
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4LH4Zn7Ndz</t>
+          <t>https://s.shopee.co.id/3B57CQaDtz</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>GLAD2GLOW Centella Salicylic Acid Exfoliating Acne Pads</t>
+          <t>LABORÉ Sensitive Skin Care BiomeProtect™ Acne &amp; Oil Correct Physical Sunscreen SPF50+ PA++++</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Eksfoliasi</t>
+          <t>Sunscreen</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>"Aqua, Potassium Cocoyl Glycinate, Hydrogenated Starch Hydrolysate, Acrylates/​Steareth-20 Methacrylate Crosspolymer, Centella Asiatica Extract, Potassium Cocoate, Salicylic Acid, Sodium Lauroamphoacetate, Lauryl Hydroxysultaine, Erythritol, Caprylyl Glycol, Potassium Hydroxide, Sodium Chloride, Disodium EDTA, Glycosyl Trehalose, Hydroxypropyl Cyclodextrin, Aroma, Phenoxyethanol"</t>
+          <t xml:space="preserve">"Aqua, Zinc Oxide, C12-15 Alkyl Benzoate, C14-22 Alcohols, Propanediol, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Bisabolol, C12-20 Alkyl Glucoside, Glycerin, 1,2-Hexanediol, Triethoxycaprylylsilane, Polyacrylate Crosspolymer-6, Allantoin, Chlorphenesin, Polyhydroxystearic Acid, Butylene Glycol, Silica, Dibutyl Adipate, Madecassoside, Bacillus Lysate, Caprylhydroxamic Acid, Aminomethyl Propanol, Maltodextrin, Chlorophyllin-Copper Complex, Glucose, Vitis Vinifera (Grape) Leaf Extract, Lactobacillus Ferment, Palmitoyl Pentapeptide-4, Actinidia Polygama Fruit Extract, Camellia Sinensis Leaf Extract"
+</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Pads</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="E302" s="3" t="n">
-        <v>59000</v>
+        <v>185000</v>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>https://down-id.img.susercontent.com/file/id-11134207-7ra0p-mbotnjq28oswbc.webp</t>
+          <t>https://down-tx-id.img.susercontent.com/sg-11134201-81zwi-mmk0tbl2bqbmc2.webp</t>
         </is>
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/9fIavdQcf6</t>
+          <t>https://s.shopee.co.id/902u9WEpb2</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Azarine Hydrasoothe Sunscreen Gel SPF45 PA++++</t>
+          <t>Ella Skincare UV Intensive Protector Sunscreen SPF 40+ PA+++</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
@@ -11247,33 +11247,33 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Aqua, Glycerin, Propanediol, Ethylhexyl Methoxycinnamate, Butyl Methoxydibenzoylmethane, Aloe Barbadensis Juice Extract, Portulaca Oleracea Extract, Sodium Hyaluronate, Cucumis Sativus Fruit Extract, Camellia Sinensis Extract, Punica Granatum Fruit Extract, Phenoxyethanol, Octocrylene, Butylene Glycol, Sodium Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Propolis, Picea Abies Extract, Allantoin, Xanthan Gum, Panthenol, Fragrance, Lecithin"
+          <t xml:space="preserve">"Aqua, Ethylhexyl Methoxycinnamate, Paraffinum Liquidum, Glycerin, Butyl Methoxydibenzoylmethane, Niacinamide, Centella Asiatica Extract, Polyacrylamide, Glycine Soja Oil, Titanium Dioxide, Octocrylene, Butylene Glycol, C13-14 Isoparaffin, Oryza Sativa Extract, Polyglyceryl-3 Diisostearate, Laureth-7, Ethylhexyl Salicylate, Lecithin, Butylene Glycol, Methylene Bis-Benzotriazolyl Tetramethylbutylphenol, Zinc Oxide, Acetyl Glucosamine, 1,2-Hexanediol, Triethoxycaprylylsilane, Aluminum Hydroxide, Sodium Hyaluronate, Decyl Glucoside, Hyaluronic Acid, Camellia Japonica Flower Extract, Madecassoside, Morus Alba Bark Extract, Broussonetia Papyrifera Bark Extract, Camellia Sinensis Leaf Extract, Rhus Semialata Extract, Pyrus Malus Fruit Extract, Ethylhexylglycerin, Caprylhydroxamic Acid, Hydrolyzed Hyaluronic Acid, Tricholoma Matsutake Extract, Propylene Glycol, Xanthan Gum, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Sodium Hyaluronate, PEG-9 Diglycidyl Ether/​Sodium Hyaluronate Crosspolymer, Sodium Acetylated Hyaluronate, Phenoxyethanol"
 </t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>Gel</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="E303" s="3" t="n">
-        <v>65000</v>
+        <v>53000</v>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>https://down-aka-id.img.susercontent.com/id-11134207-822wg-monfr5c8zguk51.webp</t>
+          <t>https://down-tx-id.img.susercontent.com/id-11134207-8224o-mj0rks3oblz6f7.webp</t>
         </is>
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/110cc7067A</t>
+          <t>https://s.shopee.co.id/110cdBUdKn</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>Facetology Triple Care Sunscreen For Acne &amp; Oily Skin SPF 40 PA+++</t>
+          <t>UNITARY Global GlowingSuncare Sunscreen UV Protector SPF 50ml 50+ PA++++</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -11283,33 +11283,32 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Centella Asiatica Extract, Methylene Bis-Benzotriazolyl Tetramethyl, Butyl Methoxydibenzoylmethane, Titanium Dioxide, Octocrylene, Zinc Oxide, Madecassoside, Artemisia Vulgaris Extract, Camellia Japonica Flower Extract, Morus Alba Bark Extract, Broussonetia Papyrifera Bark Extract, Camellia Sinensis Leaf Extract, Rhus Semialata Extract, Pyrus Malus Fruit Extract, Tricholoma Matsutake Extract, Phragmites Communis Extract, Poria Cocos Extract, Tranexamic Acid, Salicylic Acid, Butylene Glycol, Cyclopentasiloxane, Glycerin, Propylene Glycol, Carbomer, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Triethoxycaprylylsilane, Acetyl Glucosamine, Pectin, Hydrogenated Lecithin, Polysorbate 60, Sorbitan Isostearate, Citric Acid, Aluminum Hydroxide, Caprylhydroxamic Acid, Decyl Glucoside, PEG-40 Hydrogenated Castor Oil, Sodium Benzoate, Phenoxyethanol, Ethylhexylglycerin"
-</t>
+          <t>"Zinc Oxide, Isododecane, Cyclopentasiloxane, Water, Glycerin, Butylene Glycol, Cyclohexasiloxane, Neopentyl Glycol Dicaprate, Titanium Dioxide, Polyglyceryl-3 Polydimethylsiloxyethyl Dimethicone, Polymethylsilsesquioxane, Sodium Chloride, Trimethylsiloxysilicate, Triethoxycaprylylsilane, Acrylates/​Polytrimethylsiloxymethacrylate Copolymer, PEG-10 Dimethicone, Disteardimonium Hectorite, Dextrin Palmitate, Lauryl PEG-9 Polydimethylsiloxyethyl Dimethicone, 1,2-Hexanediol, Hydroxyacetophenone, Propanediol, Aluminum Hydroxide, Stearic Acid, Tocopheryl Acetate, Polyhydroxystearic Acid, Lecithin"</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gel </t>
+          <t>Lotion</t>
         </is>
       </c>
       <c r="E304" s="3" t="n">
-        <v>80000</v>
+        <v>45000</v>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>https://down-tx-id.img.susercontent.com/id-11134207-822wu-mlpv1aphagox6d.webp</t>
+          <t>https://down-bs-id.img.susercontent.com/id-11134207-81ztl-mfrqg4nthzplf5.webp</t>
         </is>
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3B57CQaDtz</t>
+          <t>https://s.shopee.co.id/185RY1tg1</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>LABORÉ Sensitive Skin Care BiomeProtect™ Acne &amp; Oil Correct Physical Sunscreen SPF50+ PA++++</t>
+          <t>SKIN1004 Madagascar Centella Hyalu-Cica Water-Fit Sun Serum SPF50 PA++++</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
@@ -11319,33 +11318,33 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Aqua, Zinc Oxide, C12-15 Alkyl Benzoate, C14-22 Alcohols, Propanediol, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Bisabolol, C12-20 Alkyl Glucoside, Glycerin, 1,2-Hexanediol, Triethoxycaprylylsilane, Polyacrylate Crosspolymer-6, Allantoin, Chlorphenesin, Polyhydroxystearic Acid, Butylene Glycol, Silica, Dibutyl Adipate, Madecassoside, Bacillus Lysate, Caprylhydroxamic Acid, Aminomethyl Propanol, Maltodextrin, Chlorophyllin-Copper Complex, Glucose, Vitis Vinifera (Grape) Leaf Extract, Lactobacillus Ferment, Palmitoyl Pentapeptide-4, Actinidia Polygama Fruit Extract, Camellia Sinensis Leaf Extract"
+          <t xml:space="preserve">"Water, Dibutyl Adipate, Propanediol, Diethylamino Hydroxybenzoyl Hexyl Benzoate, Polymethylsilsesquioxane, Ethylhexyl Triazone, Methylene Bis-Benzotriazolyl Tetramethylbutylphenol, Niacinamide, Coco-Caprylate/​Caprate, Caprylyl Methicone, Diethylhexyl Butamido Triazone, Glycerin, 1,2-Hexanediol, Butylene Glycol, Centella Asiatica Extract(9,800Ppm), Betula Platyphylla Japonica Bark Extract, Ginkgo Biloba Leaf Extract, Camellia Sinensis Leaf Extract, Triticum Vulgare (Wheat) Sprout Extract, Medicago Sativa (Alfalfa) Extract, Brassica Oleracea Italica (Broccoli) Sprout Extract, Eruca Sativa Leaf Extract, Camellia Japonica Leaf Extract, Sodium Hyaluronate(10Ppm), Behenyl Alcohol, Poly C10-30 Alkyl Acrylate, Polyglyceryl-3 Methylglucose Distearate, Decyl Glucoside, Tromethamine, Carbomer, Acrylates /​C10-30 Alkyl Acrylate Crosspolymer, Sodium Stearoyl Glutamate, Polyacrylate Crosspolymer-6, Adenosine, Xanthan Gum, T-Butyl Alcohol, Tocopherol, Hydrolyzed Hyaluronic Acid(Ppm), Inositol, Hyaluronic Acid(0.01Ppm), Pentylene Glycol, Ethylhexylglycerin"
 </t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>cair</t>
         </is>
       </c>
       <c r="E305" s="3" t="n">
-        <v>185000</v>
+        <v>144000</v>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>https://down-tx-id.img.susercontent.com/sg-11134201-81zwi-mmk0tbl2bqbmc2.webp</t>
+          <t>https://down-bs-id.img.susercontent.com/id-11134207-822wq-mop92amj5ds18a.webp</t>
         </is>
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/902u9WEpb2</t>
+          <t>https://s.shopee.co.id/3g1NoZ34OI</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>Ella Skincare UV Intensive Protector Sunscreen SPF 40+ PA+++</t>
+          <t>YOU Sunbrella Acne Shield Light Sunscreen SPF40+ PA++++</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -11355,33 +11354,33 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Aqua, Ethylhexyl Methoxycinnamate, Paraffinum Liquidum, Glycerin, Butyl Methoxydibenzoylmethane, Niacinamide, Centella Asiatica Extract, Polyacrylamide, Glycine Soja Oil, Titanium Dioxide, Octocrylene, Butylene Glycol, C13-14 Isoparaffin, Oryza Sativa Extract, Polyglyceryl-3 Diisostearate, Laureth-7, Ethylhexyl Salicylate, Lecithin, Butylene Glycol, Methylene Bis-Benzotriazolyl Tetramethylbutylphenol, Zinc Oxide, Acetyl Glucosamine, 1,2-Hexanediol, Triethoxycaprylylsilane, Aluminum Hydroxide, Sodium Hyaluronate, Decyl Glucoside, Hyaluronic Acid, Camellia Japonica Flower Extract, Madecassoside, Morus Alba Bark Extract, Broussonetia Papyrifera Bark Extract, Camellia Sinensis Leaf Extract, Rhus Semialata Extract, Pyrus Malus Fruit Extract, Ethylhexylglycerin, Caprylhydroxamic Acid, Hydrolyzed Hyaluronic Acid, Tricholoma Matsutake Extract, Propylene Glycol, Xanthan Gum, Potassium Hyaluronate, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Sodium Hyaluronate, PEG-9 Diglycidyl Ether/​Sodium Hyaluronate Crosspolymer, Sodium Acetylated Hyaluronate, Phenoxyethanol"
+          <t xml:space="preserve">"Water, Propylene Glycol, Ethylhexyl Methoxycinnamate, Propanediol, Diethylamino Hydroxybenzoyl Hexyl Benzoate, Dimethicone/​Vinyl Dimethicone Crosspolymer, Butylene Glycol, Silica, Phenoxyethanol, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Aminomethyl Propanol, Sorbitan Stearate, Magnesium Aluminum Silicate, Dihydroxypropyl Arginine Hcl, Hydrogenated Lecithin, PEG-9 Dimethicone, Cetearyl Methicone, Tridecane, Undecane, Caprylyl Methicone, Steareth-21, Caprylyl Glycol, Fragrance, Disodium EDTA, Ethylhexylglycerin, Sodium Surfactin, Phytosterols, Sucrose Cocoate, Sodium Benzoate, Zinc Pca, Butyl Methoxydibenzoylmethane, Ectoin, Glycerin, Glucosylrutin, Polyester-7, PEG-60 Hydrogenated Castor Oil, Neopentyl Glycol Diheptanoate, Zea Mays (Corn) Starch, Portulaca Oleracea Extract, Cocamidopropyl Dimethylamine, Hydrolyzed Corn Starch, Hydrolyzed Corn Starch Octenylsuccinate, Isoquercitrin, Scutellaria Baicalensis Root Extract, O-Cymen-5-Ol, Salicylic Acid, Butyrospermum Parkii (Shea) Butter, Hamamelis Virginiana (Witch Hazel) Extract, Buddleja Officinalis Flower Extract, Phenylethyl Resorcinol, Ceramide NP, 1,2-Hexanediol, Lactic Acid, 10-Hydroxydecanoic Acid, Xanthan Gum, Hydrated Silica, Palmitoyl Tripeptide-5, Madecassoside, Asiaticoside, Ceramide AS, Ceramide NS, Glucose, Asiatic Acid, Madecassic Acid, Sodium Hyaluronate, Chondrus Crispus Extract, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Hyaluronic Acid, Sodium Acetylated Hyaluronate, Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Sodium Hyaluronate Crosspolymer, Potassium Hyaluronate, Ceramide AP, Ceramide EOP"
 </t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>Cream-Gel</t>
         </is>
       </c>
       <c r="E306" s="3" t="n">
-        <v>53000</v>
+        <v>68000</v>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>https://down-tx-id.img.susercontent.com/id-11134207-8224o-mj0rks3oblz6f7.webp</t>
+          <t>https://down-bs-id.img.susercontent.com/id-11134207-822wm-mn9jz33nj951e9.webp</t>
         </is>
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/110cdBUdKn</t>
+          <t>https://s.shopee.co.id/4LH4c1uTMh</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>UNITARY Global GlowingSuncare Sunscreen UV Protector SPF 50ml 50+ PA++++</t>
+          <t xml:space="preserve">Amaterasun Acne Sunscreen SPF 40 PA++++ </t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
@@ -11391,32 +11390,32 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>"Zinc Oxide, Isododecane, Cyclopentasiloxane, Water, Glycerin, Butylene Glycol, Cyclohexasiloxane, Neopentyl Glycol Dicaprate, Titanium Dioxide, Polyglyceryl-3 Polydimethylsiloxyethyl Dimethicone, Polymethylsilsesquioxane, Sodium Chloride, Trimethylsiloxysilicate, Triethoxycaprylylsilane, Acrylates/​Polytrimethylsiloxymethacrylate Copolymer, PEG-10 Dimethicone, Disteardimonium Hectorite, Dextrin Palmitate, Lauryl PEG-9 Polydimethylsiloxyethyl Dimethicone, 1,2-Hexanediol, Hydroxyacetophenone, Propanediol, Aluminum Hydroxide, Stearic Acid, Tocopheryl Acetate, Polyhydroxystearic Acid, Lecithin"</t>
+          <t>"Water, Aloe Barbadensis Leaf Water, Ethylhexyl Methoxycinnamate, Camellia Sinensis Leaf Extract, Silica, Butylene Glycol, Glycerin, Butyl Methoxydibenzoylmethane, Dibutyl Adipate, Ethylhexyl Salicylate, Octocrylene, Pentylene Glycol, Methylene Bis-Benzotriazolyl Tetramethylbutylphenol, 1,2-Hexanediol, C12-15 Alkyl Benzoate, Caprylyl Methicone, Diisopropyl Adipate, Methyl Methacrylate Crosspolymer, Panthenol, Salix Alba (Willow) Bark Extract, Rosmarinus Officinalis (Rosemary) Leaf Extract, Bioflavonoids, Brassica Oleracea Italica (Broccoli) Extract, Aloe Barbadensis Leaf Extract, Solanum Lycopersicum (Tomato) Fruit Extract, Helianthus Annuus (Sunflower) Seed Oil, Ethyl Ferulate, Tocopherol, Polyglyceryl-3 Methylglucose Distearate, Behenyl Alcohol, Sodium Acrylates Crosspolymer-2, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Poly C10-30 Alkyl Acrylate, Tromethamine, Decyl Glucoside, Phenoxyethanol, Ammonium Acryloyldimethyltaurate/VP Copolymer, Ethylhexylglycerin, Propanediol, Xanthan Gum, BHT, Ethyl Hexanediol"</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
         <is>
-          <t>Lotion</t>
+          <t>Gel-Cream</t>
         </is>
       </c>
       <c r="E307" s="3" t="n">
-        <v>45000</v>
+        <v>39000</v>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>https://down-bs-id.img.susercontent.com/id-11134207-81ztl-mfrqg4nthzplf5.webp</t>
+          <t>https://down-bs-id.img.susercontent.com/sg-11134201-823ol-mp2gj3wb55vw96.webp</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/185RY1tg1</t>
+          <t>https://s.shopee.co.id/gNmFhDSOM</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>SKIN1004 Madagascar Centella Hyalu-Cica Water-Fit Sun Serum SPF50 PA++++</t>
+          <t>Wardah Sunscreen UV Shield Physical Serum SPF 50+ PA++++</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -11426,33 +11425,33 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Water, Dibutyl Adipate, Propanediol, Diethylamino Hydroxybenzoyl Hexyl Benzoate, Polymethylsilsesquioxane, Ethylhexyl Triazone, Methylene Bis-Benzotriazolyl Tetramethylbutylphenol, Niacinamide, Coco-Caprylate/​Caprate, Caprylyl Methicone, Diethylhexyl Butamido Triazone, Glycerin, 1,2-Hexanediol, Butylene Glycol, Centella Asiatica Extract(9,800Ppm), Betula Platyphylla Japonica Bark Extract, Ginkgo Biloba Leaf Extract, Camellia Sinensis Leaf Extract, Triticum Vulgare (Wheat) Sprout Extract, Medicago Sativa (Alfalfa) Extract, Brassica Oleracea Italica (Broccoli) Sprout Extract, Eruca Sativa Leaf Extract, Camellia Japonica Leaf Extract, Sodium Hyaluronate(10Ppm), Behenyl Alcohol, Poly C10-30 Alkyl Acrylate, Polyglyceryl-3 Methylglucose Distearate, Decyl Glucoside, Tromethamine, Carbomer, Acrylates /​C10-30 Alkyl Acrylate Crosspolymer, Sodium Stearoyl Glutamate, Polyacrylate Crosspolymer-6, Adenosine, Xanthan Gum, T-Butyl Alcohol, Tocopherol, Hydrolyzed Hyaluronic Acid(Ppm), Inositol, Hyaluronic Acid(0.01Ppm), Pentylene Glycol, Ethylhexylglycerin"
+          <t xml:space="preserve">"Aqua, Zinc Oxide, C12-15 Alkyl Benzoate, Propanediol, Maleated Soybean Oil, Glycerol, Octyldodecanol, Esters, Trisiloxane, Biosaccharide Gum-1, Dibutyl Adipate, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Bisabolol, Glycerin, Allantoin, Avena Sativa Kernel Flour, Caprylhydroxamic Acid, Phenoxyethanol, Artemisia Capillaris Flower Extract, Houttuynia Cordata Extract, Haberlea Rhodopensis Leaf Extract, Camellia Sinensis Leaf Extract, Polymethylsilsesquioxane, 1,2-Hexanediol, Arachidyl Alcohol, Butylene Glycol, Triethoxycaprylylsilane, Polyacrylate Crosspolymer-6, Polyhydroxystearic Acid, Behenyl Alcohol, Chlorphenesin, Arachidyl Glucoside"
 </t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>cair</t>
+          <t>Cair</t>
         </is>
       </c>
       <c r="E308" s="3" t="n">
-        <v>144000</v>
+        <v>79000</v>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>https://down-bs-id.img.susercontent.com/id-11134207-822wq-mop92amj5ds18a.webp</t>
+          <t>https://down-tx-id.img.susercontent.com/id-11134207-822wp-mpkiaas9vaiz9e.webp</t>
         </is>
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/3g1NoZ34OI</t>
+          <t>https://s.shopee.co.id/2g8qddhNRU</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>YOU Sunbrella Acne Shield Light Sunscreen SPF40+ PA++++</t>
+          <t>ACNAWAY Mugwort Daily Sunscreen SPF 35 PA+++</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
@@ -11462,33 +11461,33 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Water, Propylene Glycol, Ethylhexyl Methoxycinnamate, Propanediol, Diethylamino Hydroxybenzoyl Hexyl Benzoate, Dimethicone/​Vinyl Dimethicone Crosspolymer, Butylene Glycol, Silica, Phenoxyethanol, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Aminomethyl Propanol, Sorbitan Stearate, Magnesium Aluminum Silicate, Dihydroxypropyl Arginine Hcl, Hydrogenated Lecithin, PEG-9 Dimethicone, Cetearyl Methicone, Tridecane, Undecane, Caprylyl Methicone, Steareth-21, Caprylyl Glycol, Fragrance, Disodium EDTA, Ethylhexylglycerin, Sodium Surfactin, Phytosterols, Sucrose Cocoate, Sodium Benzoate, Zinc Pca, Butyl Methoxydibenzoylmethane, Ectoin, Glycerin, Glucosylrutin, Polyester-7, PEG-60 Hydrogenated Castor Oil, Neopentyl Glycol Diheptanoate, Zea Mays (Corn) Starch, Portulaca Oleracea Extract, Cocamidopropyl Dimethylamine, Hydrolyzed Corn Starch, Hydrolyzed Corn Starch Octenylsuccinate, Isoquercitrin, Scutellaria Baicalensis Root Extract, O-Cymen-5-Ol, Salicylic Acid, Butyrospermum Parkii (Shea) Butter, Hamamelis Virginiana (Witch Hazel) Extract, Buddleja Officinalis Flower Extract, Phenylethyl Resorcinol, Ceramide NP, 1,2-Hexanediol, Lactic Acid, 10-Hydroxydecanoic Acid, Xanthan Gum, Hydrated Silica, Palmitoyl Tripeptide-5, Madecassoside, Asiaticoside, Ceramide AS, Ceramide NS, Glucose, Asiatic Acid, Madecassic Acid, Sodium Hyaluronate, Chondrus Crispus Extract, Hydroxypropyltrimonium Hyaluronate, Hydrolyzed Hyaluronic Acid, Sodium Acetylated Hyaluronate, Hyaluronic Acid, Hydrolyzed Sodium Hyaluronate, Sodium Hyaluronate Crosspolymer, Potassium Hyaluronate, Ceramide AP, Ceramide EOP"
+          <t xml:space="preserve">"Mugwort, Centella Asiatica/​Cica, Panthenol, Aqua, Propylene Glycol, Butyl Methoxydibenzoylmethane, Butylene Glycol, Glycerin, Octocrylene, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Cetearyl Alcohol, Potassium Cetyl Phosphate, Niacinamide, Phenoxyethanol, PEG-20 Stearate, Allantoin, Panthenol, Bisabolol, Artemisia Vulgaris Extract, Sorbitan Olivate, Cetearyl Olivate, Anthyllis Vulneraria Flower Extract, Farnesol, Salicylic Acid, Centella Asiatica Extract, Ryoku-Cha Ekisu, Saururus Chinensis Leaf/​Root Extract, 1,2-Hexanediol, Hydroxyacetophenone, Quaternium-73, Ethylhexylglycerin, Artemisia Vulgaris Oil, Melaleuca Alternifolia (Tea Tree) Leaf Oil"
 </t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>Cream-Gel</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="E309" s="3" t="n">
-        <v>68000</v>
+        <v>46000</v>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>https://down-bs-id.img.susercontent.com/id-11134207-822wm-mn9jz33nj951e9.webp</t>
+          <t>https://down-tx-id.img.susercontent.com/id-11134207-822wp-mor2g3yo44jm2c.webp</t>
         </is>
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/4LH4c1uTMh</t>
+          <t>https://s.shopee.co.id/6L290ehAtY</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amaterasun Acne Sunscreen SPF 40 PA++++ </t>
+          <t>OMG Acne &amp; Oil Control UV Barrier Sunscreen SPF50 PA++++</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -11498,32 +11497,33 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>"Water, Aloe Barbadensis Leaf Water, Ethylhexyl Methoxycinnamate, Camellia Sinensis Leaf Extract, Silica, Butylene Glycol, Glycerin, Butyl Methoxydibenzoylmethane, Dibutyl Adipate, Ethylhexyl Salicylate, Octocrylene, Pentylene Glycol, Methylene Bis-Benzotriazolyl Tetramethylbutylphenol, 1,2-Hexanediol, C12-15 Alkyl Benzoate, Caprylyl Methicone, Diisopropyl Adipate, Methyl Methacrylate Crosspolymer, Panthenol, Salix Alba (Willow) Bark Extract, Rosmarinus Officinalis (Rosemary) Leaf Extract, Bioflavonoids, Brassica Oleracea Italica (Broccoli) Extract, Aloe Barbadensis Leaf Extract, Solanum Lycopersicum (Tomato) Fruit Extract, Helianthus Annuus (Sunflower) Seed Oil, Ethyl Ferulate, Tocopherol, Polyglyceryl-3 Methylglucose Distearate, Behenyl Alcohol, Sodium Acrylates Crosspolymer-2, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Poly C10-30 Alkyl Acrylate, Tromethamine, Decyl Glucoside, Phenoxyethanol, Ammonium Acryloyldimethyltaurate/VP Copolymer, Ethylhexylglycerin, Propanediol, Xanthan Gum, BHT, Ethyl Hexanediol"</t>
+          <t xml:space="preserve">"Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Butyl Methoxydibenzoylmethane, Propanediol, Butylene Glycol, Octocrylene, Aluminum Starch Octenylsuccinate, Cetearyl Olivate, 1,2-Hexanediol, Polymethyl Methacrylate, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Allantoin, Sorbitan Olivate, Aminomethyl Propanol, Propylene Glycol, Chlorphenesin, Salicylic Acid, Lecithin, Ethylhexyl Triazone, Glycyrrhiza Glabra (Licorice) Root Extract, Caprylhydroxamic Acid, Glycerin, Phenoxyethanol, Mentha Piperita Leaf Extract, Polysorbate 60, BHT, Chamomilla Recutita Flower/​Leaf Extract, Potassium Sorbate, Sodium Benzoate, Artemisia Capillaris Flower Extract, Ascorbyl Glucoside, Sodium Phytate"
+</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>Gel-Cream</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E310" s="3" t="n">
-        <v>39000</v>
+        <v>27000</v>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>https://down-bs-id.img.susercontent.com/sg-11134201-823ol-mp2gj3wb55vw96.webp</t>
+          <t>https://down-tx-id.img.susercontent.com/id-11134207-822wo-mpeinlz6dq8d71.webp</t>
         </is>
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/gNmFhDSOM</t>
+          <t>https://s.shopee.co.id/40eEEbC6gC</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>Wardah Sunscreen UV Shield Physical Serum SPF 50+ PA++++</t>
+          <t>Emina Sun Battle Bright Glow SPF 35 PA+++</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
@@ -11533,33 +11533,32 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Aqua, Zinc Oxide, C12-15 Alkyl Benzoate, Propanediol, Maleated Soybean Oil, Glycerol, Octyldodecanol, Esters, Trisiloxane, Biosaccharide Gum-1, Dibutyl Adipate, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, Bisabolol, Glycerin, Allantoin, Avena Sativa Kernel Flour, Caprylhydroxamic Acid, Phenoxyethanol, Artemisia Capillaris Flower Extract, Houttuynia Cordata Extract, Haberlea Rhodopensis Leaf Extract, Camellia Sinensis Leaf Extract, Polymethylsilsesquioxane, 1,2-Hexanediol, Arachidyl Alcohol, Butylene Glycol, Triethoxycaprylylsilane, Polyacrylate Crosspolymer-6, Polyhydroxystearic Acid, Behenyl Alcohol, Chlorphenesin, Arachidyl Glucoside"
-</t>
+          <t>"Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Cetearyl Olivate, Butyl Methoxydibenzoylmethane, Phenoxyethanol, Dipropylene Glycol, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, PPG-3 Benzyl Ether Myristate, Shea Butter (Butyrospermum Parkii), Butylene Glycol, Sorbitan Olivate, Aluminum Starch Octenylsuccinate, Octocrylene, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Chlorphenesin, Propylene Glycol, Aminomethyl Propanol, Fragrance, Allantoin, Tetrasodium EDTA, Glycyrrhiza Glabra (Licorice) Root Extract, Glycerin, Lecithin, Mentha Piperita Leaf Extract, Polysorbate 60, Dimethicone, Dimethicone/​Vinyl Dimethicone Crosspolymer, Glycereth-20, Pentylene Glycol, Amodimethicone, Carbomer, Disodium EDTA, Sodium Hydroxide, BHT, Potassium Sorbate, Sodium Benzoate, Arbutin, Citric Acid, Sodium Sulfite, Acetyl Tyrosine, Saxifraga Sarmentosa Extract, Paeonia Suffruticosa Root Extract, Aminopropyl Ascorbyl Phosphate, Scutellaria Baicalensis Root Extract, Glutathione"</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>Cair</t>
+          <t>Gel</t>
         </is>
       </c>
       <c r="E311" s="3" t="n">
-        <v>79000</v>
+        <v>21000</v>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>https://down-tx-id.img.susercontent.com/id-11134207-822wp-mpkiaas9vaiz9e.webp</t>
+          <t>https://down-bs-id.img.susercontent.com/sg-11134201-7rdwl-m0so3ewaubmtd5.webp</t>
         </is>
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.id/2g8qddhNRU</t>
+          <t>https://s.shopee.co.id/110cnu7m3K</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>ACNAWAY Mugwort Daily Sunscreen SPF 35 PA+++</t>
+          <t xml:space="preserve">OMG Oh My Glow Bright Booster UV Barrier Sunscreen SPF 50 PA++++ </t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -11569,8 +11568,7 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Mugwort, Centella Asiatica/​Cica, Panthenol, Aqua, Propylene Glycol, Butyl Methoxydibenzoylmethane, Butylene Glycol, Glycerin, Octocrylene, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Cetearyl Alcohol, Potassium Cetyl Phosphate, Niacinamide, Phenoxyethanol, PEG-20 Stearate, Allantoin, Panthenol, Bisabolol, Artemisia Vulgaris Extract, Sorbitan Olivate, Cetearyl Olivate, Anthyllis Vulneraria Flower Extract, Farnesol, Salicylic Acid, Centella Asiatica Extract, Ryoku-Cha Ekisu, Saururus Chinensis Leaf/​Root Extract, 1,2-Hexanediol, Hydroxyacetophenone, Quaternium-73, Ethylhexylglycerin, Artemisia Vulgaris Oil, Melaleuca Alternifolia (Tea Tree) Leaf Oil"
-</t>
+          <t>"Aqua, Ethylhexyl Methoxycinnamate, Butyl Methoxydibenzoylmethane, Polymethyl Methacrylate, Propanediol, C14-22 Alcohols, Butylene Glycol, Octocrylene, Phenoxyethanol, Propylene Glycol, Niacinamide, Nylon-12, C12-20 Alkyl Glucoside, Glycyrrhiza Glabra (Licorice) Root Extract, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Allantoin, Bis-Ethylhexyloxyphenol Methoxyphenyl Triazine, Chlorphenesin, Glycerin, Potassium Hydroxide, Lecithin, Tocopheryl Acetate, Fragrance, Dimethicone, Dimethicone/​Vinyl Dimethicone Crosspolymer, Glycereth-20, Pentylene Glycol, Amodimethicone, Carbomer, Disodium EDTA, Sodium Hydroxide, Glucose, Prunus Persica (Peach) Fruit Extract, BHT, Sodium Ascorbyl Phosphate"</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -11579,155 +11577,14 @@
         </is>
       </c>
       <c r="E312" s="3" t="n">
-        <v>46000</v>
+        <v>23000</v>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>https://down-tx-id.img.susercontent.com/id-11134207-822wp-mor2g3yo44jm2c.webp</t>
+          <t>https://down-bs-id.img.susercontent.com/id-11134207-822wr-mpdh9zjf5k3vd9.webp</t>
         </is>
       </c>
       <c r="G312" s="4" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.id/6L290ehAtY</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="3" t="inlineStr">
-        <is>
-          <t>OMG Acne &amp; Oil Control UV Barrier Sunscreen SPF50 PA++++</t>
-        </is>
-      </c>
-      <c r="B313" s="3" t="inlineStr">
-        <is>
-          <t>Sunscreen</t>
-        </is>
-      </c>
-      <c r="C313" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Butyl Methoxydibenzoylmethane, Propanediol, Butylene Glycol, Octocrylene, Aluminum Starch Octenylsuccinate, Cetearyl Olivate, 1,2-Hexanediol, Polymethyl Methacrylate, Ammonium Acryloyldimethyltaurate/​VP Copolymer, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Allantoin, Sorbitan Olivate, Aminomethyl Propanol, Propylene Glycol, Chlorphenesin, Salicylic Acid, Lecithin, Ethylhexyl Triazone, Glycyrrhiza Glabra (Licorice) Root Extract, Caprylhydroxamic Acid, Glycerin, Phenoxyethanol, Mentha Piperita Leaf Extract, Polysorbate 60, BHT, Chamomilla Recutita Flower/​Leaf Extract, Potassium Sorbate, Sodium Benzoate, Artemisia Capillaris Flower Extract, Ascorbyl Glucoside, Sodium Phytate"
-</t>
-        </is>
-      </c>
-      <c r="D313" s="3" t="inlineStr">
-        <is>
-          <t>Gel</t>
-        </is>
-      </c>
-      <c r="E313" s="3" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F313" s="4" t="inlineStr">
-        <is>
-          <t>https://down-tx-id.img.susercontent.com/id-11134207-822wo-mpeinlz6dq8d71.webp</t>
-        </is>
-      </c>
-      <c r="G313" s="4" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.id/40eEEbC6gC</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="3" t="inlineStr">
-        <is>
-          <t>WARDAH UV Shield Acne Calming Sunscreen Moisturizer SPF 35 PA+++</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>Sunscreen</t>
-        </is>
-      </c>
-      <c r="C314" s="3" t="inlineStr">
-        <is>
-          <t>"Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Butyl Methoxydibenzoylmethane, Aluminium Starch Octenylsuccinate, Phenoxyethanol, Cetearyl Olivate, Propanediol, Butylene Glycol, Octocrylene, Acrylates C10-30 Alkyl Acrylate Crosspolymer, Sorbitan Olivate, Polymethyl Methacrylate, Aminomethyl Propanol, Allantoin, Salicylic Acid, Xanthan Gum, Triethylene Glycol, Ethylhexyl Triazone, Tetrasodium EDTA, Lecithin, BHT"</t>
-        </is>
-      </c>
-      <c r="D314" s="3" t="inlineStr">
-        <is>
-          <t>Gel</t>
-        </is>
-      </c>
-      <c r="E314" s="3" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F314" s="4" t="inlineStr">
-        <is>
-          <t>https://down-bs-id.img.susercontent.com/sg-11134201-823ow-mpd2fnmfbmz34e.webp</t>
-        </is>
-      </c>
-      <c r="G314" s="4" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.id/2BCaBFrz4r</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="3" t="inlineStr">
-        <is>
-          <t>Emina Sun Battle Bright Glow SPF 35 PA+++</t>
-        </is>
-      </c>
-      <c r="B315" s="3" t="inlineStr">
-        <is>
-          <t>Sunscreen</t>
-        </is>
-      </c>
-      <c r="C315" s="3" t="inlineStr">
-        <is>
-          <t>"Aqua, Ethylhexyl Methoxycinnamate, Niacinamide, Cetearyl Olivate, Butyl Methoxydibenzoylmethane, Phenoxyethanol, Dipropylene Glycol, Hydroxyethyl Acrylate/​Sodium Acryloyldimethyl Taurate Copolymer, PPG-3 Benzyl Ether Myristate, Shea Butter (Butyrospermum Parkii), Butylene Glycol, Sorbitan Olivate, Aluminum Starch Octenylsuccinate, Octocrylene, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Chlorphenesin, Propylene Glycol, Aminomethyl Propanol, Fragrance, Allantoin, Tetrasodium EDTA, Glycyrrhiza Glabra (Licorice) Root Extract, Glycerin, Lecithin, Mentha Piperita Leaf Extract, Polysorbate 60, Dimethicone, Dimethicone/​Vinyl Dimethicone Crosspolymer, Glycereth-20, Pentylene Glycol, Amodimethicone, Carbomer, Disodium EDTA, Sodium Hydroxide, BHT, Potassium Sorbate, Sodium Benzoate, Arbutin, Citric Acid, Sodium Sulfite, Acetyl Tyrosine, Saxifraga Sarmentosa Extract, Paeonia Suffruticosa Root Extract, Aminopropyl Ascorbyl Phosphate, Scutellaria Baicalensis Root Extract, Glutathione"</t>
-        </is>
-      </c>
-      <c r="D315" s="3" t="inlineStr">
-        <is>
-          <t>Gel</t>
-        </is>
-      </c>
-      <c r="E315" s="3" t="n">
-        <v>21000</v>
-      </c>
-      <c r="F315" s="4" t="inlineStr">
-        <is>
-          <t>https://down-bs-id.img.susercontent.com/sg-11134201-7rdwl-m0so3ewaubmtd5.webp</t>
-        </is>
-      </c>
-      <c r="G315" s="4" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.id/110cnu7m3K</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OMG Oh My Glow Bright Booster UV Barrier Sunscreen SPF 50 PA++++ </t>
-        </is>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>Sunscreen</t>
-        </is>
-      </c>
-      <c r="C316" s="3" t="inlineStr">
-        <is>
-          <t>"Aqua, Ethylhexyl Methoxycinnamate, Butyl Methoxydibenzoylmethane, Polymethyl Methacrylate, Propanediol, C14-22 Alcohols, Butylene Glycol, Octocrylene, Phenoxyethanol, Propylene Glycol, Niacinamide, Nylon-12, C12-20 Alkyl Glucoside, Glycyrrhiza Glabra (Licorice) Root Extract, Acrylates/​C10-30 Alkyl Acrylate Crosspolymer, Allantoin, Bis-Ethylhexyloxyphenol Methoxyphenyl Triazine, Chlorphenesin, Glycerin, Potassium Hydroxide, Lecithin, Tocopheryl Acetate, Fragrance, Dimethicone, Dimethicone/​Vinyl Dimethicone Crosspolymer, Glycereth-20, Pentylene Glycol, Amodimethicone, Carbomer, Disodium EDTA, Sodium Hydroxide, Glucose, Prunus Persica (Peach) Fruit Extract, BHT, Sodium Ascorbyl Phosphate"</t>
-        </is>
-      </c>
-      <c r="D316" s="3" t="inlineStr">
-        <is>
-          <t>Cream</t>
-        </is>
-      </c>
-      <c r="E316" s="3" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F316" s="4" t="inlineStr">
-        <is>
-          <t>https://down-bs-id.img.susercontent.com/id-11134207-822wr-mpdh9zjf5k3vd9.webp</t>
-        </is>
-      </c>
-      <c r="G316" s="4" t="inlineStr">
         <is>
           <t>https://s.shopee.co.id/2qSH1pcAFX</t>
         </is>
@@ -12279,10 +12136,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId542"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId543"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId548"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId549"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId550"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId551"/>
@@ -12354,14 +12211,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId617"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId618"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId627"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
